--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_winter_week.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_winter_week.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cleme\Documents\heig-vd\s5\ResoHT\mini_projet_trey\courbe de charge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5373B07C-4217-4EB5-BA71-C07D57B4D03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613FBEA0-5028-4413-B1FE-ECFEAE6F65DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
@@ -634,76 +634,76 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6822.2942639472403</v>
+        <v>6.8222942639472404</v>
       </c>
       <c r="C3">
-        <v>2242.3796854123898</v>
+        <v>2.2423796854123901</v>
       </c>
       <c r="D3">
-        <v>9956.1193184084004</v>
+        <v>9.9561193184083994</v>
       </c>
       <c r="E3">
-        <v>3272.41816922505</v>
+        <v>3.27241816922505</v>
       </c>
       <c r="F3">
-        <v>1646.66684231365</v>
+        <v>1.6466668423136499</v>
       </c>
       <c r="G3">
-        <v>541.23321759356895</v>
+        <v>0.54123321759356902</v>
       </c>
       <c r="H3">
-        <v>4558.0553106212401</v>
+        <v>4.5580553106212403</v>
       </c>
       <c r="I3">
-        <v>1498.1603311273</v>
+        <v>1.4981603311273</v>
       </c>
       <c r="J3">
-        <v>2028.21675350701</v>
+        <v>2.0282167535070101</v>
       </c>
       <c r="K3">
-        <v>666.64260873523097</v>
+        <v>0.66664260873523096</v>
       </c>
       <c r="L3">
-        <v>7295.8620841683296</v>
+        <v>7.2958620841683297</v>
       </c>
       <c r="M3">
-        <v>2398.03390064326</v>
+        <v>2.3980339006432598</v>
       </c>
       <c r="N3">
-        <v>10268.775967935801</v>
+        <v>10.268775967935801</v>
       </c>
       <c r="O3">
-        <v>3375.1834403032099</v>
+        <v>3.3751834403032102</v>
       </c>
       <c r="P3">
-        <v>6038.2559786239099</v>
+        <v>6.0382559786239103</v>
       </c>
       <c r="Q3">
-        <v>1984.6787631749201</v>
+        <v>1.9846787631749201</v>
       </c>
       <c r="R3">
-        <v>761.54187096774206</v>
+        <v>0.76154187096774195</v>
       </c>
       <c r="S3">
-        <v>250.30670841526899</v>
+        <v>0.25030670841526897</v>
       </c>
       <c r="T3">
-        <v>4163.5883126252502</v>
+        <v>4.16358831262525</v>
       </c>
       <c r="U3">
-        <v>1368.5052988683999</v>
+        <v>1.3685052988684001</v>
       </c>
       <c r="V3">
-        <v>1859.6390322580601</v>
+        <v>1.85963903225806</v>
       </c>
       <c r="W3">
-        <v>611.23379127342798</v>
+        <v>0.61123379127342803</v>
       </c>
       <c r="X3">
-        <v>2120.9255241935398</v>
+        <v>2.1209255241935399</v>
       </c>
       <c r="Y3">
-        <v>697.11450807056701</v>
+        <v>0.69711450807056696</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -758,76 +758,76 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="B4">
-        <v>6168.7711417674</v>
+        <v>6.1687711417674</v>
       </c>
       <c r="C4">
-        <v>2027.5770227850101</v>
+        <v>2.0275770227850098</v>
       </c>
       <c r="D4">
-        <v>9030.2367289201902</v>
+        <v>9.0302367289201904</v>
       </c>
       <c r="E4">
-        <v>2968.0952787984302</v>
+        <v>2.96809527879843</v>
       </c>
       <c r="F4">
-        <v>1566.3919070398799</v>
+        <v>1.56639190703988</v>
       </c>
       <c r="G4">
-        <v>514.84812232481795</v>
+        <v>0.51484812232481802</v>
       </c>
       <c r="H4">
-        <v>4099.5527054108197</v>
+        <v>4.0995527054108196</v>
       </c>
       <c r="I4">
-        <v>1347.45781261154</v>
+        <v>1.34745781261154</v>
       </c>
       <c r="J4">
-        <v>1824.1949498997999</v>
+        <v>1.8241949498998</v>
       </c>
       <c r="K4">
-        <v>599.58388477961603</v>
+        <v>0.59958388477961599</v>
       </c>
       <c r="L4">
-        <v>6561.9587975951899</v>
+        <v>6.5619587975951896</v>
       </c>
       <c r="M4">
-        <v>2156.8115556081402</v>
+        <v>2.1568115556081402</v>
       </c>
       <c r="N4">
-        <v>9235.8221723446895</v>
+        <v>9.2358221723446903</v>
       </c>
       <c r="O4">
-        <v>3035.66794630821</v>
+        <v>3.0356679463082101</v>
       </c>
       <c r="P4">
-        <v>5430.85744822979</v>
+        <v>5.4308574482297898</v>
       </c>
       <c r="Q4">
-        <v>1785.0365207253701</v>
+        <v>1.78503652072537</v>
       </c>
       <c r="R4">
-        <v>739.84877419354802</v>
+        <v>0.739848774193548</v>
       </c>
       <c r="S4">
-        <v>243.17653231348501</v>
+        <v>0.24317653231348499</v>
       </c>
       <c r="T4">
-        <v>3744.7658196392699</v>
+        <v>3.7447658196392699</v>
       </c>
       <c r="U4">
-        <v>1230.8450025325201</v>
+        <v>1.2308450025325199</v>
       </c>
       <c r="V4">
-        <v>1806.66580645161</v>
+        <v>1.8066658064516099</v>
       </c>
       <c r="W4">
-        <v>593.82233395079697</v>
+        <v>0.59382233395079698</v>
       </c>
       <c r="X4">
-        <v>2060.5093548386999</v>
+        <v>2.0605093548386999</v>
       </c>
       <c r="Y4">
-        <v>677.25667350783704</v>
+        <v>0.67725667350783703</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -882,76 +882,76 @@
         <v>2.0833333333333301E-2</v>
       </c>
       <c r="B5">
-        <v>5602.0741183011096</v>
+        <v>5.6020741183011102</v>
       </c>
       <c r="C5">
-        <v>1841.31271871947</v>
+        <v>1.84131271871947</v>
       </c>
       <c r="D5">
-        <v>8219.4889229075307</v>
+        <v>8.2194889229075301</v>
       </c>
       <c r="E5">
-        <v>2701.6153616534398</v>
+        <v>2.70161536165344</v>
       </c>
       <c r="F5">
-        <v>1497.60297304285</v>
+        <v>1.4976029730428499</v>
       </c>
       <c r="G5">
-        <v>492.23829310779701</v>
+        <v>0.49223829310779699</v>
       </c>
       <c r="H5">
-        <v>3701.73426853707</v>
+        <v>3.70173426853707</v>
       </c>
       <c r="I5">
-        <v>1216.7012156640401</v>
+        <v>1.21670121566404</v>
       </c>
       <c r="J5">
-        <v>1647.1760320641199</v>
+        <v>1.64717603206412</v>
       </c>
       <c r="K5">
-        <v>541.40058017106799</v>
+        <v>0.54140058017106796</v>
       </c>
       <c r="L5">
-        <v>5925.1897695390699</v>
+        <v>5.9251897695390703</v>
       </c>
       <c r="M5">
-        <v>1947.5156974158999</v>
+        <v>1.9475156974159</v>
       </c>
       <c r="N5">
-        <v>8339.5828496993909</v>
+        <v>8.33958284969939</v>
       </c>
       <c r="O5">
-        <v>2741.0883265184402</v>
+        <v>2.7410883265184398</v>
       </c>
       <c r="P5">
-        <v>4903.8498997995903</v>
+        <v>4.9038498997995896</v>
       </c>
       <c r="Q5">
-        <v>1611.81751624708</v>
+        <v>1.61181751624708</v>
       </c>
       <c r="R5">
-        <v>721.58090322580597</v>
+        <v>0.72158090322580604</v>
       </c>
       <c r="S5">
-        <v>237.17217349092999</v>
+        <v>0.23717217349093001</v>
       </c>
       <c r="T5">
-        <v>3381.3757154308601</v>
+        <v>3.3813757154308601</v>
       </c>
       <c r="U5">
-        <v>1111.4044512999301</v>
+        <v>1.1114044512999299</v>
       </c>
       <c r="V5">
-        <v>1762.0567741935399</v>
+        <v>1.76205677419354</v>
       </c>
       <c r="W5">
-        <v>579.16005410015998</v>
+        <v>0.57916005410016003</v>
       </c>
       <c r="X5">
-        <v>2009.63258064516</v>
+        <v>2.0096325806451598</v>
       </c>
       <c r="Y5">
-        <v>660.53428650764397</v>
+        <v>0.66053428650764401</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -1006,76 +1006,76 @@
         <v>3.125E-2</v>
       </c>
       <c r="B6">
-        <v>5122.2031935483801</v>
+        <v>5.1222031935483798</v>
       </c>
       <c r="C6">
-        <v>1683.5867732157601</v>
+        <v>1.6835867732157599</v>
       </c>
       <c r="D6">
-        <v>7549.0776096117697</v>
+        <v>7.5490776096117704</v>
       </c>
       <c r="E6">
-        <v>2481.2618190410299</v>
+        <v>2.48126181904103</v>
       </c>
       <c r="F6">
-        <v>1440.3000403225799</v>
+        <v>1.4403000403225801</v>
       </c>
       <c r="G6">
-        <v>473.40372994250703</v>
+        <v>0.47340372994250701</v>
       </c>
       <c r="H6">
-        <v>3364.6</v>
+        <v>3.3645999999999998</v>
       </c>
       <c r="I6">
-        <v>1105.8905402848</v>
+        <v>1.1058905402848</v>
       </c>
       <c r="J6">
-        <v>1497.16</v>
+        <v>1.49716</v>
       </c>
       <c r="K6">
-        <v>492.09269490958599</v>
+        <v>0.49209269490958601</v>
       </c>
       <c r="L6">
-        <v>5385.5550000000003</v>
+        <v>5.3855550000000001</v>
       </c>
       <c r="M6">
-        <v>1770.14632606655</v>
+        <v>1.77014632606655</v>
       </c>
       <c r="N6">
-        <v>7580.05799999999</v>
+        <v>7.5800579999999904</v>
       </c>
       <c r="O6">
-        <v>2491.4445809338799</v>
+        <v>2.4914445809338801</v>
       </c>
       <c r="P6">
-        <v>4457.2333333333299</v>
+        <v>4.4572333333333303</v>
       </c>
       <c r="Q6">
-        <v>1465.0217497400599</v>
+        <v>1.4650217497400599</v>
       </c>
       <c r="R6">
-        <v>706.738258064516</v>
+        <v>0.70673825806451596</v>
       </c>
       <c r="S6">
-        <v>232.29363194760299</v>
+        <v>0.232293631947604</v>
       </c>
       <c r="T6">
-        <v>3073.4180000000001</v>
+        <v>3.0734180000000002</v>
       </c>
       <c r="U6">
-        <v>1010.18364517061</v>
+        <v>1.0101836451706101</v>
       </c>
       <c r="V6">
-        <v>1725.81193548387</v>
+        <v>1.7258119354838699</v>
       </c>
       <c r="W6">
-        <v>567.24695172151803</v>
+        <v>0.56724695172151796</v>
       </c>
       <c r="X6">
-        <v>1968.2952016129</v>
+        <v>1.9682952016129001</v>
       </c>
       <c r="Y6">
-        <v>646.94734706998702</v>
+        <v>0.64694734706998702</v>
       </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -1130,76 +1130,76 @@
         <v>4.1666666666666699E-2</v>
       </c>
       <c r="B7">
-        <v>4766.1591963281398</v>
+        <v>4.7661591963281396</v>
       </c>
       <c r="C7">
-        <v>1566.5607705851201</v>
+        <v>1.5665607705851201</v>
       </c>
       <c r="D7">
-        <v>7063.0380425643698</v>
+        <v>7.0630380425643704</v>
       </c>
       <c r="E7">
-        <v>2321.5083388645298</v>
+        <v>2.3215083388645299</v>
       </c>
       <c r="F7">
-        <v>1395.4464257547299</v>
+        <v>1.3954464257547301</v>
       </c>
       <c r="G7">
-        <v>458.66105977423803</v>
+        <v>0.45866105977423799</v>
       </c>
       <c r="H7">
-        <v>3115.12064128256</v>
+        <v>3.1151206412825601</v>
       </c>
       <c r="I7">
-        <v>1023.89064050416</v>
+        <v>1.0238906405041599</v>
       </c>
       <c r="J7">
-        <v>1386.1481362725399</v>
+        <v>1.3861481362725401</v>
       </c>
       <c r="K7">
-        <v>455.60485981609003</v>
+        <v>0.45560485981609</v>
       </c>
       <c r="L7">
-        <v>4986.2252705410801</v>
+        <v>4.9862252705410803</v>
       </c>
       <c r="M7">
-        <v>1638.8929912680301</v>
+        <v>1.6388929912680299</v>
       </c>
       <c r="N7">
-        <v>7018.0096112224401</v>
+        <v>7.0180096112224399</v>
       </c>
       <c r="O7">
-        <v>2306.7082092013102</v>
+        <v>2.30670820920131</v>
       </c>
       <c r="P7">
-        <v>4126.73707414829</v>
+        <v>4.1267370741482896</v>
       </c>
       <c r="Q7">
-        <v>1356.3928825248699</v>
+        <v>1.3563928825248699</v>
       </c>
       <c r="R7">
-        <v>694.179096774193</v>
+        <v>0.69417909677419298</v>
       </c>
       <c r="S7">
-        <v>228.16563525709699</v>
+        <v>0.22816563525709699</v>
       </c>
       <c r="T7">
-        <v>2845.5292905811598</v>
+        <v>2.84552929058116</v>
       </c>
       <c r="U7">
-        <v>935.28024863491396</v>
+        <v>0.93528024863491399</v>
       </c>
       <c r="V7">
-        <v>1695.1432258064499</v>
+        <v>1.69514322580645</v>
       </c>
       <c r="W7">
-        <v>557.16663432420501</v>
+        <v>0.55716663432420499</v>
       </c>
       <c r="X7">
-        <v>1933.31741935483</v>
+        <v>1.9333174193548299</v>
       </c>
       <c r="Y7">
-        <v>635.45070600735403</v>
+        <v>0.63545070600735398</v>
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
@@ -1254,76 +1254,76 @@
         <v>5.2083333333333301E-2</v>
       </c>
       <c r="B8">
-        <v>4514.4205025534902</v>
+        <v>4.5144205025534898</v>
       </c>
       <c r="C8">
-        <v>1483.8182632829</v>
+        <v>1.4838182632829</v>
       </c>
       <c r="D8">
-        <v>6730.9576197746901</v>
+        <v>6.7309576197746903</v>
       </c>
       <c r="E8">
-        <v>2212.3587822524901</v>
+        <v>2.2123587822524899</v>
       </c>
       <c r="F8">
-        <v>1359.8980313853499</v>
+        <v>1.3598980313853499</v>
       </c>
       <c r="G8">
-        <v>446.976867580391</v>
+        <v>0.44697686758039101</v>
       </c>
       <c r="H8">
-        <v>2939.8108216432802</v>
+        <v>2.9398108216432801</v>
       </c>
       <c r="I8">
-        <v>966.26908930696197</v>
+        <v>0.96626908930696198</v>
       </c>
       <c r="J8">
-        <v>1308.1397995991899</v>
+        <v>1.3081397995991899</v>
       </c>
       <c r="K8">
-        <v>429.96475948011903</v>
+        <v>0.42996475948011897</v>
       </c>
       <c r="L8">
-        <v>4705.6151903807604</v>
+        <v>4.7056151903807599</v>
       </c>
       <c r="M8">
-        <v>1546.66091816636</v>
+        <v>1.54666091816636</v>
       </c>
       <c r="N8">
-        <v>6623.05668937875</v>
+        <v>6.6230566893787497</v>
       </c>
       <c r="O8">
-        <v>2176.89346149734</v>
+        <v>2.1768934614973401</v>
       </c>
       <c r="P8">
-        <v>3894.4964595858301</v>
+        <v>3.89449645958583</v>
       </c>
       <c r="Q8">
-        <v>1280.05908394122</v>
+        <v>1.28005908394122</v>
       </c>
       <c r="R8">
-        <v>682.76167741935399</v>
+        <v>0.68276167741935401</v>
       </c>
       <c r="S8">
-        <v>224.412910993</v>
+        <v>0.22441291099300001</v>
       </c>
       <c r="T8">
-        <v>2685.3912785571101</v>
+        <v>2.6853912785571099</v>
       </c>
       <c r="U8">
-        <v>882.64542944766799</v>
+        <v>0.882645429447668</v>
       </c>
       <c r="V8">
-        <v>1667.2625806451599</v>
+        <v>1.66726258064516</v>
       </c>
       <c r="W8">
-        <v>548.00270941755696</v>
+        <v>0.54800270941755602</v>
       </c>
       <c r="X8">
-        <v>1901.51943548387</v>
+        <v>1.90151943548387</v>
       </c>
       <c r="Y8">
-        <v>624.99921413223296</v>
+        <v>0.62499921413223303</v>
       </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
@@ -1378,76 +1378,76 @@
         <v>6.25E-2</v>
       </c>
       <c r="B9">
-        <v>4348.8271010407898</v>
+        <v>4.34882710104079</v>
       </c>
       <c r="C9">
-        <v>1429.39034428318</v>
+        <v>1.4293903442831799</v>
       </c>
       <c r="D9">
-        <v>6518.1452502926604</v>
+        <v>6.51814525029266</v>
       </c>
       <c r="E9">
-        <v>2142.4107390182999</v>
+        <v>2.1424107390182998</v>
       </c>
       <c r="F9">
-        <v>1334.06067861529</v>
+        <v>1.33406067861529</v>
       </c>
       <c r="G9">
-        <v>438.48454040497501</v>
+        <v>0.43848454040497498</v>
       </c>
       <c r="H9">
-        <v>2825.1851703406801</v>
+        <v>2.8251851703406801</v>
       </c>
       <c r="I9">
-        <v>928.59345967802005</v>
+        <v>0.92859345967801998</v>
       </c>
       <c r="J9">
-        <v>1257.1343486973899</v>
+        <v>1.25713434869739</v>
       </c>
       <c r="K9">
-        <v>413.200078491216</v>
+        <v>0.41320007849121598</v>
       </c>
       <c r="L9">
-        <v>4522.1393687374702</v>
+        <v>4.52213936873747</v>
       </c>
       <c r="M9">
-        <v>1486.35533190758</v>
+        <v>1.48635533190758</v>
       </c>
       <c r="N9">
-        <v>6364.8182404809604</v>
+        <v>6.3648182404809601</v>
       </c>
       <c r="O9">
-        <v>2092.0145879985898</v>
+        <v>2.0920145879985901</v>
       </c>
       <c r="P9">
-        <v>3742.6468269872998</v>
+        <v>3.7426468269873001</v>
       </c>
       <c r="Q9">
-        <v>1230.1485233288299</v>
+        <v>1.2301485233288301</v>
       </c>
       <c r="R9">
-        <v>673.62774193548398</v>
+        <v>0.67362774193548403</v>
       </c>
       <c r="S9">
-        <v>221.41073158172199</v>
+        <v>0.221410731581722</v>
       </c>
       <c r="T9">
-        <v>2580.6856553106199</v>
+        <v>2.5806856553106199</v>
       </c>
       <c r="U9">
-        <v>848.230355363699</v>
+        <v>0.84823035536369895</v>
       </c>
       <c r="V9">
-        <v>1644.95806451612</v>
+        <v>1.6449580645161199</v>
       </c>
       <c r="W9">
-        <v>540.67156949223795</v>
+        <v>0.54067156949223805</v>
       </c>
       <c r="X9">
-        <v>1876.08104838709</v>
+        <v>1.87608104838709</v>
       </c>
       <c r="Y9">
-        <v>616.63802063213598</v>
+        <v>0.61663802063213602</v>
       </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -1502,76 +1502,76 @@
         <v>7.2916666666666699E-2</v>
       </c>
       <c r="B10">
-        <v>4241.1177653371196</v>
+        <v>4.2411177653371199</v>
       </c>
       <c r="C10">
-        <v>1393.98799765801</v>
+        <v>1.3939879976580101</v>
       </c>
       <c r="D10">
-        <v>6374.6309326092396</v>
+        <v>6.3746309326092403</v>
       </c>
       <c r="E10">
-        <v>2095.23986393017</v>
+        <v>2.0952398639301699</v>
       </c>
       <c r="F10">
-        <v>1315.8806600297301</v>
+        <v>1.3158806600297299</v>
       </c>
       <c r="G10">
-        <v>432.509057264045</v>
+        <v>0.43250905726404498</v>
       </c>
       <c r="H10">
-        <v>2751.0156312625199</v>
+        <v>2.7510156312625198</v>
       </c>
       <c r="I10">
-        <v>904.215111094588</v>
+        <v>0.90421511109458796</v>
       </c>
       <c r="J10">
-        <v>1224.1308216432799</v>
+        <v>1.22413082164328</v>
       </c>
       <c r="K10">
-        <v>402.35234373369002</v>
+        <v>0.40235234373369</v>
       </c>
       <c r="L10">
-        <v>4403.4197194388698</v>
+        <v>4.4034197194388698</v>
       </c>
       <c r="M10">
-        <v>1447.33407021072</v>
+        <v>1.44733407021072</v>
       </c>
       <c r="N10">
-        <v>6197.7227735470897</v>
+        <v>6.1977227735470901</v>
       </c>
       <c r="O10">
-        <v>2037.09296396998</v>
+        <v>2.0370929639699802</v>
       </c>
       <c r="P10">
-        <v>3644.39118236472</v>
+        <v>3.6443911823647199</v>
       </c>
       <c r="Q10">
-        <v>1197.8534546972901</v>
+        <v>1.1978534546972901</v>
       </c>
       <c r="R10">
-        <v>666.77729032258003</v>
+        <v>0.66677729032258004</v>
       </c>
       <c r="S10">
-        <v>219.159097023264</v>
+        <v>0.219159097023264</v>
       </c>
       <c r="T10">
-        <v>2512.9349579158302</v>
+        <v>2.5129349579158302</v>
       </c>
       <c r="U10">
-        <v>825.96177801524902</v>
+        <v>0.82596177801524895</v>
       </c>
       <c r="V10">
-        <v>1628.2296774193501</v>
+        <v>1.6282296774193501</v>
       </c>
       <c r="W10">
-        <v>535.17321454824901</v>
+        <v>0.53517321454824895</v>
       </c>
       <c r="X10">
-        <v>1857.00225806451</v>
+        <v>1.85700225806451</v>
       </c>
       <c r="Y10">
-        <v>610.36712550706295</v>
+        <v>0.61036712550706296</v>
       </c>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
@@ -1626,76 +1626,76 @@
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="B11">
-        <v>4172.4516778072202</v>
+        <v>4.1724516778072198</v>
       </c>
       <c r="C11">
-        <v>1371.41854612211</v>
+        <v>1.37141854612211</v>
       </c>
       <c r="D11">
-        <v>6267.9354298177304</v>
+        <v>6.2679354298177303</v>
       </c>
       <c r="E11">
-        <v>2060.17074806853</v>
+        <v>2.0601707480685301</v>
       </c>
       <c r="F11">
-        <v>1303.9888373521201</v>
+        <v>1.30398883735212</v>
       </c>
       <c r="G11">
-        <v>428.60040416830799</v>
+        <v>0.42860040416830802</v>
       </c>
       <c r="H11">
-        <v>2703.8168336673298</v>
+        <v>2.7038168336673301</v>
       </c>
       <c r="I11">
-        <v>888.70161654149501</v>
+        <v>0.88870161654149504</v>
       </c>
       <c r="J11">
-        <v>1203.1285771543</v>
+        <v>1.2031285771543001</v>
       </c>
       <c r="K11">
-        <v>395.44923979708199</v>
+        <v>0.39544923979708202</v>
       </c>
       <c r="L11">
-        <v>4327.8708517034001</v>
+        <v>4.3278708517034001</v>
       </c>
       <c r="M11">
-        <v>1422.50235822181</v>
+        <v>1.4225023582218099</v>
       </c>
       <c r="N11">
-        <v>6091.3892945891703</v>
+        <v>6.0913892945891703</v>
       </c>
       <c r="O11">
-        <v>2002.1428395881501</v>
+        <v>2.0021428395881502</v>
       </c>
       <c r="P11">
-        <v>3581.8648630594498</v>
+        <v>3.5818648630594501</v>
       </c>
       <c r="Q11">
-        <v>1177.3020473863</v>
+        <v>1.1773020473863001</v>
       </c>
       <c r="R11">
-        <v>662.21032258064497</v>
+        <v>0.66221032258064505</v>
       </c>
       <c r="S11">
-        <v>217.65800731762499</v>
+        <v>0.217658007317625</v>
       </c>
       <c r="T11">
-        <v>2469.8208777555101</v>
+        <v>2.46982087775551</v>
       </c>
       <c r="U11">
-        <v>811.79086515714403</v>
+        <v>0.81179086515714405</v>
       </c>
       <c r="V11">
-        <v>1617.07741935483</v>
+        <v>1.6170774193548301</v>
       </c>
       <c r="W11">
-        <v>531.50764458559001</v>
+        <v>0.53150764458558997</v>
       </c>
       <c r="X11">
-        <v>1844.28306451612</v>
+        <v>1.8442830645161199</v>
       </c>
       <c r="Y11">
-        <v>606.18652875701503</v>
+        <v>0.60618652875701495</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -1750,76 +1750,76 @@
         <v>9.375E-2</v>
       </c>
       <c r="B12">
-        <v>4123.3072143642103</v>
+        <v>4.1233072143642104</v>
       </c>
       <c r="C12">
-        <v>1355.26554213085</v>
+        <v>1.3552655421308499</v>
       </c>
       <c r="D12">
-        <v>6181.7885789519096</v>
+        <v>6.1817885789519096</v>
       </c>
       <c r="E12">
-        <v>2031.8556474777199</v>
+        <v>2.0318556474777201</v>
       </c>
       <c r="F12">
-        <v>1295.2411126284801</v>
+        <v>1.29524111262848</v>
       </c>
       <c r="G12">
-        <v>425.72516609516703</v>
+        <v>0.42572516609516697</v>
       </c>
       <c r="H12">
-        <v>2670.10340681362</v>
+        <v>2.6701034068136198</v>
       </c>
       <c r="I12">
-        <v>877.620549003571</v>
+        <v>0.877620549003571</v>
       </c>
       <c r="J12">
-        <v>1188.1269739478901</v>
+        <v>1.1881269739478899</v>
       </c>
       <c r="K12">
-        <v>390.51845127093401</v>
+        <v>0.39051845127093399</v>
       </c>
       <c r="L12">
-        <v>4273.9073747494904</v>
+        <v>4.2739073747494896</v>
       </c>
       <c r="M12">
-        <v>1404.76542108688</v>
+        <v>1.4047654210868801</v>
       </c>
       <c r="N12">
-        <v>6015.4368096192302</v>
+        <v>6.0154368096192297</v>
       </c>
       <c r="O12">
-        <v>1977.17846502969</v>
+        <v>1.97717846502969</v>
       </c>
       <c r="P12">
-        <v>3537.2032064128198</v>
+        <v>3.53720320641282</v>
       </c>
       <c r="Q12">
-        <v>1162.6224707356</v>
+        <v>1.1626224707356001</v>
       </c>
       <c r="R12">
-        <v>658.78509677419299</v>
+        <v>0.65878509677419295</v>
       </c>
       <c r="S12">
-        <v>216.53219003839601</v>
+        <v>0.21653219003839599</v>
       </c>
       <c r="T12">
-        <v>2439.0251062124198</v>
+        <v>2.4390251062124202</v>
       </c>
       <c r="U12">
-        <v>801.66878454421203</v>
+        <v>0.80166878454421198</v>
       </c>
       <c r="V12">
-        <v>1608.7132258064501</v>
+        <v>1.60871322580645</v>
       </c>
       <c r="W12">
-        <v>528.758467113596</v>
+        <v>0.52875846711359598</v>
       </c>
       <c r="X12">
-        <v>1834.74366935483</v>
+        <v>1.83474366935483</v>
       </c>
       <c r="Y12">
-        <v>603.05108119447902</v>
+        <v>0.60305108119447903</v>
       </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -1874,76 +1874,76 @@
         <v>0.104166666666667</v>
       </c>
       <c r="B13">
-        <v>4103.10478382571</v>
+        <v>4.1031047838257102</v>
       </c>
       <c r="C13">
-        <v>1348.62532432686</v>
+        <v>1.34862532432686</v>
       </c>
       <c r="D13">
-        <v>6128.8217791453399</v>
+        <v>6.1288217791453397</v>
       </c>
       <c r="E13">
-        <v>2014.4463022791099</v>
+        <v>2.0144463022791101</v>
       </c>
       <c r="F13">
-        <v>1290.3220549970899</v>
+        <v>1.29032205499709</v>
       </c>
       <c r="G13">
-        <v>424.10835003927002</v>
+        <v>0.42410835003927</v>
       </c>
       <c r="H13">
-        <v>2656.6180360721401</v>
+        <v>2.6566180360721399</v>
       </c>
       <c r="I13">
-        <v>873.18812198840101</v>
+        <v>0.87318812198840101</v>
       </c>
       <c r="J13">
-        <v>1182.12633266533</v>
+        <v>1.18212633266533</v>
       </c>
       <c r="K13">
-        <v>388.54613586047498</v>
+        <v>0.38854613586047498</v>
       </c>
       <c r="L13">
-        <v>4252.3219839679296</v>
+        <v>4.2523219839679296</v>
       </c>
       <c r="M13">
-        <v>1397.6706462329</v>
+        <v>1.3976706462329</v>
       </c>
       <c r="N13">
-        <v>5985.05581563126</v>
+        <v>5.9850558156312603</v>
       </c>
       <c r="O13">
-        <v>1967.1927152063099</v>
+        <v>1.96719271520631</v>
       </c>
       <c r="P13">
-        <v>3519.3385437541701</v>
+        <v>3.51933854375417</v>
       </c>
       <c r="Q13">
-        <v>1156.75064007532</v>
+        <v>1.15675064007532</v>
       </c>
       <c r="R13">
-        <v>656.50161290322501</v>
+        <v>0.65650161290322595</v>
       </c>
       <c r="S13">
-        <v>215.78164518557699</v>
+        <v>0.21578164518557699</v>
       </c>
       <c r="T13">
-        <v>2426.70679759519</v>
+        <v>2.4267067975951901</v>
       </c>
       <c r="U13">
-        <v>797.61995229903903</v>
+        <v>0.79761995229903904</v>
       </c>
       <c r="V13">
-        <v>1603.13709677419</v>
+        <v>1.60313709677419</v>
       </c>
       <c r="W13">
-        <v>526.92568213226605</v>
+        <v>0.52692568213226598</v>
       </c>
       <c r="X13">
-        <v>1828.3840725806399</v>
+        <v>1.82838407258064</v>
       </c>
       <c r="Y13">
-        <v>600.96078281945404</v>
+        <v>0.60096078281945398</v>
       </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
@@ -1998,76 +1998,76 @@
         <v>0.114583333333333</v>
       </c>
       <c r="B14">
-        <v>4072.8011380179701</v>
+        <v>4.0728011380179696</v>
       </c>
       <c r="C14">
-        <v>1338.6649976208901</v>
+        <v>1.33866499762089</v>
       </c>
       <c r="D14">
-        <v>6081.3540699343503</v>
+        <v>6.08135406993435</v>
       </c>
       <c r="E14">
-        <v>1998.84442075221</v>
+        <v>1.99884442075221</v>
       </c>
       <c r="F14">
-        <v>1282.94346855</v>
+        <v>1.2829434685500001</v>
       </c>
       <c r="G14">
-        <v>421.68312595542398</v>
+        <v>0.42168312595542401</v>
       </c>
       <c r="H14">
-        <v>2636.3899799599199</v>
+        <v>2.6363899799599202</v>
       </c>
       <c r="I14">
-        <v>866.53948146564699</v>
+        <v>0.86653948146564697</v>
       </c>
       <c r="J14">
-        <v>1173.1253707414801</v>
+        <v>1.1731253707414799</v>
       </c>
       <c r="K14">
-        <v>385.58766274478597</v>
+        <v>0.38558766274478601</v>
       </c>
       <c r="L14">
-        <v>4219.9438977955897</v>
+        <v>4.2199438977955896</v>
       </c>
       <c r="M14">
-        <v>1387.02848395194</v>
+        <v>1.38702848395194</v>
       </c>
       <c r="N14">
-        <v>5939.4843246493001</v>
+        <v>5.9394843246492997</v>
       </c>
       <c r="O14">
-        <v>1952.2140904712301</v>
+        <v>1.95221409047123</v>
       </c>
       <c r="P14">
-        <v>3492.5415497661902</v>
+        <v>3.49254154976619</v>
       </c>
       <c r="Q14">
-        <v>1147.9428940849</v>
+        <v>1.1479428940848999</v>
       </c>
       <c r="R14">
-        <v>653.07638709677406</v>
+        <v>0.65307638709677396</v>
       </c>
       <c r="S14">
-        <v>214.65582790634801</v>
+        <v>0.21465582790634799</v>
       </c>
       <c r="T14">
-        <v>2408.22933466933</v>
+        <v>2.40822933466933</v>
       </c>
       <c r="U14">
-        <v>791.54670393128004</v>
+        <v>0.79154670393128002</v>
       </c>
       <c r="V14">
-        <v>1594.7729032258001</v>
+        <v>1.5947729032258</v>
       </c>
       <c r="W14">
-        <v>524.17650466027101</v>
+        <v>0.52417650466027099</v>
       </c>
       <c r="X14">
-        <v>1818.8446774193501</v>
+        <v>1.8188446774193501</v>
       </c>
       <c r="Y14">
-        <v>597.82533525691804</v>
+        <v>0.59782533525691794</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
@@ -2122,76 +2122,76 @@
         <v>0.125</v>
       </c>
       <c r="B15">
-        <v>4043.17829866183</v>
+        <v>4.0431782986618297</v>
       </c>
       <c r="C15">
-        <v>1328.9284411742599</v>
+        <v>1.3289284411742599</v>
       </c>
       <c r="D15">
-        <v>6049.8049964091297</v>
+        <v>6.0498049964091303</v>
       </c>
       <c r="E15">
-        <v>1988.4747417513499</v>
+        <v>1.98847474175135</v>
       </c>
       <c r="F15">
-        <v>1277.3398417803301</v>
+        <v>1.2773398417803301</v>
       </c>
       <c r="G15">
-        <v>419.841302904879</v>
+        <v>0.41984130290487898</v>
       </c>
       <c r="H15">
-        <v>2616.1619238476901</v>
+        <v>2.6161619238476899</v>
       </c>
       <c r="I15">
-        <v>859.89084094289205</v>
+        <v>0.85989084094289203</v>
       </c>
       <c r="J15">
-        <v>1164.12440881763</v>
+        <v>1.1641244088176299</v>
       </c>
       <c r="K15">
-        <v>382.62918962909703</v>
+        <v>0.38262918962909698</v>
       </c>
       <c r="L15">
-        <v>4187.5658116232398</v>
+        <v>4.1875658116232399</v>
       </c>
       <c r="M15">
-        <v>1376.3863216709799</v>
+        <v>1.37638632167098</v>
       </c>
       <c r="N15">
-        <v>5893.9128336673302</v>
+        <v>5.8939128336673301</v>
       </c>
       <c r="O15">
-        <v>1937.23546573616</v>
+        <v>1.9372354657361599</v>
       </c>
       <c r="P15">
-        <v>3465.7445557782198</v>
+        <v>3.4657445557782198</v>
       </c>
       <c r="Q15">
-        <v>1139.13514809448</v>
+        <v>1.13913514809448</v>
       </c>
       <c r="R15">
-        <v>650.79290322580596</v>
+        <v>0.65079290322580596</v>
       </c>
       <c r="S15">
-        <v>213.905283053528</v>
+        <v>0.21390528305352799</v>
       </c>
       <c r="T15">
-        <v>2389.75187174348</v>
+        <v>2.38975187174348</v>
       </c>
       <c r="U15">
-        <v>785.47345556352104</v>
+        <v>0.78547345556352099</v>
       </c>
       <c r="V15">
-        <v>1589.19677419354</v>
+        <v>1.58919677419354</v>
       </c>
       <c r="W15">
-        <v>522.34371967894197</v>
+        <v>0.522343719678942</v>
       </c>
       <c r="X15">
-        <v>1812.48508064516</v>
+        <v>1.81248508064516</v>
       </c>
       <c r="Y15">
-        <v>595.73503688189396</v>
+        <v>0.595735036881894</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
@@ -2246,76 +2246,76 @@
         <v>0.13541666666666699</v>
       </c>
       <c r="B16">
-        <v>4022.2950616717299</v>
+        <v>4.0222950616717297</v>
       </c>
       <c r="C16">
-        <v>1322.0644531109299</v>
+        <v>1.32206445311093</v>
       </c>
       <c r="D16">
-        <v>6046.6607385759098</v>
+        <v>6.0466607385759099</v>
       </c>
       <c r="E16">
-        <v>1987.4412741789799</v>
+        <v>1.98744127417898</v>
       </c>
       <c r="F16">
-        <v>1270.64582447152</v>
+        <v>1.27064582447152</v>
       </c>
       <c r="G16">
-        <v>417.64108581568098</v>
+        <v>0.41764108581568099</v>
       </c>
       <c r="H16">
-        <v>2602.6765531062101</v>
+        <v>2.6026765531062099</v>
       </c>
       <c r="I16">
-        <v>855.45841392772297</v>
+        <v>0.85545841392772304</v>
       </c>
       <c r="J16">
-        <v>1158.1237675350701</v>
+        <v>1.15812376753507</v>
       </c>
       <c r="K16">
-        <v>380.65687421863799</v>
+        <v>0.38065687421863798</v>
       </c>
       <c r="L16">
-        <v>4165.9804208416799</v>
+        <v>4.16598042084168</v>
       </c>
       <c r="M16">
-        <v>1369.2915468170099</v>
+        <v>1.3692915468170099</v>
       </c>
       <c r="N16">
-        <v>5863.53183967935</v>
+        <v>5.8635318396793501</v>
       </c>
       <c r="O16">
-        <v>1927.2497159127799</v>
+        <v>1.9272497159127799</v>
       </c>
       <c r="P16">
-        <v>3447.8798931195702</v>
+        <v>3.4478798931195702</v>
       </c>
       <c r="Q16">
-        <v>1133.2633174342</v>
+        <v>1.1332633174341999</v>
       </c>
       <c r="R16">
-        <v>647.367677419355</v>
+        <v>0.64736767741935497</v>
       </c>
       <c r="S16">
-        <v>212.77946577429901</v>
+        <v>0.21277946577429899</v>
       </c>
       <c r="T16">
-        <v>2377.4335631262502</v>
+        <v>2.37743356312625</v>
       </c>
       <c r="U16">
-        <v>781.42462331834804</v>
+        <v>0.78142462331834806</v>
       </c>
       <c r="V16">
-        <v>1580.8325806451601</v>
+        <v>1.58083258064516</v>
       </c>
       <c r="W16">
-        <v>519.59454220694704</v>
+        <v>0.51959454220694701</v>
       </c>
       <c r="X16">
-        <v>1802.94568548387</v>
+        <v>1.8029456854838699</v>
       </c>
       <c r="Y16">
-        <v>592.59958931935796</v>
+        <v>0.59259958931935797</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
@@ -2370,76 +2370,76 @@
         <v>0.14583333333333301</v>
       </c>
       <c r="B17">
-        <v>3991.9914158639799</v>
+        <v>3.9919914158639802</v>
       </c>
       <c r="C17">
-        <v>1312.10412640495</v>
+        <v>1.31210412640495</v>
       </c>
       <c r="D17">
-        <v>6050.9369871269901</v>
+        <v>6.05093698712699</v>
       </c>
       <c r="E17">
-        <v>1988.8468091075199</v>
+        <v>1.98884680910752</v>
       </c>
       <c r="F17">
-        <v>1263.2672380244301</v>
+        <v>1.2632672380244301</v>
       </c>
       <c r="G17">
-        <v>415.21586173183499</v>
+        <v>0.415215861731835</v>
       </c>
       <c r="H17">
-        <v>2582.4484969939799</v>
+        <v>2.58244849699398</v>
       </c>
       <c r="I17">
-        <v>848.80977340496895</v>
+        <v>0.84880977340496899</v>
       </c>
       <c r="J17">
-        <v>1149.12280561122</v>
+        <v>1.1491228056112199</v>
       </c>
       <c r="K17">
-        <v>377.69840110294899</v>
+        <v>0.377698401102949</v>
       </c>
       <c r="L17">
-        <v>4133.60233466933</v>
+        <v>4.1336023346693302</v>
       </c>
       <c r="M17">
-        <v>1358.6493845360501</v>
+        <v>1.3586493845360501</v>
       </c>
       <c r="N17">
-        <v>5817.9603486973901</v>
+        <v>5.8179603486973903</v>
       </c>
       <c r="O17">
-        <v>1912.2710911777001</v>
+        <v>1.9122710911777001</v>
       </c>
       <c r="P17">
-        <v>3421.0828991315898</v>
+        <v>3.4210828991315898</v>
       </c>
       <c r="Q17">
-        <v>1124.4555714437699</v>
+        <v>1.1244555714437701</v>
       </c>
       <c r="R17">
-        <v>643.94245161290303</v>
+        <v>0.64394245161290298</v>
       </c>
       <c r="S17">
-        <v>211.65364849507</v>
+        <v>0.21165364849507001</v>
       </c>
       <c r="T17">
-        <v>2358.9561002004002</v>
+        <v>2.3589561002004</v>
       </c>
       <c r="U17">
-        <v>775.35137495058905</v>
+        <v>0.77535137495058903</v>
       </c>
       <c r="V17">
-        <v>1572.4683870967699</v>
+        <v>1.5724683870967699</v>
       </c>
       <c r="W17">
-        <v>516.84536473495302</v>
+        <v>0.51684536473495302</v>
       </c>
       <c r="X17">
-        <v>1793.4062903225799</v>
+        <v>1.79340629032258</v>
       </c>
       <c r="Y17">
-        <v>589.46414175682105</v>
+        <v>0.58946414175682105</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -2494,76 +2494,76 @@
         <v>0.15625</v>
       </c>
       <c r="B18">
-        <v>3989.9489965091402</v>
+        <v>3.9899489965091401</v>
       </c>
       <c r="C18">
-        <v>1311.43281562691</v>
+        <v>1.3114328156269099</v>
       </c>
       <c r="D18">
-        <v>6099.7429952089597</v>
+        <v>6.0997429952089597</v>
       </c>
       <c r="E18">
-        <v>2004.8885682012899</v>
+        <v>2.0048885682012898</v>
       </c>
       <c r="F18">
-        <v>1257.9423589921701</v>
+        <v>1.2579423589921701</v>
       </c>
       <c r="G18">
-        <v>413.465658631932</v>
+        <v>0.41346565863193202</v>
       </c>
       <c r="H18">
-        <v>2582.4484969939799</v>
+        <v>2.58244849699398</v>
       </c>
       <c r="I18">
-        <v>848.80977340496895</v>
+        <v>0.84880977340496899</v>
       </c>
       <c r="J18">
-        <v>1149.12280561122</v>
+        <v>1.1491228056112199</v>
       </c>
       <c r="K18">
-        <v>377.69840110294899</v>
+        <v>0.377698401102949</v>
       </c>
       <c r="L18">
-        <v>4133.60233466933</v>
+        <v>4.1336023346693302</v>
       </c>
       <c r="M18">
-        <v>1358.6493845360501</v>
+        <v>1.3586493845360501</v>
       </c>
       <c r="N18">
-        <v>5817.9603486973901</v>
+        <v>5.8179603486973903</v>
       </c>
       <c r="O18">
-        <v>1912.2710911777001</v>
+        <v>1.9122710911777001</v>
       </c>
       <c r="P18">
-        <v>3421.0828991315898</v>
+        <v>3.4210828991315898</v>
       </c>
       <c r="Q18">
-        <v>1124.4555714437699</v>
+        <v>1.1244555714437701</v>
       </c>
       <c r="R18">
-        <v>640.51722580645105</v>
+        <v>0.64051722580645098</v>
       </c>
       <c r="S18">
-        <v>210.52783121584099</v>
+        <v>0.21052783121584101</v>
       </c>
       <c r="T18">
-        <v>2358.9561002004002</v>
+        <v>2.3589561002004</v>
       </c>
       <c r="U18">
-        <v>775.35137495058905</v>
+        <v>0.77535137495058903</v>
       </c>
       <c r="V18">
-        <v>1564.10419354838</v>
+        <v>1.5641041935483799</v>
       </c>
       <c r="W18">
-        <v>514.09618726295901</v>
+        <v>0.51409618726295903</v>
       </c>
       <c r="X18">
-        <v>1783.8668951612899</v>
+        <v>1.7838668951612899</v>
       </c>
       <c r="Y18">
-        <v>586.32869419428505</v>
+        <v>0.58632869419428502</v>
       </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
@@ -2618,76 +2618,76 @@
         <v>0.16666666666666699</v>
       </c>
       <c r="B19">
-        <v>3996.64617952033</v>
+        <v>3.9966461795203299</v>
       </c>
       <c r="C19">
-        <v>1313.6340732321601</v>
+        <v>1.3136340732321601</v>
       </c>
       <c r="D19">
-        <v>6169.7373803434002</v>
+        <v>6.1697373803433999</v>
       </c>
       <c r="E19">
-        <v>2027.8946100467499</v>
+        <v>2.0278946100467499</v>
       </c>
       <c r="F19">
-        <v>1251.5270894207699</v>
+        <v>1.25152708942077</v>
       </c>
       <c r="G19">
-        <v>411.357061493375</v>
+        <v>0.41135706149337498</v>
       </c>
       <c r="H19">
-        <v>2589.1911823647201</v>
+        <v>2.5891911823647198</v>
       </c>
       <c r="I19">
-        <v>851.02598691255298</v>
+        <v>0.85102598691255305</v>
       </c>
       <c r="J19">
-        <v>1152.1231262525</v>
+        <v>1.1521231262525</v>
       </c>
       <c r="K19">
-        <v>378.684558808178</v>
+        <v>0.37868455880817897</v>
       </c>
       <c r="L19">
-        <v>4144.39503006012</v>
+        <v>4.14439503006012</v>
       </c>
       <c r="M19">
-        <v>1362.19677196303</v>
+        <v>1.3621967719630299</v>
       </c>
       <c r="N19">
-        <v>5833.1508456913798</v>
+        <v>5.8331508456913799</v>
       </c>
       <c r="O19">
-        <v>1917.2639660893999</v>
+        <v>1.9172639660894</v>
       </c>
       <c r="P19">
-        <v>3430.0152304609201</v>
+        <v>3.4300152304609202</v>
       </c>
       <c r="Q19">
-        <v>1127.39148677392</v>
+        <v>1.1273914867739101</v>
       </c>
       <c r="R19">
-        <v>635.95025806451599</v>
+        <v>0.63595025806451599</v>
       </c>
       <c r="S19">
-        <v>209.02674151020199</v>
+        <v>0.20902674151020201</v>
       </c>
       <c r="T19">
-        <v>2365.1152545090099</v>
+        <v>2.3651152545090102</v>
       </c>
       <c r="U19">
-        <v>777.37579107317504</v>
+        <v>0.777375791073175</v>
       </c>
       <c r="V19">
-        <v>1552.9519354838701</v>
+        <v>1.5529519354838699</v>
       </c>
       <c r="W19">
-        <v>510.43061730029899</v>
+        <v>0.51043061730029904</v>
       </c>
       <c r="X19">
-        <v>1771.1477016128999</v>
+        <v>1.7711477016129</v>
       </c>
       <c r="Y19">
-        <v>582.14809744423701</v>
+        <v>0.58214809744423701</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
@@ -2742,76 +2742,76 @@
         <v>0.17708333333333301</v>
       </c>
       <c r="B20">
-        <v>4032.9662018876402</v>
+        <v>4.03296620188764</v>
       </c>
       <c r="C20">
-        <v>1325.57188728403</v>
+        <v>1.3255718872840301</v>
       </c>
       <c r="D20">
-        <v>6277.6259628785601</v>
+        <v>6.2776259628785596</v>
       </c>
       <c r="E20">
-        <v>2063.3558722563398</v>
+        <v>2.0633558722563401</v>
       </c>
       <c r="F20">
-        <v>1250.71544661904</v>
+        <v>1.25071544661904</v>
       </c>
       <c r="G20">
-        <v>411.09028740536201</v>
+        <v>0.41109028740536202</v>
       </c>
       <c r="H20">
-        <v>2616.1619238476901</v>
+        <v>2.6161619238476899</v>
       </c>
       <c r="I20">
-        <v>859.89084094289205</v>
+        <v>0.85989084094289203</v>
       </c>
       <c r="J20">
-        <v>1164.12440881763</v>
+        <v>1.1641244088176299</v>
       </c>
       <c r="K20">
-        <v>382.62918962909703</v>
+        <v>0.38262918962909698</v>
       </c>
       <c r="L20">
-        <v>4187.5658116232398</v>
+        <v>4.1875658116232399</v>
       </c>
       <c r="M20">
-        <v>1376.3863216709799</v>
+        <v>1.37638632167098</v>
       </c>
       <c r="N20">
-        <v>5893.9128336673302</v>
+        <v>5.8939128336673301</v>
       </c>
       <c r="O20">
-        <v>1937.23546573616</v>
+        <v>1.9372354657361599</v>
       </c>
       <c r="P20">
-        <v>3465.7445557782198</v>
+        <v>3.4657445557782198</v>
       </c>
       <c r="Q20">
-        <v>1139.13514809448</v>
+        <v>1.13913514809448</v>
       </c>
       <c r="R20">
-        <v>633.66677419354801</v>
+        <v>0.633666774193548</v>
       </c>
       <c r="S20">
-        <v>208.276196657383</v>
+        <v>0.20827619665738301</v>
       </c>
       <c r="T20">
-        <v>2389.75187174348</v>
+        <v>2.38975187174348</v>
       </c>
       <c r="U20">
-        <v>785.47345556352104</v>
+        <v>0.78547345556352099</v>
       </c>
       <c r="V20">
-        <v>1547.3758064516101</v>
+        <v>1.5473758064516101</v>
       </c>
       <c r="W20">
-        <v>508.59783231897001</v>
+        <v>0.50859783231897004</v>
       </c>
       <c r="X20">
-        <v>1764.7881048387001</v>
+        <v>1.7647881048387</v>
       </c>
       <c r="Y20">
-        <v>580.05779906921305</v>
+        <v>0.58005779906921295</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
@@ -2866,76 +2866,76 @@
         <v>0.1875</v>
       </c>
       <c r="B21">
-        <v>4080.7490524274299</v>
+        <v>4.0807490524274304</v>
       </c>
       <c r="C21">
-        <v>1341.2773507566001</v>
+        <v>1.3412773507566</v>
       </c>
       <c r="D21">
-        <v>6396.07930963124</v>
+        <v>6.3960793096312401</v>
       </c>
       <c r="E21">
-        <v>2102.2896045391799</v>
+        <v>2.1022896045391799</v>
       </c>
       <c r="F21">
-        <v>1255.9132519878401</v>
+        <v>1.25591325198784</v>
       </c>
       <c r="G21">
-        <v>412.79872341190099</v>
+        <v>0.41279872341190099</v>
       </c>
       <c r="H21">
-        <v>2649.8753507013998</v>
+        <v>2.6498753507014001</v>
       </c>
       <c r="I21">
-        <v>870.97190848081596</v>
+        <v>0.87097190848081596</v>
       </c>
       <c r="J21">
-        <v>1179.1260120240399</v>
+        <v>1.1791260120240401</v>
       </c>
       <c r="K21">
-        <v>387.55997815524501</v>
+        <v>0.38755997815524501</v>
       </c>
       <c r="L21">
-        <v>4241.5292885771496</v>
+        <v>4.2415292885771496</v>
       </c>
       <c r="M21">
-        <v>1394.1232588059199</v>
+        <v>1.39412325880592</v>
       </c>
       <c r="N21">
-        <v>5969.8653186372703</v>
+        <v>5.9698653186372699</v>
       </c>
       <c r="O21">
-        <v>1962.1998402946199</v>
+        <v>1.9621998402946199</v>
       </c>
       <c r="P21">
-        <v>3510.4062124248499</v>
+        <v>3.5104062124248498</v>
       </c>
       <c r="Q21">
-        <v>1153.81472474518</v>
+        <v>1.15381472474518</v>
       </c>
       <c r="R21">
-        <v>634.808516129032</v>
+        <v>0.634808516129032</v>
       </c>
       <c r="S21">
-        <v>208.65146908379199</v>
+        <v>0.20865146908379201</v>
       </c>
       <c r="T21">
-        <v>2420.5476432865698</v>
+        <v>2.4205476432865698</v>
       </c>
       <c r="U21">
-        <v>795.59553617645304</v>
+        <v>0.79559553617645296</v>
       </c>
       <c r="V21">
-        <v>1550.16387096774</v>
+        <v>1.5501638709677401</v>
       </c>
       <c r="W21">
-        <v>509.51422480963402</v>
+        <v>0.50951422480963404</v>
       </c>
       <c r="X21">
-        <v>1767.9679032258</v>
+        <v>1.7679679032258</v>
       </c>
       <c r="Y21">
-        <v>581.10294825672497</v>
+        <v>0.58110294825672504</v>
       </c>
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
@@ -2990,76 +2990,76 @@
         <v>0.19791666666666699</v>
       </c>
       <c r="B22">
-        <v>4150.0959464089401</v>
+        <v>4.15009594640894</v>
       </c>
       <c r="C22">
-        <v>1364.0705725518501</v>
+        <v>1.36407057255185</v>
       </c>
       <c r="D22">
-        <v>6524.6029146019901</v>
+        <v>6.5246029146019904</v>
       </c>
       <c r="E22">
-        <v>2144.5332706333502</v>
+        <v>2.14453327063335</v>
       </c>
       <c r="F22">
-        <v>1269.58003434287</v>
+        <v>1.26958003434287</v>
       </c>
       <c r="G22">
-        <v>417.29077754093902</v>
+        <v>0.41729077754093902</v>
       </c>
       <c r="H22">
-        <v>2697.07414829659</v>
+        <v>2.6970741482965899</v>
       </c>
       <c r="I22">
-        <v>886.48540303390996</v>
+        <v>0.88648540303390999</v>
       </c>
       <c r="J22">
-        <v>1200.12825651302</v>
+        <v>1.20012825651302</v>
       </c>
       <c r="K22">
-        <v>394.46308209185298</v>
+        <v>0.39446308209185299</v>
       </c>
       <c r="L22">
-        <v>4317.0781563126202</v>
+        <v>4.3170781563126202</v>
       </c>
       <c r="M22">
-        <v>1418.9549707948299</v>
+        <v>1.4189549707948299</v>
       </c>
       <c r="N22">
-        <v>6076.1987975951897</v>
+        <v>6.0761987975951897</v>
       </c>
       <c r="O22">
-        <v>1997.1499646764501</v>
+        <v>1.9971499646764499</v>
       </c>
       <c r="P22">
-        <v>3572.93253173012</v>
+        <v>3.5729325317301202</v>
       </c>
       <c r="Q22">
-        <v>1174.36613205616</v>
+        <v>1.17436613205616</v>
       </c>
       <c r="R22">
-        <v>640.51722580645105</v>
+        <v>0.64051722580645098</v>
       </c>
       <c r="S22">
-        <v>210.52783121584099</v>
+        <v>0.21052783121584101</v>
       </c>
       <c r="T22">
-        <v>2463.6617234468899</v>
+        <v>2.4636617234468901</v>
       </c>
       <c r="U22">
-        <v>809.76644903455804</v>
+        <v>0.80976644903455797</v>
       </c>
       <c r="V22">
-        <v>1564.10419354838</v>
+        <v>1.5641041935483799</v>
       </c>
       <c r="W22">
-        <v>514.09618726295901</v>
+        <v>0.51409618726295903</v>
       </c>
       <c r="X22">
-        <v>1783.8668951612899</v>
+        <v>1.7838668951612899</v>
       </c>
       <c r="Y22">
-        <v>586.32869419428505</v>
+        <v>0.58632869419428502</v>
       </c>
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
@@ -3114,76 +3114,76 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="B23">
-        <v>4242.3684967354002</v>
+        <v>4.2423684967354003</v>
       </c>
       <c r="C23">
-        <v>1394.39909318847</v>
+        <v>1.39439909318847</v>
       </c>
       <c r="D23">
-        <v>6663.3419969181596</v>
+        <v>6.6633419969181604</v>
       </c>
       <c r="E23">
-        <v>2190.1346017577798</v>
+        <v>2.1901346017577801</v>
       </c>
       <c r="F23">
-        <v>1295.26571303898</v>
+        <v>1.29526571303898</v>
       </c>
       <c r="G23">
-        <v>425.73325185907902</v>
+        <v>0.42573325185907901</v>
       </c>
       <c r="H23">
-        <v>2757.7583166332602</v>
+        <v>2.75775831663326</v>
       </c>
       <c r="I23">
-        <v>906.43132460217305</v>
+        <v>0.90643132460217302</v>
       </c>
       <c r="J23">
-        <v>1227.1311422845599</v>
+        <v>1.2271311422845601</v>
       </c>
       <c r="K23">
-        <v>403.33850143891902</v>
+        <v>0.40333850143891897</v>
       </c>
       <c r="L23">
-        <v>4414.2124148296498</v>
+        <v>4.4142124148296498</v>
       </c>
       <c r="M23">
-        <v>1450.8814576377099</v>
+        <v>1.45088145763771</v>
       </c>
       <c r="N23">
-        <v>6212.9132705410802</v>
+        <v>6.2129132705410797</v>
       </c>
       <c r="O23">
-        <v>2042.08583888167</v>
+        <v>2.0420858388816798</v>
       </c>
       <c r="P23">
-        <v>3653.3235136940498</v>
+        <v>3.6533235136940498</v>
       </c>
       <c r="Q23">
-        <v>1200.7893700274301</v>
+        <v>1.2007893700274299</v>
       </c>
       <c r="R23">
-        <v>653.07638709677406</v>
+        <v>0.65307638709677396</v>
       </c>
       <c r="S23">
-        <v>214.65582790634801</v>
+        <v>0.21465582790634799</v>
       </c>
       <c r="T23">
-        <v>2519.0941122244399</v>
+        <v>2.5190941122244399</v>
       </c>
       <c r="U23">
-        <v>827.98619413783501</v>
+        <v>0.82798619413783503</v>
       </c>
       <c r="V23">
-        <v>1594.7729032258001</v>
+        <v>1.5947729032258</v>
       </c>
       <c r="W23">
-        <v>524.17650466027101</v>
+        <v>0.52417650466027099</v>
       </c>
       <c r="X23">
-        <v>1818.8446774193501</v>
+        <v>1.8188446774193501</v>
       </c>
       <c r="Y23">
-        <v>597.82533525691804</v>
+        <v>0.59782533525691794</v>
       </c>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
@@ -3238,76 +3238,76 @@
         <v>0.21875</v>
       </c>
       <c r="B24">
-        <v>4464.5952326588604</v>
+        <v>4.4645952326588603</v>
       </c>
       <c r="C24">
-        <v>1467.4414890322901</v>
+        <v>1.46744148903229</v>
       </c>
       <c r="D24">
-        <v>6931.1900415311702</v>
+        <v>6.9311900415311696</v>
       </c>
       <c r="E24">
-        <v>2278.1719966253199</v>
+        <v>2.27817199662532</v>
       </c>
       <c r="F24">
-        <v>1349.37534698429</v>
+        <v>1.34937534698429</v>
       </c>
       <c r="G24">
-        <v>443.51822847394902</v>
+        <v>0.44351822847394901</v>
       </c>
       <c r="H24">
-        <v>2906.09739478957</v>
+        <v>2.9060973947895699</v>
       </c>
       <c r="I24">
-        <v>955.18802176903796</v>
+        <v>0.95518802176903805</v>
       </c>
       <c r="J24">
-        <v>1293.1381963927799</v>
+        <v>1.2931381963927799</v>
       </c>
       <c r="K24">
-        <v>425.03397095397099</v>
+        <v>0.425033970953971</v>
       </c>
       <c r="L24">
-        <v>4651.6517134268497</v>
+        <v>4.6516517134268502</v>
       </c>
       <c r="M24">
-        <v>1528.92398103143</v>
+        <v>1.5289239810314299</v>
       </c>
       <c r="N24">
-        <v>6547.1042044088099</v>
+        <v>6.5471042044088099</v>
       </c>
       <c r="O24">
-        <v>2151.9290869388801</v>
+        <v>2.1519290869388801</v>
       </c>
       <c r="P24">
-        <v>3849.83480293921</v>
+        <v>3.8498348029392102</v>
       </c>
       <c r="Q24">
-        <v>1265.37950729051</v>
+        <v>1.2653795072905101</v>
       </c>
       <c r="R24">
-        <v>678.19470967741904</v>
+        <v>0.67819470967741902</v>
       </c>
       <c r="S24">
-        <v>222.91182128736099</v>
+        <v>0.22291182128736101</v>
       </c>
       <c r="T24">
-        <v>2654.5955070140199</v>
+        <v>2.6545955070140201</v>
       </c>
       <c r="U24">
-        <v>872.523348834736</v>
+        <v>0.87252334883473603</v>
       </c>
       <c r="V24">
-        <v>1656.1103225806401</v>
+        <v>1.6561103225806399</v>
       </c>
       <c r="W24">
-        <v>544.33713945489706</v>
+        <v>0.54433713945489703</v>
       </c>
       <c r="X24">
-        <v>1888.80024193548</v>
+        <v>1.8888002419354799</v>
       </c>
       <c r="Y24">
-        <v>620.81861738218402</v>
+        <v>0.62081861738218402</v>
       </c>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
@@ -3362,76 +3362,76 @@
         <v>0.22916666666666699</v>
       </c>
       <c r="B25">
-        <v>4920.4006511733096</v>
+        <v>4.9204006511733098</v>
       </c>
       <c r="C25">
-        <v>1617.25748515239</v>
+        <v>1.61725748515239</v>
       </c>
       <c r="D25">
-        <v>7451.3190223519096</v>
+        <v>7.4513190223519103</v>
       </c>
       <c r="E25">
-        <v>2449.1301252639801</v>
+        <v>2.4491301252639799</v>
       </c>
       <c r="F25">
-        <v>1439.4391966998501</v>
+        <v>1.4394391966998501</v>
       </c>
       <c r="G25">
-        <v>473.12078432667198</v>
+        <v>0.47312078432667198</v>
       </c>
       <c r="H25">
-        <v>3216.2609218436801</v>
+        <v>3.2162609218436802</v>
       </c>
       <c r="I25">
-        <v>1057.1338431179299</v>
+        <v>1.05713384311793</v>
       </c>
       <c r="J25">
-        <v>1431.1529458917801</v>
+        <v>1.43115294589178</v>
       </c>
       <c r="K25">
-        <v>470.39722539453402</v>
+        <v>0.47039722539453399</v>
       </c>
       <c r="L25">
-        <v>5148.1157014028004</v>
+        <v>5.1481157014027996</v>
       </c>
       <c r="M25">
-        <v>1692.1038026728299</v>
+        <v>1.6921038026728299</v>
       </c>
       <c r="N25">
-        <v>7245.8670661322603</v>
+        <v>7.2458670661322602</v>
       </c>
       <c r="O25">
-        <v>2381.6013328766699</v>
+        <v>2.3816013328766701</v>
       </c>
       <c r="P25">
-        <v>4260.7220440881702</v>
+        <v>4.2607220440881699</v>
       </c>
       <c r="Q25">
-        <v>1400.43161247697</v>
+        <v>1.40043161247697</v>
       </c>
       <c r="R25">
-        <v>715.87219354838703</v>
+        <v>0.71587219354838705</v>
       </c>
       <c r="S25">
-        <v>235.295811358881</v>
+        <v>0.235295811358881</v>
       </c>
       <c r="T25">
-        <v>2937.9166052104201</v>
+        <v>2.93791660521042</v>
       </c>
       <c r="U25">
-        <v>965.64649047370995</v>
+        <v>0.96564649047370998</v>
       </c>
       <c r="V25">
-        <v>1748.1164516128999</v>
+        <v>1.7481164516129</v>
       </c>
       <c r="W25">
-        <v>574.57809164683601</v>
+        <v>0.57457809164683604</v>
       </c>
       <c r="X25">
-        <v>1993.7335887096699</v>
+        <v>1.9937335887096701</v>
       </c>
       <c r="Y25">
-        <v>655.30854057008298</v>
+        <v>0.65530854057008303</v>
       </c>
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
@@ -3486,76 +3486,76 @@
         <v>0.23958333333333301</v>
       </c>
       <c r="B26">
-        <v>5718.1748944340297</v>
+        <v>5.7181748944340303</v>
       </c>
       <c r="C26">
-        <v>1879.47319843328</v>
+        <v>1.87947319843328</v>
       </c>
       <c r="D26">
-        <v>8348.9675482072998</v>
+        <v>8.3489675482073</v>
       </c>
       <c r="E26">
-        <v>2744.1729277498798</v>
+        <v>2.7441729277498799</v>
       </c>
       <c r="F26">
-        <v>1585.41224044863</v>
+        <v>1.5854122404486299</v>
       </c>
       <c r="G26">
-        <v>521.09980359147698</v>
+        <v>0.52109980359147701</v>
       </c>
       <c r="H26">
-        <v>3762.4184368737401</v>
+        <v>3.7624184368737401</v>
       </c>
       <c r="I26">
-        <v>1236.6471372323001</v>
+        <v>1.2366471372323</v>
       </c>
       <c r="J26">
-        <v>1674.1789178356701</v>
+        <v>1.6741789178356701</v>
       </c>
       <c r="K26">
-        <v>550.275999518135</v>
+        <v>0.550275999518135</v>
       </c>
       <c r="L26">
-        <v>6022.3240280561104</v>
+        <v>6.0223240280561097</v>
       </c>
       <c r="M26">
-        <v>1979.4421842587799</v>
+        <v>1.9794421842587799</v>
       </c>
       <c r="N26">
-        <v>8476.2973226452905</v>
+        <v>8.4762973226452907</v>
       </c>
       <c r="O26">
-        <v>2786.0242007236602</v>
+        <v>2.7860242007236602</v>
       </c>
       <c r="P26">
-        <v>4984.2408817635196</v>
+        <v>4.9842408817635198</v>
       </c>
       <c r="Q26">
-        <v>1638.24075421835</v>
+        <v>1.6382407542183499</v>
       </c>
       <c r="R26">
-        <v>774.10103225806404</v>
+        <v>0.77410103225806404</v>
       </c>
       <c r="S26">
-        <v>254.434705105776</v>
+        <v>0.25443470510577598</v>
       </c>
       <c r="T26">
-        <v>3436.80810420841</v>
+        <v>3.43680810420841</v>
       </c>
       <c r="U26">
-        <v>1129.6241964031999</v>
+        <v>1.1296241964032001</v>
       </c>
       <c r="V26">
-        <v>1890.30774193548</v>
+        <v>1.8903077419354799</v>
       </c>
       <c r="W26">
-        <v>621.31410867074101</v>
+        <v>0.62131410867074199</v>
       </c>
       <c r="X26">
-        <v>2155.9033064516102</v>
+        <v>2.1559033064516102</v>
       </c>
       <c r="Y26">
-        <v>708.6111491332</v>
+        <v>0.7086111491332</v>
       </c>
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
@@ -3610,76 +3610,76 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>6915.1212217984303</v>
+        <v>6.9151212217984304</v>
       </c>
       <c r="C27">
-        <v>2272.89043099018</v>
+        <v>2.2728904309901798</v>
       </c>
       <c r="D27">
-        <v>9700.0692330261099</v>
+        <v>9.7000692330261096</v>
       </c>
       <c r="E27">
-        <v>3188.25857603021</v>
+        <v>3.18825857603021</v>
       </c>
       <c r="F27">
-        <v>1793.1768527377301</v>
+        <v>1.7931768527377301</v>
       </c>
       <c r="G27">
-        <v>589.38872926955196</v>
+        <v>0.58938872926955199</v>
       </c>
       <c r="H27">
-        <v>4585.0260521042001</v>
+        <v>4.5850260521042001</v>
       </c>
       <c r="I27">
-        <v>1507.02518515764</v>
+        <v>1.5070251851576399</v>
       </c>
       <c r="J27">
-        <v>2040.21803607214</v>
+        <v>2.0402180360721398</v>
       </c>
       <c r="K27">
-        <v>670.58723955615005</v>
+        <v>0.67058723955614996</v>
       </c>
       <c r="L27">
-        <v>7339.0328657314603</v>
+        <v>7.3390328657314603</v>
       </c>
       <c r="M27">
-        <v>2412.22345035121</v>
+        <v>2.4122234503512101</v>
       </c>
       <c r="N27">
-        <v>10329.537955911799</v>
+        <v>10.3295379559118</v>
       </c>
       <c r="O27">
-        <v>3395.15493994998</v>
+        <v>3.3951549399499799</v>
       </c>
       <c r="P27">
-        <v>6073.9853039412101</v>
+        <v>6.0739853039412104</v>
       </c>
       <c r="Q27">
-        <v>1996.4224244954801</v>
+        <v>1.99642242449548</v>
       </c>
       <c r="R27">
-        <v>854.02296774193496</v>
+        <v>0.85402296774193498</v>
       </c>
       <c r="S27">
-        <v>280.70377495445501</v>
+        <v>0.28070377495445498</v>
       </c>
       <c r="T27">
-        <v>4188.2249298597199</v>
+        <v>4.1882249298597198</v>
       </c>
       <c r="U27">
-        <v>1376.60296335874</v>
+        <v>1.37660296335874</v>
       </c>
       <c r="V27">
-        <v>2085.4722580645098</v>
+        <v>2.08547225806451</v>
       </c>
       <c r="W27">
-        <v>685.46158301727803</v>
+        <v>0.685461583017278</v>
       </c>
       <c r="X27">
-        <v>2378.4891935483802</v>
+        <v>2.3784891935483801</v>
       </c>
       <c r="Y27">
-        <v>781.771592259047</v>
+        <v>0.78177159225904702</v>
       </c>
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
@@ -3734,76 +3734,76 @@
         <v>0.26041666666666702</v>
       </c>
       <c r="B28">
-        <v>8378.1031784213501</v>
+        <v>8.37810317842135</v>
       </c>
       <c r="C28">
-        <v>2753.7493462956099</v>
+        <v>2.75374934629561</v>
       </c>
       <c r="D28">
-        <v>11346.264265539499</v>
+        <v>11.346264265539499</v>
       </c>
       <c r="E28">
-        <v>3729.3367172417902</v>
+        <v>3.7293367172417899</v>
       </c>
       <c r="F28">
-        <v>2073.7640126220099</v>
+        <v>2.0737640126220098</v>
       </c>
       <c r="G28">
-        <v>681.61326884079597</v>
+        <v>0.68161326884079598</v>
       </c>
       <c r="H28">
-        <v>5582.9434869739398</v>
+        <v>5.5829434869739396</v>
       </c>
       <c r="I28">
-        <v>1835.02478428019</v>
+        <v>1.8350247842801899</v>
       </c>
       <c r="J28">
-        <v>2484.2654909819598</v>
+        <v>2.4842654909819601</v>
       </c>
       <c r="K28">
-        <v>816.53857993013503</v>
+        <v>0.81653857993013501</v>
       </c>
       <c r="L28">
-        <v>8936.35178356713</v>
+        <v>8.9363517835671296</v>
       </c>
       <c r="M28">
-        <v>2937.2367895452999</v>
+        <v>2.9372367895453002</v>
       </c>
       <c r="N28">
-        <v>12577.731511022001</v>
+        <v>12.577731511022</v>
       </c>
       <c r="O28">
-        <v>4134.1004268802699</v>
+        <v>4.1341004268802699</v>
       </c>
       <c r="P28">
-        <v>7395.9703406813596</v>
+        <v>7.3959703406813597</v>
       </c>
       <c r="Q28">
-        <v>2430.9378933562598</v>
+        <v>2.4309378933562602</v>
       </c>
       <c r="R28">
-        <v>969.33890322580601</v>
+        <v>0.96933890322580596</v>
       </c>
       <c r="S28">
-        <v>318.60629002183401</v>
+        <v>0.31860629002183399</v>
       </c>
       <c r="T28">
-        <v>5099.7797675350703</v>
+        <v>5.09977976753507</v>
       </c>
       <c r="U28">
-        <v>1676.2165495015299</v>
+        <v>1.67621654950153</v>
       </c>
       <c r="V28">
-        <v>2367.0667741935399</v>
+        <v>2.3670667741935398</v>
       </c>
       <c r="W28">
-        <v>778.01722457442395</v>
+        <v>0.77801722457442402</v>
       </c>
       <c r="X28">
-        <v>2699.6488306451602</v>
+        <v>2.69964883064516</v>
       </c>
       <c r="Y28">
-        <v>887.331660197769</v>
+        <v>0.88733166019776899</v>
       </c>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
@@ -3858,76 +3858,76 @@
         <v>0.27083333333333298</v>
       </c>
       <c r="B29">
-        <v>9905.3182219277205</v>
+        <v>9.90531822192772</v>
       </c>
       <c r="C29">
-        <v>3255.7206562862002</v>
+        <v>3.2557206562862002</v>
       </c>
       <c r="D29">
-        <v>13072.465092788099</v>
+        <v>13.0724650927881</v>
       </c>
       <c r="E29">
-        <v>4296.7114915049997</v>
+        <v>4.2967114915050004</v>
       </c>
       <c r="F29">
-        <v>2426.3128764787598</v>
+        <v>2.42631287647876</v>
       </c>
       <c r="G29">
-        <v>797.49047668937601</v>
+        <v>0.797490476689376</v>
       </c>
       <c r="H29">
-        <v>6607.8316633266504</v>
+        <v>6.6078316633266496</v>
       </c>
       <c r="I29">
-        <v>2171.8892374330799</v>
+        <v>2.17188923743308</v>
       </c>
       <c r="J29">
-        <v>2940.3142284569099</v>
+        <v>2.9403142284569102</v>
       </c>
       <c r="K29">
-        <v>966.43455112504</v>
+        <v>0.96643455112503995</v>
       </c>
       <c r="L29">
-        <v>10576.8414829659</v>
+        <v>10.5768414829659</v>
       </c>
       <c r="M29">
-        <v>3476.4396784473302</v>
+        <v>3.4764396784473299</v>
       </c>
       <c r="N29">
-        <v>14886.687054108201</v>
+        <v>14.886687054108201</v>
       </c>
       <c r="O29">
-        <v>4893.0174134573199</v>
+        <v>4.8930174134573203</v>
       </c>
       <c r="P29">
-        <v>8753.6847027388103</v>
+        <v>8.7536847027388092</v>
       </c>
       <c r="Q29">
-        <v>2877.1970235376002</v>
+        <v>2.8771970235376001</v>
       </c>
       <c r="R29">
-        <v>1129.1827741935399</v>
+        <v>1.1291827741935401</v>
       </c>
       <c r="S29">
-        <v>371.14442971919198</v>
+        <v>0.37114442971919198</v>
       </c>
       <c r="T29">
-        <v>6035.9712224448804</v>
+        <v>6.0359712224448803</v>
       </c>
       <c r="U29">
-        <v>1983.9278001346599</v>
+        <v>1.9839278001346601</v>
       </c>
       <c r="V29">
-        <v>2757.39580645161</v>
+        <v>2.7573958064516102</v>
       </c>
       <c r="W29">
-        <v>906.312173267498</v>
+        <v>0.90631217326749802</v>
       </c>
       <c r="X29">
-        <v>3144.8206048387001</v>
+        <v>3.1448206048387002</v>
       </c>
       <c r="Y29">
-        <v>1033.65254644946</v>
+        <v>1.0336525464494599</v>
       </c>
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
@@ -3982,76 +3982,76 @@
         <v>0.28125</v>
       </c>
       <c r="B30">
-        <v>11307.1074445665</v>
+        <v>11.307107444566499</v>
       </c>
       <c r="C30">
-        <v>3716.4664925786101</v>
+        <v>3.7164664925786099</v>
       </c>
       <c r="D30">
-        <v>14662.5087793034</v>
+        <v>14.662508779303399</v>
       </c>
       <c r="E30">
-        <v>4819.3335778025703</v>
+        <v>4.8193335778025697</v>
       </c>
       <c r="F30">
-        <v>2857.7470085331902</v>
+        <v>2.85774700853319</v>
       </c>
       <c r="G30">
-        <v>939.296018327306</v>
+        <v>0.93929601832730603</v>
       </c>
       <c r="H30">
-        <v>7518.09418837675</v>
+        <v>7.5180941883767503</v>
       </c>
       <c r="I30">
-        <v>2471.0780609570202</v>
+        <v>2.4710780609570202</v>
       </c>
       <c r="J30">
-        <v>3345.3575150300599</v>
+        <v>3.3453575150300598</v>
       </c>
       <c r="K30">
-        <v>1099.56584133104</v>
+        <v>1.0995658413310401</v>
       </c>
       <c r="L30">
-        <v>12033.8553607214</v>
+        <v>12.0338553607214</v>
       </c>
       <c r="M30">
-        <v>3955.3369810905901</v>
+        <v>3.9553369810905901</v>
       </c>
       <c r="N30">
-        <v>16937.4041482965</v>
+        <v>16.937404148296501</v>
       </c>
       <c r="O30">
-        <v>5567.0555265356297</v>
+        <v>5.5670555265356203</v>
       </c>
       <c r="P30">
-        <v>9959.5494321977203</v>
+        <v>9.9595494321977203</v>
       </c>
       <c r="Q30">
-        <v>3273.5455931065599</v>
+        <v>3.2735455931065598</v>
       </c>
       <c r="R30">
-        <v>1347.25548387096</v>
+        <v>1.3472554838709601</v>
       </c>
       <c r="S30">
-        <v>442.821463163445</v>
+        <v>0.44282146316344501</v>
       </c>
       <c r="T30">
-        <v>6867.4570541082103</v>
+        <v>6.8674570541082103</v>
       </c>
       <c r="U30">
-        <v>2257.2239766838302</v>
+        <v>2.25722397668383</v>
       </c>
       <c r="V30">
-        <v>3289.91612903225</v>
+        <v>3.2899161290322501</v>
       </c>
       <c r="W30">
-        <v>1081.34313898447</v>
+        <v>1.0813431389844701</v>
       </c>
       <c r="X30">
-        <v>3752.1620967741901</v>
+        <v>3.7521620967741902</v>
       </c>
       <c r="Y30">
-        <v>1233.2760412642699</v>
+        <v>1.23327604126427</v>
       </c>
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
@@ -4106,76 +4106,76 @@
         <v>0.29166666666666702</v>
       </c>
       <c r="B31">
-        <v>12425.3663157928</v>
+        <v>12.4253663157928</v>
       </c>
       <c r="C31">
-        <v>4084.0204090259599</v>
+        <v>4.0840204090259604</v>
       </c>
       <c r="D31">
-        <v>15953.260278449399</v>
+        <v>15.953260278449401</v>
       </c>
       <c r="E31">
-        <v>5243.5830793076502</v>
+        <v>5.2435830793076503</v>
       </c>
       <c r="F31">
-        <v>3361.75361246686</v>
+        <v>3.3617536124668601</v>
       </c>
       <c r="G31">
-        <v>1104.9549779454801</v>
+        <v>1.1049549779454799</v>
       </c>
       <c r="H31">
-        <v>8199.1054108216395</v>
+        <v>8.1991054108216392</v>
       </c>
       <c r="I31">
-        <v>2694.91562522308</v>
+        <v>2.6949156252230799</v>
       </c>
       <c r="J31">
-        <v>3648.3898997995898</v>
+        <v>3.6483898997995898</v>
       </c>
       <c r="K31">
-        <v>1199.16776955923</v>
+        <v>1.19916776955923</v>
       </c>
       <c r="L31">
-        <v>13123.9175951903</v>
+        <v>13.123917595190299</v>
       </c>
       <c r="M31">
-        <v>4313.6231112162804</v>
+        <v>4.3136231112162804</v>
       </c>
       <c r="N31">
-        <v>18471.644344689299</v>
+        <v>18.471644344689299</v>
       </c>
       <c r="O31">
-        <v>6071.3358926164301</v>
+        <v>6.07133589261643</v>
       </c>
       <c r="P31">
-        <v>10861.7148964595</v>
+        <v>10.8617148964595</v>
       </c>
       <c r="Q31">
-        <v>3570.0730414507402</v>
+        <v>3.57007304145074</v>
       </c>
       <c r="R31">
-        <v>1626.98225806451</v>
+        <v>1.6269822580645099</v>
       </c>
       <c r="S31">
-        <v>534.76320763382103</v>
+        <v>0.53476320763382101</v>
       </c>
       <c r="T31">
-        <v>7489.5316392785498</v>
+        <v>7.4895316392785496</v>
       </c>
       <c r="U31">
-        <v>2461.6900050650502</v>
+        <v>2.4616900050650501</v>
       </c>
       <c r="V31">
-        <v>3972.9919354838698</v>
+        <v>3.9729919354838699</v>
       </c>
       <c r="W31">
-        <v>1305.8592991973501</v>
+        <v>1.3058592991973501</v>
       </c>
       <c r="X31">
-        <v>4531.2127016128998</v>
+        <v>4.5312127016129002</v>
       </c>
       <c r="Y31">
-        <v>1489.3375922047301</v>
+        <v>1.4893375922047301</v>
       </c>
       <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
@@ -4230,76 +4230,76 @@
         <v>0.30208333333333298</v>
       </c>
       <c r="B32">
-        <v>13268.723556467699</v>
+        <v>13.2687235564677</v>
       </c>
       <c r="C32">
-        <v>4361.2185290233101</v>
+        <v>4.3612185290233096</v>
       </c>
       <c r="D32">
-        <v>16981.041658710201</v>
+        <v>16.9810416587102</v>
       </c>
       <c r="E32">
-        <v>5581.3984825981597</v>
+        <v>5.5813984825981597</v>
       </c>
       <c r="F32">
-        <v>3913.0774313950401</v>
+        <v>3.9130774313950401</v>
       </c>
       <c r="G32">
-        <v>1286.1663540336799</v>
+        <v>1.2861663540336801</v>
       </c>
       <c r="H32">
-        <v>8664.3507014028</v>
+        <v>8.6643507014027996</v>
       </c>
       <c r="I32">
-        <v>2847.83435724643</v>
+        <v>2.84783435724643</v>
       </c>
       <c r="J32">
-        <v>3855.4120240480902</v>
+        <v>3.85541202404809</v>
       </c>
       <c r="K32">
-        <v>1267.21265122007</v>
+        <v>1.2672126512200701</v>
       </c>
       <c r="L32">
-        <v>13868.613577154299</v>
+        <v>13.868613577154299</v>
       </c>
       <c r="M32">
-        <v>4558.3928436783899</v>
+        <v>4.5583928436783898</v>
       </c>
       <c r="N32">
-        <v>19519.788637274502</v>
+        <v>19.519788637274502</v>
       </c>
       <c r="O32">
-        <v>6415.8442615231197</v>
+        <v>6.4158442615231204</v>
       </c>
       <c r="P32">
-        <v>11478.045758183</v>
+        <v>11.478045758183001</v>
       </c>
       <c r="Q32">
-        <v>3772.6511992304299</v>
+        <v>3.7726511992304301</v>
       </c>
       <c r="R32">
-        <v>1951.2369677419299</v>
+        <v>1.9512369677419299</v>
       </c>
       <c r="S32">
-        <v>641.34057673417601</v>
+        <v>0.64134057673417599</v>
       </c>
       <c r="T32">
-        <v>7914.5132865731402</v>
+        <v>7.9145132865731398</v>
       </c>
       <c r="U32">
-        <v>2601.3747175235098</v>
+        <v>2.6013747175235098</v>
       </c>
       <c r="V32">
-        <v>4764.8022580645102</v>
+        <v>4.7648022580645097</v>
       </c>
       <c r="W32">
-        <v>1566.1147665461599</v>
+        <v>1.5661147665461601</v>
       </c>
       <c r="X32">
-        <v>5434.2754435483803</v>
+        <v>5.4342754435483798</v>
       </c>
       <c r="Y32">
-        <v>1786.1599614581701</v>
+        <v>1.78615996145817</v>
       </c>
       <c r="Z32" s="4"/>
       <c r="AA32" s="4"/>
@@ -4354,76 +4354,76 @@
         <v>0.3125</v>
       </c>
       <c r="B33">
-        <v>13867.9418558407</v>
+        <v>13.8679418558407</v>
       </c>
       <c r="C33">
-        <v>4558.1720595594998</v>
+        <v>4.5581720595595003</v>
       </c>
       <c r="D33">
-        <v>17822.281040014001</v>
+        <v>17.822281040014001</v>
       </c>
       <c r="E33">
-        <v>5857.9004958832202</v>
+        <v>5.8579004958832197</v>
       </c>
       <c r="F33">
-        <v>4472.5422787510497</v>
+        <v>4.4725422787510496</v>
       </c>
       <c r="G33">
-        <v>1470.0535567659199</v>
+        <v>1.4700535567659201</v>
       </c>
       <c r="H33">
-        <v>8947.5434869739402</v>
+        <v>8.9475434869739399</v>
       </c>
       <c r="I33">
-        <v>2940.91532456499</v>
+        <v>2.9409153245649899</v>
       </c>
       <c r="J33">
-        <v>3981.4254909819601</v>
+        <v>3.9814254909819602</v>
       </c>
       <c r="K33">
-        <v>1308.6312748397199</v>
+        <v>1.30863127483972</v>
       </c>
       <c r="L33">
-        <v>14321.906783567099</v>
+        <v>14.321906783567099</v>
       </c>
       <c r="M33">
-        <v>4707.3831156118504</v>
+        <v>4.70738311561185</v>
       </c>
       <c r="N33">
-        <v>20157.789511022002</v>
+        <v>20.157789511021999</v>
       </c>
       <c r="O33">
-        <v>6625.5450078141503</v>
+        <v>6.62554500781415</v>
       </c>
       <c r="P33">
-        <v>11853.2036740146</v>
+        <v>11.853203674014599</v>
       </c>
       <c r="Q33">
-        <v>3895.9596430963302</v>
+        <v>3.8959596430963299</v>
       </c>
       <c r="R33">
-        <v>2292.6178064516098</v>
+        <v>2.2926178064516098</v>
       </c>
       <c r="S33">
-        <v>753.547032230676</v>
+        <v>0.75354703223067598</v>
       </c>
       <c r="T33">
-        <v>8173.1977675350599</v>
+        <v>8.1731977675350596</v>
       </c>
       <c r="U33">
-        <v>2686.4001946721401</v>
+        <v>2.6864001946721401</v>
       </c>
       <c r="V33">
-        <v>5598.43354838709</v>
+        <v>5.5984335483870904</v>
       </c>
       <c r="W33">
-        <v>1840.11612125494</v>
+        <v>1.84011612125494</v>
       </c>
       <c r="X33">
-        <v>6385.0351612903196</v>
+        <v>6.38503516129032</v>
       </c>
       <c r="Y33">
-        <v>2098.6595685242801</v>
+        <v>2.0986595685242802</v>
       </c>
       <c r="Z33" s="4"/>
       <c r="AA33" s="4"/>
@@ -4478,76 +4478,76 @@
         <v>0.32291666666666702</v>
       </c>
       <c r="B34">
-        <v>14265.927537785199</v>
+        <v>14.265927537785201</v>
       </c>
       <c r="C34">
-        <v>4688.9836273034398</v>
+        <v>4.6889836273034398</v>
       </c>
       <c r="D34">
-        <v>18559.2571601651</v>
+        <v>18.5592571601651</v>
       </c>
       <c r="E34">
-        <v>6100.1328324732804</v>
+        <v>6.10013283247328</v>
       </c>
       <c r="F34">
-        <v>5008.7563758161396</v>
+        <v>5.00875637581614</v>
       </c>
       <c r="G34">
-        <v>1646.29860744405</v>
+        <v>1.64629860744405</v>
       </c>
       <c r="H34">
-        <v>9089.1398797595193</v>
+        <v>9.0891398797595198</v>
       </c>
       <c r="I34">
-        <v>2987.4558082242702</v>
+        <v>2.9874558082242699</v>
       </c>
       <c r="J34">
-        <v>4044.4322244488899</v>
+        <v>4.0444322244488902</v>
       </c>
       <c r="K34">
-        <v>1329.34058664954</v>
+        <v>1.32934058664954</v>
       </c>
       <c r="L34">
-        <v>14548.553386773499</v>
+        <v>14.5485533867735</v>
       </c>
       <c r="M34">
-        <v>4781.8782515785797</v>
+        <v>4.78187825157858</v>
       </c>
       <c r="N34">
-        <v>20476.789947895701</v>
+        <v>20.4767899478957</v>
       </c>
       <c r="O34">
-        <v>6730.3953809596596</v>
+        <v>6.7303953809596599</v>
       </c>
       <c r="P34">
-        <v>12040.7826319305</v>
+        <v>12.040782631930499</v>
       </c>
       <c r="Q34">
-        <v>3957.6138650292801</v>
+        <v>3.95761386502928</v>
       </c>
       <c r="R34">
-        <v>2628.2899354838701</v>
+        <v>2.62828993548387</v>
       </c>
       <c r="S34">
-        <v>863.87712559512795</v>
+        <v>0.86387712559512797</v>
       </c>
       <c r="T34">
-        <v>8302.5400080160307</v>
+        <v>8.3025400080160292</v>
       </c>
       <c r="U34">
-        <v>2728.9129332464599</v>
+        <v>2.7289129332464599</v>
       </c>
       <c r="V34">
-        <v>6418.1245161290299</v>
+        <v>6.4181245161290299</v>
       </c>
       <c r="W34">
-        <v>2109.53551351039</v>
+        <v>2.1095355135103899</v>
       </c>
       <c r="X34">
-        <v>7319.8958870967699</v>
+        <v>7.3198958870967701</v>
       </c>
       <c r="Y34">
-        <v>2405.93342965284</v>
+        <v>2.4059334296528401</v>
       </c>
       <c r="Z34" s="4"/>
       <c r="AA34" s="4"/>
@@ -4602,76 +4602,76 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="B35">
-        <v>14500.821281013599</v>
+        <v>14.5008212810136</v>
       </c>
       <c r="C35">
-        <v>4766.1894671085802</v>
+        <v>4.76618946710858</v>
       </c>
       <c r="D35">
-        <v>19258.765778664001</v>
+        <v>19.258765778663999</v>
       </c>
       <c r="E35">
-        <v>6330.0501968095105</v>
+        <v>6.33005019680951</v>
       </c>
       <c r="F35">
-        <v>5477.9032261296697</v>
+        <v>5.4779032261296701</v>
       </c>
       <c r="G35">
-        <v>1800.4997201368401</v>
+        <v>1.80049972013684</v>
       </c>
       <c r="H35">
-        <v>9129.5959919839697</v>
+        <v>9.1295959919839706</v>
       </c>
       <c r="I35">
-        <v>3000.75308926978</v>
+        <v>3.00075308926978</v>
       </c>
       <c r="J35">
-        <v>4062.4341482965901</v>
+        <v>4.0624341482965898</v>
       </c>
       <c r="K35">
-        <v>1335.2575328809201</v>
+        <v>1.33525753288092</v>
       </c>
       <c r="L35">
-        <v>14613.309559118199</v>
+        <v>14.6133095591182</v>
       </c>
       <c r="M35">
-        <v>4803.1625761405003</v>
+        <v>4.8031625761405001</v>
       </c>
       <c r="N35">
-        <v>20567.9329298597</v>
+        <v>20.567932929859701</v>
       </c>
       <c r="O35">
-        <v>6760.3526304298102</v>
+        <v>6.7603526304298098</v>
       </c>
       <c r="P35">
-        <v>12094.376619906399</v>
+        <v>12.0943766199064</v>
       </c>
       <c r="Q35">
-        <v>3975.2293570101201</v>
+        <v>3.9752293570101198</v>
       </c>
       <c r="R35">
-        <v>2927.4263225806399</v>
+        <v>2.9274263225806401</v>
       </c>
       <c r="S35">
-        <v>962.19850131446901</v>
+        <v>0.96219850131446905</v>
       </c>
       <c r="T35">
-        <v>8339.4949338677307</v>
+        <v>8.33949493386773</v>
       </c>
       <c r="U35">
-        <v>2741.05942998197</v>
+        <v>2.7410594299819699</v>
       </c>
       <c r="V35">
-        <v>7148.59741935483</v>
+        <v>7.1485974193548296</v>
       </c>
       <c r="W35">
-        <v>2349.6303460645699</v>
+        <v>2.3496303460645702</v>
       </c>
       <c r="X35">
-        <v>8153.0030645161196</v>
+        <v>8.1530030645161204</v>
       </c>
       <c r="Y35">
-        <v>2679.7625167810102</v>
+        <v>2.6797625167810102</v>
       </c>
       <c r="Z35" s="4"/>
       <c r="AA35" s="4"/>
@@ -4726,76 +4726,76 @@
         <v>0.34375</v>
       </c>
       <c r="B36">
-        <v>14579.7793119787</v>
+        <v>14.579779311978699</v>
       </c>
       <c r="C36">
-        <v>4792.1417168630496</v>
+        <v>4.7921417168630498</v>
       </c>
       <c r="D36">
-        <v>19882.626740672102</v>
+        <v>19.882626740672102</v>
       </c>
       <c r="E36">
-        <v>6535.1033788631703</v>
+        <v>6.5351033788631696</v>
       </c>
       <c r="F36">
-        <v>5827.0127871064697</v>
+        <v>5.8270127871064696</v>
       </c>
       <c r="G36">
-        <v>1915.2464837958801</v>
+        <v>1.91524648379588</v>
       </c>
       <c r="H36">
-        <v>9089.1398797595193</v>
+        <v>9.0891398797595198</v>
       </c>
       <c r="I36">
-        <v>2987.4558082242702</v>
+        <v>2.9874558082242699</v>
       </c>
       <c r="J36">
-        <v>4044.4322244488899</v>
+        <v>4.0444322244488902</v>
       </c>
       <c r="K36">
-        <v>1329.34058664954</v>
+        <v>1.32934058664954</v>
       </c>
       <c r="L36">
-        <v>14548.553386773499</v>
+        <v>14.5485533867735</v>
       </c>
       <c r="M36">
-        <v>4781.8782515785797</v>
+        <v>4.78187825157858</v>
       </c>
       <c r="N36">
-        <v>20476.789947895701</v>
+        <v>20.4767899478957</v>
       </c>
       <c r="O36">
-        <v>6730.3953809596596</v>
+        <v>6.7303953809596599</v>
       </c>
       <c r="P36">
-        <v>12040.7826319305</v>
+        <v>12.040782631930499</v>
       </c>
       <c r="Q36">
-        <v>3957.6138650292801</v>
+        <v>3.95761386502928</v>
       </c>
       <c r="R36">
-        <v>3154.6329677419299</v>
+        <v>3.15463296774193</v>
       </c>
       <c r="S36">
-        <v>1036.87771416999</v>
+        <v>1.0368777141699901</v>
       </c>
       <c r="T36">
-        <v>8302.5400080160307</v>
+        <v>8.3025400080160292</v>
       </c>
       <c r="U36">
-        <v>2728.9129332464599</v>
+        <v>2.7289129332464599</v>
       </c>
       <c r="V36">
-        <v>7703.4222580645101</v>
+        <v>7.70342225806451</v>
       </c>
       <c r="W36">
-        <v>2531.9924517068698</v>
+        <v>2.5319924517068699</v>
       </c>
       <c r="X36">
-        <v>8785.78294354838</v>
+        <v>8.7857829435483801</v>
       </c>
       <c r="Y36">
-        <v>2887.74720509592</v>
+        <v>2.8877472050959199</v>
       </c>
       <c r="Z36" s="4"/>
       <c r="AA36" s="4"/>
@@ -4850,76 +4850,76 @@
         <v>0.35416666666666702</v>
       </c>
       <c r="B37">
-        <v>14487.7130072402</v>
+        <v>14.487713007240201</v>
       </c>
       <c r="C37">
-        <v>4761.8809858729501</v>
+        <v>4.7618809858729501</v>
       </c>
       <c r="D37">
-        <v>20351.4784573978</v>
+        <v>20.3514784573978</v>
       </c>
       <c r="E37">
-        <v>6689.2074858367296</v>
+        <v>6.6892074858367296</v>
       </c>
       <c r="F37">
-        <v>5992.8710794976996</v>
+        <v>5.9928710794977</v>
       </c>
       <c r="G37">
-        <v>1969.7614682169899</v>
+        <v>1.9697614682169899</v>
       </c>
       <c r="H37">
-        <v>8974.5142284569101</v>
+        <v>8.9745142284569095</v>
       </c>
       <c r="I37">
-        <v>2949.7801785953302</v>
+        <v>2.9497801785953301</v>
       </c>
       <c r="J37">
-        <v>3993.4267735470899</v>
+        <v>3.9934267735470899</v>
       </c>
       <c r="K37">
-        <v>1312.57590566064</v>
+        <v>1.3125759056606401</v>
       </c>
       <c r="L37">
-        <v>14365.077565130199</v>
+        <v>14.3650775651302</v>
       </c>
       <c r="M37">
-        <v>4721.5726653197999</v>
+        <v>4.7215726653198002</v>
       </c>
       <c r="N37">
-        <v>20218.551498998</v>
+        <v>20.218551498998</v>
       </c>
       <c r="O37">
-        <v>6645.5165074609104</v>
+        <v>6.6455165074609202</v>
       </c>
       <c r="P37">
-        <v>11888.932999331901</v>
+        <v>11.8889329993319</v>
       </c>
       <c r="Q37">
-        <v>3907.7033044168902</v>
+        <v>3.9077033044168901</v>
       </c>
       <c r="R37">
-        <v>3268.80716129032</v>
+        <v>3.26880716129032</v>
       </c>
       <c r="S37">
-        <v>1074.4049568109599</v>
+        <v>1.0744049568109599</v>
       </c>
       <c r="T37">
-        <v>8197.8343847695305</v>
+        <v>8.1978343847695303</v>
       </c>
       <c r="U37">
-        <v>2694.4978591624899</v>
+        <v>2.6944978591624902</v>
       </c>
       <c r="V37">
-        <v>7982.2287096774098</v>
+        <v>7.9822287096774103</v>
       </c>
       <c r="W37">
-        <v>2623.6317007733501</v>
+        <v>2.6236317007733501</v>
       </c>
       <c r="X37">
-        <v>9103.7627822580598</v>
+        <v>9.1037627822580607</v>
       </c>
       <c r="Y37">
-        <v>2992.2621238471202</v>
+        <v>2.9922621238471199</v>
       </c>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
@@ -4974,76 +4974,76 @@
         <v>0.36458333333333298</v>
       </c>
       <c r="B38">
-        <v>14237.1141633589</v>
+        <v>14.2371141633589</v>
       </c>
       <c r="C38">
-        <v>4679.5131291129601</v>
+        <v>4.6795131291129604</v>
       </c>
       <c r="D38">
-        <v>20617.5084135748</v>
+        <v>20.6175084135748</v>
       </c>
       <c r="E38">
-        <v>6776.6473039335197</v>
+        <v>6.7766473039335198</v>
       </c>
       <c r="F38">
-        <v>5912.5428717919604</v>
+        <v>5.9125428717919597</v>
       </c>
       <c r="G38">
-        <v>1943.3588631466</v>
+        <v>1.9433588631465999</v>
       </c>
       <c r="H38">
-        <v>8812.6897795591103</v>
+        <v>8.8126897795591095</v>
       </c>
       <c r="I38">
-        <v>2896.5910544132998</v>
+        <v>2.8965910544133</v>
       </c>
       <c r="J38">
-        <v>3921.4190781563102</v>
+        <v>3.9214190781563101</v>
       </c>
       <c r="K38">
-        <v>1288.9081207351301</v>
+        <v>1.2889081207351301</v>
       </c>
       <c r="L38">
-        <v>14106.0528757515</v>
+        <v>14.1060528757515</v>
       </c>
       <c r="M38">
-        <v>4636.4353670721102</v>
+        <v>4.6364353670721101</v>
       </c>
       <c r="N38">
-        <v>19853.979571142201</v>
+        <v>19.853979571142201</v>
       </c>
       <c r="O38">
-        <v>6525.6875095803298</v>
+        <v>6.5256875095803304</v>
       </c>
       <c r="P38">
-        <v>11674.557047428099</v>
+        <v>11.674557047428101</v>
       </c>
       <c r="Q38">
-        <v>3837.2413364935201</v>
+        <v>3.8372413364935198</v>
       </c>
       <c r="R38">
-        <v>3227.7044516128999</v>
+        <v>3.2277044516129001</v>
       </c>
       <c r="S38">
-        <v>1060.89514946022</v>
+        <v>1.0608951494602199</v>
       </c>
       <c r="T38">
-        <v>8050.0146813627198</v>
+        <v>8.05001468136272</v>
       </c>
       <c r="U38">
-        <v>2645.9118722204098</v>
+        <v>2.64591187222041</v>
       </c>
       <c r="V38">
-        <v>7881.8583870967695</v>
+        <v>7.88185838709677</v>
       </c>
       <c r="W38">
-        <v>2590.6415711094201</v>
+        <v>2.5906415711094199</v>
       </c>
       <c r="X38">
-        <v>8989.2900403225794</v>
+        <v>8.9892900403225795</v>
       </c>
       <c r="Y38">
-        <v>2954.63675309669</v>
+        <v>2.9546367530966902</v>
       </c>
       <c r="Z38" s="4"/>
       <c r="AA38" s="4"/>
@@ -5098,76 +5098,76 @@
         <v>0.375</v>
       </c>
       <c r="B39">
-        <v>13825.829479475</v>
+        <v>13.825829479475001</v>
       </c>
       <c r="C39">
-        <v>4544.33039081681</v>
+        <v>4.5443303908168096</v>
       </c>
       <c r="D39">
-        <v>20633.047072655601</v>
+        <v>20.6330470726556</v>
       </c>
       <c r="E39">
-        <v>6781.7546141891698</v>
+        <v>6.78175461418917</v>
       </c>
       <c r="F39">
-        <v>5556.5384186114097</v>
+        <v>5.5565384186114102</v>
       </c>
       <c r="G39">
-        <v>1826.3458580132601</v>
+        <v>1.8263458580132601</v>
       </c>
       <c r="H39">
-        <v>8610.4092184368692</v>
+        <v>8.6104092184368692</v>
       </c>
       <c r="I39">
-        <v>2830.1046491857501</v>
+        <v>2.83010464918575</v>
       </c>
       <c r="J39">
-        <v>3831.4094589178299</v>
+        <v>3.8314094589178298</v>
       </c>
       <c r="K39">
-        <v>1259.32338957824</v>
+        <v>1.2593233895782401</v>
       </c>
       <c r="L39">
-        <v>13782.272014028</v>
+        <v>13.782272014028001</v>
       </c>
       <c r="M39">
-        <v>4530.0137442625</v>
+        <v>4.5300137442624999</v>
       </c>
       <c r="N39">
-        <v>19398.264661322599</v>
+        <v>19.3982646613226</v>
       </c>
       <c r="O39">
-        <v>6375.9012622295904</v>
+        <v>6.3759012622295899</v>
       </c>
       <c r="P39">
-        <v>11406.587107548399</v>
+        <v>11.4065871075484</v>
       </c>
       <c r="Q39">
-        <v>3749.1638765893099</v>
+        <v>3.7491638765893098</v>
       </c>
       <c r="R39">
-        <v>3011.9152258064501</v>
+        <v>3.0119152258064501</v>
       </c>
       <c r="S39">
-        <v>989.96866086878697</v>
+        <v>0.98996866086878699</v>
       </c>
       <c r="T39">
-        <v>7865.2400521042</v>
+        <v>7.8652400521042001</v>
       </c>
       <c r="U39">
-        <v>2585.1793885428201</v>
+        <v>2.5851793885428198</v>
       </c>
       <c r="V39">
-        <v>7354.9141935483804</v>
+        <v>7.3549141935483799</v>
       </c>
       <c r="W39">
-        <v>2417.4433903737699</v>
+        <v>2.4174433903737702</v>
       </c>
       <c r="X39">
-        <v>8388.3081451612907</v>
+        <v>8.3883081451612895</v>
       </c>
       <c r="Y39">
-        <v>2757.1035566568999</v>
+        <v>2.7571035566569</v>
       </c>
       <c r="Z39" s="4"/>
       <c r="AA39" s="4"/>
@@ -5222,76 +5222,76 @@
         <v>0.38541666666666702</v>
       </c>
       <c r="B40">
-        <v>13333.6397093541</v>
+        <v>13.333639709354101</v>
       </c>
       <c r="C40">
-        <v>4382.5554366464303</v>
+        <v>4.3825554366464301</v>
       </c>
       <c r="D40">
-        <v>20488.3745553382</v>
+        <v>20.488374555338201</v>
       </c>
       <c r="E40">
-        <v>6734.2030572907297</v>
+        <v>6.7342030572907303</v>
       </c>
       <c r="F40">
-        <v>5013.4786301635504</v>
+        <v>5.0134786301635499</v>
       </c>
       <c r="G40">
-        <v>1647.85073738865</v>
+        <v>1.6478507373886599</v>
       </c>
       <c r="H40">
-        <v>8401.3859719438806</v>
+        <v>8.4013859719438795</v>
       </c>
       <c r="I40">
-        <v>2761.4020304506298</v>
+        <v>2.7614020304506299</v>
       </c>
       <c r="J40">
-        <v>3738.3995190380701</v>
+        <v>3.7383995190380701</v>
       </c>
       <c r="K40">
-        <v>1228.75250071612</v>
+        <v>1.22875250071612</v>
       </c>
       <c r="L40">
-        <v>13447.6984569138</v>
+        <v>13.4476984569138</v>
       </c>
       <c r="M40">
-        <v>4420.0447340258997</v>
+        <v>4.4200447340258897</v>
       </c>
       <c r="N40">
-        <v>18927.359254509</v>
+        <v>18.927359254509</v>
       </c>
       <c r="O40">
-        <v>6221.1221399671704</v>
+        <v>6.2211221399671697</v>
       </c>
       <c r="P40">
-        <v>11129.6848363393</v>
+        <v>11.129684836339299</v>
       </c>
       <c r="Q40">
-        <v>3658.1505013549499</v>
+        <v>3.65815050135495</v>
       </c>
       <c r="R40">
-        <v>2676.2430967741898</v>
+        <v>2.6762430967741899</v>
       </c>
       <c r="S40">
-        <v>879.63856750433501</v>
+        <v>0.879638567504335</v>
       </c>
       <c r="T40">
-        <v>7674.3062685370696</v>
+        <v>7.6743062685370704</v>
       </c>
       <c r="U40">
-        <v>2522.4224887426399</v>
+        <v>2.5224224887426399</v>
       </c>
       <c r="V40">
-        <v>6535.2232258064496</v>
+        <v>6.5352232258064502</v>
       </c>
       <c r="W40">
-        <v>2148.0239981183099</v>
+        <v>2.14802399811831</v>
       </c>
       <c r="X40">
-        <v>7453.4474193548303</v>
+        <v>7.4534474193548297</v>
       </c>
       <c r="Y40">
-        <v>2449.8296955283499</v>
+        <v>2.4498296955283498</v>
       </c>
       <c r="Z40" s="4"/>
       <c r="AA40" s="4"/>
@@ -5346,76 +5346,76 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B41">
-        <v>12814.898487620399</v>
+        <v>12.8148984876204</v>
       </c>
       <c r="C41">
-        <v>4212.0534423614699</v>
+        <v>4.2120534423614702</v>
       </c>
       <c r="D41">
-        <v>20263.784854204001</v>
+        <v>20.263784854204001</v>
       </c>
       <c r="E41">
-        <v>6660.3839923410396</v>
+        <v>6.6603839923410399</v>
       </c>
       <c r="F41">
-        <v>4401.1954142963295</v>
+        <v>4.4011954142963301</v>
       </c>
       <c r="G41">
-        <v>1446.6029764652999</v>
+        <v>1.4466029764652999</v>
       </c>
       <c r="H41">
-        <v>8192.3627254508992</v>
+        <v>8.1923627254509004</v>
       </c>
       <c r="I41">
-        <v>2692.6994117155</v>
+        <v>2.6926994117155001</v>
       </c>
       <c r="J41">
-        <v>3645.38957915831</v>
+        <v>3.64538957915831</v>
       </c>
       <c r="K41">
-        <v>1198.181611854</v>
+        <v>1.1981816118540001</v>
       </c>
       <c r="L41">
-        <v>13113.124899799601</v>
+        <v>13.113124899799599</v>
       </c>
       <c r="M41">
-        <v>4310.0757237893004</v>
+        <v>4.3100757237892999</v>
       </c>
       <c r="N41">
-        <v>18456.453847695298</v>
+        <v>18.4564538476953</v>
       </c>
       <c r="O41">
-        <v>6066.3430177047403</v>
+        <v>6.0663430177047397</v>
       </c>
       <c r="P41">
-        <v>10852.782565130199</v>
+        <v>10.8527825651302</v>
       </c>
       <c r="Q41">
-        <v>3567.1371261206</v>
+        <v>3.5671371261206</v>
       </c>
       <c r="R41">
-        <v>2296.0430322580601</v>
+        <v>2.2960430322580598</v>
       </c>
       <c r="S41">
-        <v>754.67284950990495</v>
+        <v>0.75467284950990499</v>
       </c>
       <c r="T41">
-        <v>7483.3724849699302</v>
+        <v>7.4833724849699301</v>
       </c>
       <c r="U41">
-        <v>2459.6655889424701</v>
+        <v>2.4596655889424701</v>
       </c>
       <c r="V41">
-        <v>5606.7977419354802</v>
+        <v>5.6067977419354804</v>
       </c>
       <c r="W41">
-        <v>1842.86529872693</v>
+        <v>1.8428652987269301</v>
       </c>
       <c r="X41">
-        <v>6394.5745564516101</v>
+        <v>6.3945745564516097</v>
       </c>
       <c r="Y41">
-        <v>2101.7950160868199</v>
+        <v>2.10179501608682</v>
       </c>
       <c r="Z41" s="4"/>
       <c r="AA41" s="4"/>
@@ -5470,76 +5470,76 @@
         <v>0.40625</v>
       </c>
       <c r="B42">
-        <v>12371.742299437499</v>
+        <v>12.3717422994375</v>
       </c>
       <c r="C42">
-        <v>4066.3950471941298</v>
+        <v>4.0663950471941304</v>
       </c>
       <c r="D42">
-        <v>20098.3052494154</v>
+        <v>20.0983052494154</v>
       </c>
       <c r="E42">
-        <v>6605.9934765157604</v>
+        <v>6.60599347651576</v>
       </c>
       <c r="F42">
-        <v>3842.7184842265101</v>
+        <v>3.8427184842265101</v>
       </c>
       <c r="G42">
-        <v>1263.0404864422701</v>
+        <v>1.26304048644227</v>
       </c>
       <c r="H42">
-        <v>8023.7955911823601</v>
+        <v>8.0237955911823597</v>
       </c>
       <c r="I42">
-        <v>2637.29407402588</v>
+        <v>2.6372940740258799</v>
       </c>
       <c r="J42">
-        <v>3570.3815631262501</v>
+        <v>3.5703815631262499</v>
       </c>
       <c r="K42">
-        <v>1173.5276692232601</v>
+        <v>1.1735276692232599</v>
       </c>
       <c r="L42">
-        <v>12843.307515029999</v>
+        <v>12.84330751503</v>
       </c>
       <c r="M42">
-        <v>4221.3910381146197</v>
+        <v>4.2213910381146196</v>
       </c>
       <c r="N42">
-        <v>18076.691422845601</v>
+        <v>18.076691422845599</v>
       </c>
       <c r="O42">
-        <v>5941.5211449124599</v>
+        <v>5.9415211449124596</v>
       </c>
       <c r="P42">
-        <v>10629.474281897101</v>
+        <v>10.6294742818971</v>
       </c>
       <c r="Q42">
-        <v>3493.7392428670901</v>
+        <v>3.4937392428670901</v>
       </c>
       <c r="R42">
-        <v>1947.8117419354801</v>
+        <v>1.9478117419354799</v>
       </c>
       <c r="S42">
-        <v>640.21475945494694</v>
+        <v>0.64021475945494699</v>
       </c>
       <c r="T42">
-        <v>7329.3936272544997</v>
+        <v>7.3293936272545004</v>
       </c>
       <c r="U42">
-        <v>2409.0551858778099</v>
+        <v>2.40905518587781</v>
       </c>
       <c r="V42">
-        <v>4756.43806451612</v>
+        <v>4.7564380645161197</v>
       </c>
       <c r="W42">
-        <v>1563.36558907416</v>
+        <v>1.56336558907416</v>
       </c>
       <c r="X42">
-        <v>5424.7360483870898</v>
+        <v>5.4247360483870901</v>
       </c>
       <c r="Y42">
-        <v>1783.02451389563</v>
+        <v>1.78302451389563</v>
       </c>
       <c r="Z42" s="4"/>
       <c r="AA42" s="4"/>
@@ -5594,76 +5594,76 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B43">
-        <v>12058.4138979248</v>
+        <v>12.058413897924799</v>
       </c>
       <c r="C43">
-        <v>3963.4089819157998</v>
+        <v>3.9634089819158</v>
       </c>
       <c r="D43">
-        <v>20062.4521539989</v>
+        <v>20.062452153998901</v>
       </c>
       <c r="E43">
-        <v>6594.2091339309</v>
+        <v>6.5942091339309004</v>
       </c>
       <c r="F43">
-        <v>3431.7148814564598</v>
+        <v>3.4317148814564602</v>
       </c>
       <c r="G43">
-        <v>1127.9501350405001</v>
+        <v>1.1279501350404999</v>
       </c>
       <c r="H43">
-        <v>7909.16993987976</v>
+        <v>7.9091699398797601</v>
       </c>
       <c r="I43">
-        <v>2599.61844439694</v>
+        <v>2.5996184443969401</v>
       </c>
       <c r="J43">
-        <v>3519.37611222444</v>
+        <v>3.5193761122244398</v>
       </c>
       <c r="K43">
-        <v>1156.7629882343499</v>
+        <v>1.15676298823435</v>
       </c>
       <c r="L43">
-        <v>12659.831693386701</v>
+        <v>12.6598316933867</v>
       </c>
       <c r="M43">
-        <v>4161.0854518558399</v>
+        <v>4.1610854518558398</v>
       </c>
       <c r="N43">
-        <v>17818.452973947798</v>
+        <v>17.818452973947799</v>
       </c>
       <c r="O43">
-        <v>5856.6422714137098</v>
+        <v>5.8566422714137101</v>
       </c>
       <c r="P43">
-        <v>10477.624649298499</v>
+        <v>10.4776246492985</v>
       </c>
       <c r="Q43">
-        <v>3443.8286822547002</v>
+        <v>3.4438286822547002</v>
       </c>
       <c r="R43">
-        <v>1690.9198064516099</v>
+        <v>1.69091980645161</v>
       </c>
       <c r="S43">
-        <v>555.77846351276401</v>
+        <v>0.55577846351276405</v>
       </c>
       <c r="T43">
-        <v>7224.6880040080096</v>
+        <v>7.2246880040080104</v>
       </c>
       <c r="U43">
-        <v>2374.6401117938399</v>
+        <v>2.3746401117938398</v>
       </c>
       <c r="V43">
-        <v>4129.1235483870896</v>
+        <v>4.1291235483870903</v>
       </c>
       <c r="W43">
-        <v>1357.1772786745801</v>
+        <v>1.3571772786745799</v>
       </c>
       <c r="X43">
-        <v>4709.2814112903197</v>
+        <v>4.7092814112903199</v>
       </c>
       <c r="Y43">
-        <v>1547.8659467054099</v>
+        <v>1.5478659467054099</v>
       </c>
       <c r="Z43" s="4"/>
       <c r="AA43" s="4"/>
@@ -5718,76 +5718,76 @@
         <v>0.42708333333333298</v>
       </c>
       <c r="B44">
-        <v>11856.7532718986</v>
+        <v>11.856753271898601</v>
       </c>
       <c r="C44">
-        <v>3897.1263395005599</v>
+        <v>3.8971263395005602</v>
       </c>
       <c r="D44">
-        <v>20153.516967503201</v>
+        <v>20.153516967503201</v>
       </c>
       <c r="E44">
-        <v>6624.1406906708498</v>
+        <v>6.62414069067085</v>
       </c>
       <c r="F44">
-        <v>3168.5904273870301</v>
+        <v>3.1685904273870298</v>
       </c>
       <c r="G44">
-        <v>1041.4653093040099</v>
+        <v>1.04146530930401</v>
       </c>
       <c r="H44">
-        <v>7835.0004008016003</v>
+        <v>7.8350004008015999</v>
       </c>
       <c r="I44">
-        <v>2575.2400958134999</v>
+        <v>2.5752400958135002</v>
       </c>
       <c r="J44">
-        <v>3486.3725851703398</v>
+        <v>3.48637258517034</v>
       </c>
       <c r="K44">
-        <v>1145.91525347683</v>
+        <v>1.14591525347683</v>
       </c>
       <c r="L44">
-        <v>12541.1120440881</v>
+        <v>12.5411120440881</v>
       </c>
       <c r="M44">
-        <v>4122.0641901589797</v>
+        <v>4.1220641901589801</v>
       </c>
       <c r="N44">
-        <v>17651.357507014</v>
+        <v>17.651357507014001</v>
       </c>
       <c r="O44">
-        <v>5801.7206473851102</v>
+        <v>5.8017206473851104</v>
       </c>
       <c r="P44">
-        <v>10379.369004676</v>
+        <v>10.379369004676001</v>
       </c>
       <c r="Q44">
-        <v>3411.5336136231599</v>
+        <v>3.4115336136231602</v>
       </c>
       <c r="R44">
-        <v>1526.5089677419301</v>
+        <v>1.5265089677419299</v>
       </c>
       <c r="S44">
-        <v>501.73923410976801</v>
+        <v>0.50173923410976795</v>
       </c>
       <c r="T44">
-        <v>7156.9373066132202</v>
+        <v>7.1569373066132203</v>
       </c>
       <c r="U44">
-        <v>2352.3715344453899</v>
+        <v>2.3523715344453899</v>
       </c>
       <c r="V44">
-        <v>3727.6422580645099</v>
+        <v>3.7276422580645101</v>
       </c>
       <c r="W44">
-        <v>1225.21676001885</v>
+        <v>1.2252167600188499</v>
       </c>
       <c r="X44">
-        <v>4251.3904435483801</v>
+        <v>4.25139044354838</v>
       </c>
       <c r="Y44">
-        <v>1397.36446370367</v>
+        <v>1.39736446370367</v>
       </c>
       <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
@@ -5842,76 +5842,76 @@
         <v>0.4375</v>
       </c>
       <c r="B45">
-        <v>11757.2291310362</v>
+        <v>11.757229131036199</v>
       </c>
       <c r="C45">
-        <v>3864.4143363175099</v>
+        <v>3.8644143363175099</v>
       </c>
       <c r="D45">
-        <v>20365.154566052901</v>
+        <v>20.365154566052901</v>
       </c>
       <c r="E45">
-        <v>6693.7026053723603</v>
+        <v>6.6937026053723603</v>
       </c>
       <c r="F45">
-        <v>3028.4956865343502</v>
+        <v>3.0284956865343502</v>
       </c>
       <c r="G45">
-        <v>995.41839476659197</v>
+        <v>0.995418394766592</v>
       </c>
       <c r="H45">
-        <v>7801.2869739478901</v>
+        <v>7.8012869739478896</v>
       </c>
       <c r="I45">
-        <v>2564.1590282755801</v>
+        <v>2.5641590282755802</v>
       </c>
       <c r="J45">
-        <v>3471.3709819639198</v>
+        <v>3.4713709819639198</v>
       </c>
       <c r="K45">
-        <v>1140.9844649506799</v>
+        <v>1.14098446495068</v>
       </c>
       <c r="L45">
-        <v>12487.1485671342</v>
+        <v>12.4871485671342</v>
       </c>
       <c r="M45">
-        <v>4104.3272530240502</v>
+        <v>4.1043272530240502</v>
       </c>
       <c r="N45">
-        <v>17575.405022044</v>
+        <v>17.575405022043999</v>
       </c>
       <c r="O45">
-        <v>5776.7562728266503</v>
+        <v>5.7767562728266499</v>
       </c>
       <c r="P45">
-        <v>10334.7073480293</v>
+        <v>10.334707348029299</v>
       </c>
       <c r="Q45">
-        <v>3396.8540369724601</v>
+        <v>3.39685403697246</v>
       </c>
       <c r="R45">
-        <v>1438.5948387096701</v>
+        <v>1.4385948387096701</v>
       </c>
       <c r="S45">
-        <v>472.84325727622098</v>
+        <v>0.47284325727622101</v>
       </c>
       <c r="T45">
-        <v>7126.14153507014</v>
+        <v>7.1261415350701398</v>
       </c>
       <c r="U45">
-        <v>2342.2494538324499</v>
+        <v>2.3422494538324501</v>
       </c>
       <c r="V45">
-        <v>3512.9612903225802</v>
+        <v>3.51296129032258</v>
       </c>
       <c r="W45">
-        <v>1154.6545382376601</v>
+        <v>1.1546545382376601</v>
       </c>
       <c r="X45">
-        <v>4006.5459677419299</v>
+        <v>4.0065459677419302</v>
       </c>
       <c r="Y45">
-        <v>1316.88797626524</v>
+        <v>1.3168879762652399</v>
       </c>
       <c r="Z45" s="4"/>
       <c r="AA45" s="4"/>
@@ -5966,76 +5966,76 @@
         <v>0.44791666666666702</v>
       </c>
       <c r="B46">
-        <v>11742.2513891007</v>
+        <v>11.7422513891007</v>
       </c>
       <c r="C46">
-        <v>3859.49139061185</v>
+        <v>3.8594913906118502</v>
       </c>
       <c r="D46">
-        <v>20693.871404942602</v>
+        <v>20.693871404942598</v>
       </c>
       <c r="E46">
-        <v>6801.7466054200404</v>
+        <v>6.8017466054200399</v>
       </c>
       <c r="F46">
-        <v>2989.4465736311299</v>
+        <v>2.9894465736311302</v>
       </c>
       <c r="G46">
-        <v>982.58357203396702</v>
+        <v>0.98258357203396696</v>
       </c>
       <c r="H46">
-        <v>7801.2869739478901</v>
+        <v>7.8012869739478896</v>
       </c>
       <c r="I46">
-        <v>2564.1590282755801</v>
+        <v>2.5641590282755802</v>
       </c>
       <c r="J46">
-        <v>3471.3709819639198</v>
+        <v>3.4713709819639198</v>
       </c>
       <c r="K46">
-        <v>1140.9844649506799</v>
+        <v>1.14098446495068</v>
       </c>
       <c r="L46">
-        <v>12487.1485671342</v>
+        <v>12.4871485671342</v>
       </c>
       <c r="M46">
-        <v>4104.3272530240502</v>
+        <v>4.1043272530240502</v>
       </c>
       <c r="N46">
-        <v>17575.405022044</v>
+        <v>17.575405022043999</v>
       </c>
       <c r="O46">
-        <v>5776.7562728266503</v>
+        <v>5.7767562728266499</v>
       </c>
       <c r="P46">
-        <v>10334.7073480293</v>
+        <v>10.334707348029299</v>
       </c>
       <c r="Q46">
-        <v>3396.8540369724601</v>
+        <v>3.39685403697246</v>
       </c>
       <c r="R46">
-        <v>1413.47651612903</v>
+        <v>1.4134765161290299</v>
       </c>
       <c r="S46">
-        <v>464.587263895207</v>
+        <v>0.46458726389520799</v>
       </c>
       <c r="T46">
-        <v>7126.14153507014</v>
+        <v>7.1261415350701398</v>
       </c>
       <c r="U46">
-        <v>2342.2494538324499</v>
+        <v>2.3422494538324501</v>
       </c>
       <c r="V46">
-        <v>3451.62387096774</v>
+        <v>3.4516238709677398</v>
       </c>
       <c r="W46">
-        <v>1134.4939034430299</v>
+        <v>1.1344939034430299</v>
       </c>
       <c r="X46">
-        <v>3936.5904032257999</v>
+        <v>3.9365904032258001</v>
       </c>
       <c r="Y46">
-        <v>1293.8946941399699</v>
+        <v>1.29389469413997</v>
       </c>
       <c r="Z46" s="4"/>
       <c r="AA46" s="4"/>
@@ -6090,76 +6090,76 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="B47">
-        <v>11792.8683469519</v>
+        <v>11.7928683469519</v>
       </c>
       <c r="C47">
-        <v>3876.1283801100399</v>
+        <v>3.8761283801100399</v>
       </c>
       <c r="D47">
-        <v>21111.2626684803</v>
+        <v>21.1112626684803</v>
       </c>
       <c r="E47">
-        <v>6938.9364793854002</v>
+        <v>6.9389364793853998</v>
       </c>
       <c r="F47">
-        <v>3025.9090840551999</v>
+        <v>3.0259090840552001</v>
       </c>
       <c r="G47">
-        <v>994.56821964527899</v>
+        <v>0.99456821964527897</v>
       </c>
       <c r="H47">
-        <v>7828.2577154308601</v>
+        <v>7.8282577154308601</v>
       </c>
       <c r="I47">
-        <v>2573.0238823059199</v>
+        <v>2.5730238823059199</v>
       </c>
       <c r="J47">
-        <v>3483.37226452905</v>
+        <v>3.4833722645290499</v>
       </c>
       <c r="K47">
-        <v>1144.9290957716</v>
+        <v>1.1449290957716001</v>
       </c>
       <c r="L47">
-        <v>12530.3193486973</v>
+        <v>12.530319348697301</v>
       </c>
       <c r="M47">
-        <v>4118.5168027319896</v>
+        <v>4.1185168027319898</v>
       </c>
       <c r="N47">
-        <v>17636.167010019999</v>
+        <v>17.636167010019999</v>
       </c>
       <c r="O47">
-        <v>5796.7277724734204</v>
+        <v>5.7967277724734201</v>
       </c>
       <c r="P47">
-        <v>10370.436673346599</v>
+        <v>10.3704366733466</v>
       </c>
       <c r="Q47">
-        <v>3408.5976982930201</v>
+        <v>3.4085976982930202</v>
       </c>
       <c r="R47">
-        <v>1435.16961290322</v>
+        <v>1.4351696129032201</v>
       </c>
       <c r="S47">
-        <v>471.71743999699203</v>
+        <v>0.47171743999699201</v>
       </c>
       <c r="T47">
-        <v>7150.7781523045996</v>
+        <v>7.1507781523045999</v>
       </c>
       <c r="U47">
-        <v>2350.3471183227998</v>
+        <v>2.3503471183228002</v>
       </c>
       <c r="V47">
-        <v>3504.59709677419</v>
+        <v>3.50459709677419</v>
       </c>
       <c r="W47">
-        <v>1151.9053607656599</v>
+        <v>1.15190536076566</v>
       </c>
       <c r="X47">
-        <v>3997.0065725806398</v>
+        <v>3.9970065725806401</v>
       </c>
       <c r="Y47">
-        <v>1313.7525287026999</v>
+        <v>1.3137525287027001</v>
       </c>
       <c r="Z47" s="4"/>
       <c r="AA47" s="4"/>
@@ -6214,76 +6214,76 @@
         <v>0.46875</v>
       </c>
       <c r="B48">
-        <v>11902.161058568699</v>
+        <v>11.9021610585687</v>
       </c>
       <c r="C48">
-        <v>3912.0511572303799</v>
+        <v>3.9120511572303802</v>
       </c>
       <c r="D48">
-        <v>21569.982825506599</v>
+        <v>21.5699828255066</v>
       </c>
       <c r="E48">
-        <v>7089.7105037251104</v>
+        <v>7.0897105037251098</v>
       </c>
       <c r="F48">
-        <v>3095.9687546867899</v>
+        <v>3.09596875468679</v>
       </c>
       <c r="G48">
-        <v>1017.59571979594</v>
+        <v>1.01759571979594</v>
       </c>
       <c r="H48">
-        <v>7888.9418837675303</v>
+        <v>7.8889418837675302</v>
       </c>
       <c r="I48">
-        <v>2592.9698038741799</v>
+        <v>2.5929698038741802</v>
       </c>
       <c r="J48">
-        <v>3510.3751503006001</v>
+        <v>3.5103751503006002</v>
       </c>
       <c r="K48">
-        <v>1153.80451511867</v>
+        <v>1.15380451511867</v>
       </c>
       <c r="L48">
-        <v>12627.4536072144</v>
+        <v>12.627453607214401</v>
       </c>
       <c r="M48">
-        <v>4150.4432895748796</v>
+        <v>4.1504432895748797</v>
       </c>
       <c r="N48">
-        <v>17772.881482965899</v>
+        <v>17.7728814829659</v>
       </c>
       <c r="O48">
-        <v>5841.6636466786404</v>
+        <v>5.84166364667864</v>
       </c>
       <c r="P48">
-        <v>10450.827655310601</v>
+        <v>10.450827655310601</v>
       </c>
       <c r="Q48">
-        <v>3435.02093626428</v>
+        <v>3.4350209362642801</v>
       </c>
       <c r="R48">
-        <v>1476.2723225806401</v>
+        <v>1.47627232258064</v>
       </c>
       <c r="S48">
-        <v>485.22724734774101</v>
+        <v>0.48522724734774098</v>
       </c>
       <c r="T48">
-        <v>7206.2105410821596</v>
+        <v>7.20621054108216</v>
       </c>
       <c r="U48">
-        <v>2368.5668634260801</v>
+        <v>2.3685668634260799</v>
       </c>
       <c r="V48">
-        <v>3604.9674193548299</v>
+        <v>3.6049674193548298</v>
       </c>
       <c r="W48">
-        <v>1184.8954904295999</v>
+        <v>1.1848954904296001</v>
       </c>
       <c r="X48">
-        <v>4111.4793145161202</v>
+        <v>4.1114793145161297</v>
       </c>
       <c r="Y48">
-        <v>1351.3778994531301</v>
+        <v>1.35137789945313</v>
       </c>
       <c r="Z48" s="4"/>
       <c r="AA48" s="4"/>
@@ -6338,76 +6338,76 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B49">
-        <v>12082.0513955653</v>
+        <v>12.0820513955653</v>
       </c>
       <c r="C49">
-        <v>3971.1782516764201</v>
+        <v>3.9711782516764198</v>
       </c>
       <c r="D49">
-        <v>22029.382996018201</v>
+        <v>22.029382996018199</v>
       </c>
       <c r="E49">
-        <v>7240.7080376886997</v>
+        <v>7.2407080376886999</v>
       </c>
       <c r="F49">
-        <v>3159.0802606826501</v>
+        <v>3.15908026068265</v>
       </c>
       <c r="G49">
-        <v>1038.3394686706799</v>
+        <v>1.0383394686706799</v>
       </c>
       <c r="H49">
-        <v>8003.5675350701404</v>
+        <v>8.0035675350701396</v>
       </c>
       <c r="I49">
-        <v>2630.6454335031199</v>
+        <v>2.63064543350312</v>
       </c>
       <c r="J49">
-        <v>3561.3806012024002</v>
+        <v>3.5613806012024001</v>
       </c>
       <c r="K49">
-        <v>1170.56919610757</v>
+        <v>1.1705691961075699</v>
       </c>
       <c r="L49">
-        <v>12810.9294288577</v>
+        <v>12.810929428857699</v>
       </c>
       <c r="M49">
-        <v>4210.7488758336603</v>
+        <v>4.2107488758336604</v>
       </c>
       <c r="N49">
-        <v>18031.119931863701</v>
+        <v>18.031119931863699</v>
       </c>
       <c r="O49">
-        <v>5926.5425201773896</v>
+        <v>5.9265425201773896</v>
       </c>
       <c r="P49">
-        <v>10602.6772879091</v>
+        <v>10.602677287909099</v>
       </c>
       <c r="Q49">
-        <v>3484.9314968766698</v>
+        <v>3.48493149687667</v>
       </c>
       <c r="R49">
-        <v>1509.3828387096701</v>
+        <v>1.5093828387096699</v>
       </c>
       <c r="S49">
-        <v>496.11014771362198</v>
+        <v>0.496110147713622</v>
       </c>
       <c r="T49">
-        <v>7310.9161643286498</v>
+        <v>7.31091616432865</v>
       </c>
       <c r="U49">
-        <v>2402.9819375100501</v>
+        <v>2.4029819375100501</v>
       </c>
       <c r="V49">
-        <v>3685.8212903225799</v>
+        <v>3.68582129032258</v>
       </c>
       <c r="W49">
-        <v>1211.4708726588799</v>
+        <v>1.2114708726588701</v>
       </c>
       <c r="X49">
-        <v>4203.6934677419304</v>
+        <v>4.20369346774193</v>
       </c>
       <c r="Y49">
-        <v>1381.68722589099</v>
+        <v>1.38168722589099</v>
       </c>
       <c r="Z49" s="4"/>
       <c r="AA49" s="4"/>
@@ -6462,76 +6462,76 @@
         <v>0.48958333333333298</v>
       </c>
       <c r="B50">
-        <v>12344.4612295558</v>
+        <v>12.344461229555799</v>
       </c>
       <c r="C50">
-        <v>4057.4281931517398</v>
+        <v>4.0574281931517397</v>
       </c>
       <c r="D50">
-        <v>22449.104738266102</v>
+        <v>22.449104738266101</v>
       </c>
       <c r="E50">
-        <v>7378.6639029635899</v>
+        <v>7.3786639029635896</v>
       </c>
       <c r="F50">
-        <v>3174.6982771995599</v>
+        <v>3.17469827719956</v>
       </c>
       <c r="G50">
-        <v>1043.4728624542099</v>
+        <v>1.04347286245421</v>
       </c>
       <c r="H50">
-        <v>8192.3627254508992</v>
+        <v>8.1923627254509004</v>
       </c>
       <c r="I50">
-        <v>2692.6994117155</v>
+        <v>2.6926994117155001</v>
       </c>
       <c r="J50">
-        <v>3645.38957915831</v>
+        <v>3.64538957915831</v>
       </c>
       <c r="K50">
-        <v>1198.181611854</v>
+        <v>1.1981816118540001</v>
       </c>
       <c r="L50">
-        <v>13113.124899799601</v>
+        <v>13.113124899799599</v>
       </c>
       <c r="M50">
-        <v>4310.0757237893004</v>
+        <v>4.3100757237892999</v>
       </c>
       <c r="N50">
-        <v>18456.453847695298</v>
+        <v>18.4564538476953</v>
       </c>
       <c r="O50">
-        <v>6066.3430177047403</v>
+        <v>6.0663430177047397</v>
       </c>
       <c r="P50">
-        <v>10852.782565130199</v>
+        <v>10.8527825651302</v>
       </c>
       <c r="Q50">
-        <v>3567.1371261206</v>
+        <v>3.5671371261206</v>
       </c>
       <c r="R50">
-        <v>1507.09935483871</v>
+        <v>1.5070993548387099</v>
       </c>
       <c r="S50">
-        <v>495.35960286080302</v>
+        <v>0.49535960286080299</v>
       </c>
       <c r="T50">
-        <v>7483.3724849699302</v>
+        <v>7.4833724849699301</v>
       </c>
       <c r="U50">
-        <v>2459.6655889424701</v>
+        <v>2.4596655889424701</v>
       </c>
       <c r="V50">
-        <v>3680.2451612903201</v>
+        <v>3.68024516129032</v>
       </c>
       <c r="W50">
-        <v>1209.6380876775499</v>
+        <v>1.2096380876775501</v>
       </c>
       <c r="X50">
-        <v>4197.33387096774</v>
+        <v>4.1973338709677401</v>
       </c>
       <c r="Y50">
-        <v>1379.59692751596</v>
+        <v>1.3795969275159601</v>
       </c>
       <c r="Z50" s="4"/>
       <c r="AA50" s="4"/>
@@ -6586,76 +6586,76 @@
         <v>0.5</v>
       </c>
       <c r="B51">
-        <v>12677.816850863001</v>
+        <v>12.677816850863</v>
       </c>
       <c r="C51">
-        <v>4166.9968872474201</v>
+        <v>4.1669968872474197</v>
       </c>
       <c r="D51">
-        <v>22780.666049556501</v>
+        <v>22.780666049556501</v>
       </c>
       <c r="E51">
-        <v>7487.6428358769999</v>
+        <v>7.4876428358769997</v>
       </c>
       <c r="F51">
-        <v>3112.64848972137</v>
+        <v>3.1126484897213702</v>
       </c>
       <c r="G51">
-        <v>1023.07808358041</v>
+        <v>1.0230780835804101</v>
       </c>
       <c r="H51">
-        <v>8455.3274549098205</v>
+        <v>8.4553274549098205</v>
       </c>
       <c r="I51">
-        <v>2779.1317385112998</v>
+        <v>2.7791317385113001</v>
       </c>
       <c r="J51">
-        <v>3762.40208416833</v>
+        <v>3.7624020841683299</v>
       </c>
       <c r="K51">
-        <v>1236.64176235795</v>
+        <v>1.23664176235795</v>
       </c>
       <c r="L51">
-        <v>13534.04002004</v>
+        <v>13.534040020040001</v>
       </c>
       <c r="M51">
-        <v>4448.4238334417896</v>
+        <v>4.4484238334417903</v>
       </c>
       <c r="N51">
-        <v>19048.883230460899</v>
+        <v>19.048883230460898</v>
       </c>
       <c r="O51">
-        <v>6261.0651392606997</v>
+        <v>6.2610651392607002</v>
       </c>
       <c r="P51">
-        <v>11201.143486973901</v>
+        <v>11.201143486973899</v>
       </c>
       <c r="Q51">
-        <v>3681.63782399608</v>
+        <v>3.6816378239960801</v>
       </c>
       <c r="R51">
-        <v>1450.01225806451</v>
+        <v>1.4500122580645101</v>
       </c>
       <c r="S51">
-        <v>476.59598154031801</v>
+        <v>0.47659598154031801</v>
       </c>
       <c r="T51">
-        <v>7723.5795030060099</v>
+        <v>7.7235795030060101</v>
       </c>
       <c r="U51">
-        <v>2538.6178177233301</v>
+        <v>2.5386178177233401</v>
       </c>
       <c r="V51">
-        <v>3540.8419354838702</v>
+        <v>3.5408419354838698</v>
       </c>
       <c r="W51">
-        <v>1163.8184631443</v>
+        <v>1.16381846314431</v>
       </c>
       <c r="X51">
-        <v>4038.3439516129001</v>
+        <v>4.0383439516128998</v>
       </c>
       <c r="Y51">
-        <v>1327.3394681403599</v>
+        <v>1.3273394681403601</v>
       </c>
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
@@ -6710,76 +6710,76 @@
         <v>0.51041666666666696</v>
       </c>
       <c r="B52">
-        <v>13017.647892171401</v>
+        <v>13.0176478921714</v>
       </c>
       <c r="C52">
-        <v>4278.6939489718798</v>
+        <v>4.2786939489718803</v>
       </c>
       <c r="D52">
-        <v>22986.9807178185</v>
+        <v>22.986980717818501</v>
       </c>
       <c r="E52">
-        <v>7555.4551879999699</v>
+        <v>7.5554551879999696</v>
       </c>
       <c r="F52">
-        <v>2995.8536999806001</v>
+        <v>2.9958536999806</v>
       </c>
       <c r="G52">
-        <v>984.68949262491105</v>
+        <v>0.98468949262491101</v>
       </c>
       <c r="H52">
-        <v>8738.5202404809606</v>
+        <v>8.7385202404809608</v>
       </c>
       <c r="I52">
-        <v>2872.2127058298602</v>
+        <v>2.8722127058298601</v>
       </c>
       <c r="J52">
-        <v>3888.4155511022</v>
+        <v>3.8884155511022001</v>
       </c>
       <c r="K52">
-        <v>1278.0603859775999</v>
+        <v>1.2780603859776001</v>
       </c>
       <c r="L52">
-        <v>13987.3332264529</v>
+        <v>13.9873332264529</v>
       </c>
       <c r="M52">
-        <v>4597.4141053752501</v>
+        <v>4.5974141053752504</v>
       </c>
       <c r="N52">
-        <v>19686.884104208399</v>
+        <v>19.686884104208399</v>
       </c>
       <c r="O52">
-        <v>6470.7658855517202</v>
+        <v>6.4707658855517201</v>
       </c>
       <c r="P52">
-        <v>11576.3014028056</v>
+        <v>11.576301402805599</v>
       </c>
       <c r="Q52">
-        <v>3804.9462678619798</v>
+        <v>3.8049462678619799</v>
       </c>
       <c r="R52">
-        <v>1356.3894193548299</v>
+        <v>1.35638941935483</v>
       </c>
       <c r="S52">
-        <v>445.82364257472301</v>
+        <v>0.44582364257472301</v>
       </c>
       <c r="T52">
-        <v>7982.2639839679296</v>
+        <v>7.9822639839679299</v>
       </c>
       <c r="U52">
-        <v>2623.6432948719598</v>
+        <v>2.6236432948719601</v>
       </c>
       <c r="V52">
-        <v>3312.2206451612901</v>
+        <v>3.3122206451612901</v>
       </c>
       <c r="W52">
-        <v>1088.67427890979</v>
+        <v>1.0886742789097901</v>
       </c>
       <c r="X52">
-        <v>3777.60048387096</v>
+        <v>3.7776004838709598</v>
       </c>
       <c r="Y52">
-        <v>1241.6372347643601</v>
+        <v>1.2416372347643601</v>
       </c>
       <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
@@ -6834,76 +6834,76 @@
         <v>0.52083333333333304</v>
       </c>
       <c r="B53">
-        <v>13275.3075984226</v>
+        <v>13.2753075984226</v>
       </c>
       <c r="C53">
-        <v>4363.3825989617098</v>
+        <v>4.3633825989617101</v>
       </c>
       <c r="D53">
-        <v>23029.619751293601</v>
+        <v>23.029619751293598</v>
       </c>
       <c r="E53">
-        <v>7569.4699605634096</v>
+        <v>7.5694699605634099</v>
       </c>
       <c r="F53">
-        <v>2855.8327603594198</v>
+        <v>2.8558327603594198</v>
       </c>
       <c r="G53">
-        <v>938.66683537922097</v>
+        <v>0.93866683537922102</v>
       </c>
       <c r="H53">
-        <v>8967.7715430861699</v>
+        <v>8.9677715430861706</v>
       </c>
       <c r="I53">
-        <v>2947.5639650877501</v>
+        <v>2.9475639650877499</v>
       </c>
       <c r="J53">
-        <v>3990.42645290581</v>
+        <v>3.99042645290581</v>
       </c>
       <c r="K53">
-        <v>1311.5897479554101</v>
+        <v>1.3115897479554099</v>
       </c>
       <c r="L53">
-        <v>14354.2848697394</v>
+        <v>14.3542848697394</v>
       </c>
       <c r="M53">
-        <v>4718.0252778928098</v>
+        <v>4.71802527789281</v>
       </c>
       <c r="N53">
-        <v>20203.361002004</v>
+        <v>20.203361002004002</v>
       </c>
       <c r="O53">
-        <v>6640.5236325492197</v>
+        <v>6.6405236325492201</v>
       </c>
       <c r="P53">
-        <v>11880.0006680026</v>
+        <v>11.8800006680026</v>
       </c>
       <c r="Q53">
-        <v>3904.76738908675</v>
+        <v>3.90476738908675</v>
       </c>
       <c r="R53">
-        <v>1251.3491612903199</v>
+        <v>1.25134916129032</v>
       </c>
       <c r="S53">
-        <v>411.29857934503002</v>
+        <v>0.41129857934503</v>
       </c>
       <c r="T53">
-        <v>8191.6752304609199</v>
+        <v>8.1916752304609197</v>
       </c>
       <c r="U53">
-        <v>2692.4734430398998</v>
+        <v>2.6924734430399</v>
       </c>
       <c r="V53">
-        <v>3055.7187096774101</v>
+        <v>3.0557187096774099</v>
       </c>
       <c r="W53">
-        <v>1004.36616976863</v>
+        <v>1.0043661697686299</v>
       </c>
       <c r="X53">
-        <v>3485.0590322580601</v>
+        <v>3.4850590322580599</v>
       </c>
       <c r="Y53">
-        <v>1145.4835095132501</v>
+        <v>1.1454835095132501</v>
       </c>
       <c r="Z53" s="4"/>
       <c r="AA53" s="4"/>
@@ -6958,76 +6958,76 @@
         <v>0.53125</v>
       </c>
       <c r="B54">
-        <v>13390.410441010999</v>
+        <v>13.390410441010999</v>
       </c>
       <c r="C54">
-        <v>4401.21507378142</v>
+        <v>4.4012150737814197</v>
       </c>
       <c r="D54">
-        <v>22894.777231363401</v>
+        <v>22.894777231363399</v>
       </c>
       <c r="E54">
-        <v>7525.1493675601096</v>
+        <v>7.5251493675601102</v>
       </c>
       <c r="F54">
-        <v>2726.1582306548498</v>
+        <v>2.7261582306548502</v>
       </c>
       <c r="G54">
-        <v>896.04487861878397</v>
+        <v>0.89604487861878401</v>
       </c>
       <c r="H54">
-        <v>9089.1398797595193</v>
+        <v>9.0891398797595198</v>
       </c>
       <c r="I54">
-        <v>2987.4558082242702</v>
+        <v>2.9874558082242699</v>
       </c>
       <c r="J54">
-        <v>4044.4322244488899</v>
+        <v>4.0444322244488902</v>
       </c>
       <c r="K54">
-        <v>1329.34058664954</v>
+        <v>1.32934058664954</v>
       </c>
       <c r="L54">
-        <v>14548.553386773499</v>
+        <v>14.5485533867735</v>
       </c>
       <c r="M54">
-        <v>4781.8782515785797</v>
+        <v>4.78187825157858</v>
       </c>
       <c r="N54">
-        <v>20476.789947895701</v>
+        <v>20.4767899478957</v>
       </c>
       <c r="O54">
-        <v>6730.3953809596596</v>
+        <v>6.7303953809596599</v>
       </c>
       <c r="P54">
-        <v>12040.7826319305</v>
+        <v>12.040782631930499</v>
       </c>
       <c r="Q54">
-        <v>3957.6138650292801</v>
+        <v>3.95761386502928</v>
       </c>
       <c r="R54">
-        <v>1160.0098064516101</v>
+        <v>1.16000980645161</v>
       </c>
       <c r="S54">
-        <v>381.27678523225399</v>
+        <v>0.381276785232254</v>
       </c>
       <c r="T54">
-        <v>8302.5400080160307</v>
+        <v>8.3025400080160292</v>
       </c>
       <c r="U54">
-        <v>2728.9129332464599</v>
+        <v>2.7289129332464599</v>
       </c>
       <c r="V54">
-        <v>2832.6735483870898</v>
+        <v>2.8326735483870902</v>
       </c>
       <c r="W54">
-        <v>931.05477051544801</v>
+        <v>0.93105477051544805</v>
       </c>
       <c r="X54">
-        <v>3230.6751612903199</v>
+        <v>3.23067516129032</v>
       </c>
       <c r="Y54">
-        <v>1061.8715745122799</v>
+        <v>1.06187157451228</v>
       </c>
       <c r="Z54" s="4"/>
       <c r="AA54" s="4"/>
@@ -7082,76 +7082,76 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="B55">
-        <v>13301.209278427799</v>
+        <v>13.3012092784278</v>
       </c>
       <c r="C55">
-        <v>4371.8960694768402</v>
+        <v>4.3718960694768398</v>
       </c>
       <c r="D55">
-        <v>22549.6454349167</v>
+        <v>22.549645434916702</v>
       </c>
       <c r="E55">
-        <v>7411.7100318762596</v>
+        <v>7.4117100318762601</v>
       </c>
       <c r="F55">
-        <v>2636.8527513090598</v>
+        <v>2.6368527513090601</v>
       </c>
       <c r="G55">
-        <v>866.69158705244399</v>
+        <v>0.86669158705244398</v>
       </c>
       <c r="H55">
-        <v>9048.6837675350598</v>
+        <v>9.04868376753506</v>
       </c>
       <c r="I55">
-        <v>2974.1585271787599</v>
+        <v>2.9741585271787598</v>
       </c>
       <c r="J55">
-        <v>4026.4303006012001</v>
+        <v>4.0264303006012003</v>
       </c>
       <c r="K55">
-        <v>1323.4236404181599</v>
+        <v>1.3234236404181601</v>
       </c>
       <c r="L55">
-        <v>14483.7972144288</v>
+        <v>14.483797214428799</v>
       </c>
       <c r="M55">
-        <v>4760.59392701665</v>
+        <v>4.7605939270166502</v>
       </c>
       <c r="N55">
-        <v>20385.646965931799</v>
+        <v>20.385646965931802</v>
       </c>
       <c r="O55">
-        <v>6700.4381314895199</v>
+        <v>6.7004381314895198</v>
       </c>
       <c r="P55">
-        <v>11987.1886439545</v>
+        <v>11.9871886439545</v>
       </c>
       <c r="Q55">
-        <v>3939.99837304843</v>
+        <v>3.93999837304843</v>
       </c>
       <c r="R55">
-        <v>1105.20619354838</v>
+        <v>1.1052061935483799</v>
       </c>
       <c r="S55">
-        <v>363.26370876458901</v>
+        <v>0.36326370876458902</v>
       </c>
       <c r="T55">
-        <v>8265.5850821643198</v>
+        <v>8.2655850821643195</v>
       </c>
       <c r="U55">
-        <v>2716.7664365109399</v>
+        <v>2.7167664365109401</v>
       </c>
       <c r="V55">
-        <v>2698.8464516129002</v>
+        <v>2.6988464516129</v>
       </c>
       <c r="W55">
-        <v>887.06793096353601</v>
+        <v>0.88706793096353698</v>
       </c>
       <c r="X55">
-        <v>3078.0448387096699</v>
+        <v>3.0780448387096699</v>
       </c>
       <c r="Y55">
-        <v>1011.7044135117</v>
+        <v>1.0117044135116999</v>
       </c>
       <c r="Z55" s="4"/>
       <c r="AA55" s="4"/>
@@ -7206,76 +7206,76 @@
         <v>0.55208333333333304</v>
       </c>
       <c r="B56">
-        <v>13050.7213160514</v>
+        <v>13.0507213160514</v>
       </c>
       <c r="C56">
-        <v>4289.5646577050802</v>
+        <v>4.2895646577050801</v>
       </c>
       <c r="D56">
-        <v>22038.234334000801</v>
+        <v>22.038234334000801</v>
       </c>
       <c r="E56">
-        <v>7243.6173317931598</v>
+        <v>7.2436173317931596</v>
       </c>
       <c r="F56">
-        <v>2580.68940994892</v>
+        <v>2.5806894099489202</v>
       </c>
       <c r="G56">
-        <v>848.23158945363195</v>
+        <v>0.84823158945363197</v>
       </c>
       <c r="H56">
-        <v>8880.1166332665307</v>
+        <v>8.88011663326653</v>
       </c>
       <c r="I56">
-        <v>2918.7531894891399</v>
+        <v>2.9187531894891401</v>
       </c>
       <c r="J56">
-        <v>3951.4222845691302</v>
+        <v>3.95142228456913</v>
       </c>
       <c r="K56">
-        <v>1298.76969778742</v>
+        <v>1.2987696977874199</v>
       </c>
       <c r="L56">
-        <v>14213.9798296593</v>
+        <v>14.2139798296593</v>
       </c>
       <c r="M56">
-        <v>4671.9092413419803</v>
+        <v>4.6719092413419796</v>
       </c>
       <c r="N56">
-        <v>20005.884541082101</v>
+        <v>20.0058845410821</v>
       </c>
       <c r="O56">
-        <v>6575.6162586972396</v>
+        <v>6.5756162586972398</v>
       </c>
       <c r="P56">
-        <v>11763.880360721399</v>
+        <v>11.7638803607214</v>
       </c>
       <c r="Q56">
-        <v>3866.6004897949201</v>
+        <v>3.8666004897949202</v>
       </c>
       <c r="R56">
-        <v>1080.0878709677399</v>
+        <v>1.0800878709677399</v>
       </c>
       <c r="S56">
-        <v>355.00771538357498</v>
+        <v>0.35500771538357501</v>
       </c>
       <c r="T56">
-        <v>8111.6062244488903</v>
+        <v>8.1116062244488898</v>
       </c>
       <c r="U56">
-        <v>2666.1560334462802</v>
+        <v>2.6661560334462799</v>
       </c>
       <c r="V56">
-        <v>2637.50903225806</v>
+        <v>2.6375090322580599</v>
       </c>
       <c r="W56">
-        <v>866.90729616891099</v>
+        <v>0.86690729616891105</v>
       </c>
       <c r="X56">
-        <v>3008.0892741935399</v>
+        <v>3.0080892741935399</v>
       </c>
       <c r="Y56">
-        <v>988.71113138644205</v>
+        <v>0.98871113138644195</v>
       </c>
       <c r="Z56" s="4"/>
       <c r="AA56" s="4"/>
@@ -7330,76 +7330,76 @@
         <v>0.5625</v>
       </c>
       <c r="B57">
-        <v>12699.4429639925</v>
+        <v>12.6994429639925</v>
       </c>
       <c r="C57">
-        <v>4174.1050468898802</v>
+        <v>4.1741050468898804</v>
       </c>
       <c r="D57">
-        <v>21404.3245514341</v>
+        <v>21.404324551434101</v>
       </c>
       <c r="E57">
-        <v>7035.2612621461003</v>
+        <v>7.0352612621460997</v>
       </c>
       <c r="F57">
-        <v>2548.2605131230198</v>
+        <v>2.54826051312302</v>
       </c>
       <c r="G57">
-        <v>837.57272651846995</v>
+        <v>0.83757272651847003</v>
       </c>
       <c r="H57">
-        <v>8630.6372745490899</v>
+        <v>8.6306372745491</v>
       </c>
       <c r="I57">
-        <v>2836.7532897085098</v>
+        <v>2.8367532897085099</v>
       </c>
       <c r="J57">
-        <v>3840.4104208416802</v>
+        <v>3.8404104208416801</v>
       </c>
       <c r="K57">
-        <v>1262.2818626939199</v>
+        <v>1.2622818626939201</v>
       </c>
       <c r="L57">
-        <v>13814.650100200401</v>
+        <v>13.814650100200399</v>
       </c>
       <c r="M57">
-        <v>4540.6559065434603</v>
+        <v>4.54065590654346</v>
       </c>
       <c r="N57">
-        <v>19443.836152304601</v>
+        <v>19.443836152304598</v>
       </c>
       <c r="O57">
-        <v>6390.8798869646698</v>
+        <v>6.3908798869646697</v>
       </c>
       <c r="P57">
-        <v>11433.3841015364</v>
+        <v>11.433384101536401</v>
       </c>
       <c r="Q57">
-        <v>3757.9716225797301</v>
+        <v>3.7579716225797299</v>
       </c>
       <c r="R57">
-        <v>1075.5209032258001</v>
+        <v>1.0755209032258</v>
       </c>
       <c r="S57">
-        <v>353.50662567793597</v>
+        <v>0.353506625677936</v>
       </c>
       <c r="T57">
-        <v>7883.71751503006</v>
+        <v>7.8837175150300602</v>
       </c>
       <c r="U57">
-        <v>2591.2526369105799</v>
+        <v>2.5912526369105802</v>
       </c>
       <c r="V57">
-        <v>2626.3567741935399</v>
+        <v>2.6263567741935399</v>
       </c>
       <c r="W57">
-        <v>863.241726206252</v>
+        <v>0.86324172620625195</v>
       </c>
       <c r="X57">
-        <v>2995.3700806451602</v>
+        <v>2.9953700806451602</v>
       </c>
       <c r="Y57">
-        <v>984.53053463639299</v>
+        <v>0.98453053463639395</v>
       </c>
       <c r="Z57" s="4"/>
       <c r="AA57" s="4"/>
@@ -7454,76 +7454,76 @@
         <v>0.57291666666666696</v>
       </c>
       <c r="B58">
-        <v>12325.349837093499</v>
+        <v>12.3253498370935</v>
       </c>
       <c r="C58">
-        <v>4051.14658222153</v>
+        <v>4.0511465822215298</v>
       </c>
       <c r="D58">
-        <v>20710.178727044698</v>
+        <v>20.710178727044699</v>
       </c>
       <c r="E58">
-        <v>6807.1065629930099</v>
+        <v>6.8071065629930096</v>
       </c>
       <c r="F58">
-        <v>2527.9775863016298</v>
+        <v>2.5279775863016298</v>
       </c>
       <c r="G58">
-        <v>830.906050865775</v>
+        <v>0.83090605086577496</v>
       </c>
       <c r="H58">
-        <v>8360.9298597194393</v>
+        <v>8.3609298597194392</v>
       </c>
       <c r="I58">
-        <v>2748.1047494051199</v>
+        <v>2.7481047494051198</v>
       </c>
       <c r="J58">
-        <v>3720.3975951903799</v>
+        <v>3.7203975951903798</v>
       </c>
       <c r="K58">
-        <v>1222.83555448474</v>
+        <v>1.22283555448474</v>
       </c>
       <c r="L58">
-        <v>13382.942284569101</v>
+        <v>13.382942284569101</v>
       </c>
       <c r="M58">
-        <v>4398.7604094639701</v>
+        <v>4.3987604094639696</v>
       </c>
       <c r="N58">
-        <v>18836.216272545</v>
+        <v>18.836216272544998</v>
       </c>
       <c r="O58">
-        <v>6191.1648904970198</v>
+        <v>6.1911648904970198</v>
       </c>
       <c r="P58">
-        <v>11076.090848363299</v>
+        <v>11.0760908483633</v>
       </c>
       <c r="Q58">
-        <v>3640.5350093741099</v>
+        <v>3.6405350093741098</v>
       </c>
       <c r="R58">
-        <v>1080.0878709677399</v>
+        <v>1.0800878709677399</v>
       </c>
       <c r="S58">
-        <v>355.00771538357498</v>
+        <v>0.35500771538357501</v>
       </c>
       <c r="T58">
-        <v>7637.3513426853697</v>
+        <v>7.6373513426853696</v>
       </c>
       <c r="U58">
-        <v>2510.2759920071298</v>
+        <v>2.5102759920071298</v>
       </c>
       <c r="V58">
-        <v>2637.50903225806</v>
+        <v>2.6375090322580599</v>
       </c>
       <c r="W58">
-        <v>866.90729616891099</v>
+        <v>0.86690729616891105</v>
       </c>
       <c r="X58">
-        <v>3008.0892741935399</v>
+        <v>3.0080892741935399</v>
       </c>
       <c r="Y58">
-        <v>988.71113138644205</v>
+        <v>0.98871113138644195</v>
       </c>
       <c r="Z58" s="4"/>
       <c r="AA58" s="4"/>
@@ -7578,76 +7578,76 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="B59">
-        <v>11970.7783342814</v>
+        <v>11.9707783342814</v>
       </c>
       <c r="C59">
-        <v>3934.6045650978199</v>
+        <v>3.9346045650978199</v>
       </c>
       <c r="D59">
-        <v>19995.383124793101</v>
+        <v>19.995383124793101</v>
       </c>
       <c r="E59">
-        <v>6572.1646100811604</v>
+        <v>6.5721646100811597</v>
       </c>
       <c r="F59">
-        <v>2510.83875743422</v>
+        <v>2.5108387574342199</v>
       </c>
       <c r="G59">
-        <v>825.27279023567598</v>
+        <v>0.82527279023567601</v>
       </c>
       <c r="H59">
-        <v>8104.70781563126</v>
+        <v>8.1047078156312597</v>
       </c>
       <c r="I59">
-        <v>2663.8886361169002</v>
+        <v>2.6638886361169001</v>
       </c>
       <c r="J59">
-        <v>3606.3854108216401</v>
+        <v>3.6063854108216402</v>
       </c>
       <c r="K59">
-        <v>1185.36156168601</v>
+        <v>1.18536156168601</v>
       </c>
       <c r="L59">
-        <v>12972.8198597194</v>
+        <v>12.972819859719401</v>
       </c>
       <c r="M59">
-        <v>4263.95968723846</v>
+        <v>4.2639596872384598</v>
       </c>
       <c r="N59">
-        <v>18258.977386773498</v>
+        <v>18.258977386773498</v>
       </c>
       <c r="O59">
-        <v>6001.4356438527602</v>
+        <v>6.0014356438527603</v>
       </c>
       <c r="P59">
-        <v>10736.662257849001</v>
+        <v>10.736662257849</v>
       </c>
       <c r="Q59">
-        <v>3528.9702268287801</v>
+        <v>3.5289702268287799</v>
       </c>
       <c r="R59">
-        <v>1085.79658064516</v>
+        <v>1.0857965806451599</v>
       </c>
       <c r="S59">
-        <v>356.88407751562403</v>
+        <v>0.35688407751562401</v>
       </c>
       <c r="T59">
-        <v>7403.3034789579096</v>
+        <v>7.40330347895791</v>
       </c>
       <c r="U59">
-        <v>2433.3481793488399</v>
+        <v>2.4333481793488398</v>
       </c>
       <c r="V59">
-        <v>2651.4493548386999</v>
+        <v>2.6514493548387001</v>
       </c>
       <c r="W59">
-        <v>871.48925862223496</v>
+        <v>0.87148925862223503</v>
       </c>
       <c r="X59">
-        <v>3023.9882661290299</v>
+        <v>3.02398826612903</v>
       </c>
       <c r="Y59">
-        <v>993.93687732400201</v>
+        <v>0.99393687732400204</v>
       </c>
       <c r="Z59" s="4"/>
       <c r="AA59" s="4"/>
@@ -7702,76 +7702,76 @@
         <v>0.59375</v>
       </c>
       <c r="B60">
-        <v>11653.207660288301</v>
+        <v>11.653207660288301</v>
       </c>
       <c r="C60">
-        <v>3830.2241322853401</v>
+        <v>3.8302241322853399</v>
       </c>
       <c r="D60">
-        <v>19320.992297889399</v>
+        <v>19.320992297889401</v>
       </c>
       <c r="E60">
-        <v>6350.5030645995002</v>
+        <v>6.3505030645994998</v>
       </c>
       <c r="F60">
-        <v>2494.6632454424898</v>
+        <v>2.49466324544249</v>
       </c>
       <c r="G60">
-        <v>819.95615655086601</v>
+        <v>0.81995615655086596</v>
       </c>
       <c r="H60">
-        <v>7875.4565130260498</v>
+        <v>7.8754565130260499</v>
       </c>
       <c r="I60">
-        <v>2588.5373768590098</v>
+        <v>2.5885373768590099</v>
       </c>
       <c r="J60">
-        <v>3504.37450901803</v>
+        <v>3.5043745090180298</v>
       </c>
       <c r="K60">
-        <v>1151.8321997082101</v>
+        <v>1.1518321997082099</v>
       </c>
       <c r="L60">
-        <v>12605.8682164328</v>
+        <v>12.6058682164328</v>
       </c>
       <c r="M60">
-        <v>4143.3485147209003</v>
+        <v>4.1433485147209002</v>
       </c>
       <c r="N60">
-        <v>17742.500488977901</v>
+        <v>17.7425004889779</v>
       </c>
       <c r="O60">
-        <v>5831.6778968552599</v>
+        <v>5.8316778968552603</v>
       </c>
       <c r="P60">
-        <v>10432.962992651899</v>
+        <v>10.4329629926519</v>
       </c>
       <c r="Q60">
-        <v>3429.1491056039999</v>
+        <v>3.429149105604</v>
       </c>
       <c r="R60">
-        <v>1090.3635483870901</v>
+        <v>1.0903635483870899</v>
       </c>
       <c r="S60">
-        <v>358.38516722126298</v>
+        <v>0.35838516722126201</v>
       </c>
       <c r="T60">
-        <v>7193.8922324649302</v>
+        <v>7.1938922324649299</v>
       </c>
       <c r="U60">
-        <v>2364.5180311809099</v>
+        <v>2.3645180311809</v>
       </c>
       <c r="V60">
-        <v>2662.60161290322</v>
+        <v>2.6626016129032202</v>
       </c>
       <c r="W60">
-        <v>875.15482858489395</v>
+        <v>0.87515482858489402</v>
       </c>
       <c r="X60">
-        <v>3036.70745967741</v>
+        <v>3.0367074596774102</v>
       </c>
       <c r="Y60">
-        <v>998.11747407405096</v>
+        <v>0.99811747407405105</v>
       </c>
       <c r="Z60" s="4"/>
       <c r="AA60" s="4"/>
@@ -7826,76 +7826,76 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="B61">
-        <v>11362.5365998448</v>
+        <v>11.3625365998448</v>
       </c>
       <c r="C61">
-        <v>3734.68517488208</v>
+        <v>3.7346851748820802</v>
       </c>
       <c r="D61">
-        <v>18735.803968766599</v>
+        <v>18.7358039687666</v>
       </c>
       <c r="E61">
-        <v>6158.16096228064</v>
+        <v>6.1581609622806397</v>
       </c>
       <c r="F61">
-        <v>2476.9915215107599</v>
+        <v>2.4769915215107599</v>
       </c>
       <c r="G61">
-        <v>814.14774178339496</v>
+        <v>0.814147741783395</v>
       </c>
       <c r="H61">
-        <v>7666.4332665330603</v>
+        <v>7.6664332665330601</v>
       </c>
       <c r="I61">
-        <v>2519.83475812389</v>
+        <v>2.5198347581238898</v>
       </c>
       <c r="J61">
-        <v>3411.3645691382699</v>
+        <v>3.4113645691382701</v>
       </c>
       <c r="K61">
-        <v>1121.2613108460901</v>
+        <v>1.12126131084609</v>
       </c>
       <c r="L61">
-        <v>12271.294659318601</v>
+        <v>12.271294659318601</v>
       </c>
       <c r="M61">
-        <v>4033.3795044843</v>
+        <v>4.0333795044842997</v>
       </c>
       <c r="N61">
-        <v>17271.595082164298</v>
+        <v>17.2715950821643</v>
       </c>
       <c r="O61">
-        <v>5676.8987745928298</v>
+        <v>5.6768987745928303</v>
       </c>
       <c r="P61">
-        <v>10156.0607214428</v>
+        <v>10.156060721442801</v>
       </c>
       <c r="Q61">
-        <v>3338.13573036965</v>
+        <v>3.3381357303696499</v>
       </c>
       <c r="R61">
-        <v>1092.6470322580601</v>
+        <v>1.0926470322580599</v>
       </c>
       <c r="S61">
-        <v>359.13571207408199</v>
+        <v>0.35913571207408201</v>
       </c>
       <c r="T61">
-        <v>7002.9584488977898</v>
+        <v>7.0029584488977896</v>
       </c>
       <c r="U61">
-        <v>2301.7611313807301</v>
+        <v>2.3017611313807298</v>
       </c>
       <c r="V61">
-        <v>2668.1777419354798</v>
+        <v>2.6681777419354802</v>
       </c>
       <c r="W61">
-        <v>876.98761356622401</v>
+        <v>0.87698761356622401</v>
       </c>
       <c r="X61">
-        <v>3043.0670564516099</v>
+        <v>3.0430670564516098</v>
       </c>
       <c r="Y61">
-        <v>1000.20777244907</v>
+        <v>1.0002077724490701</v>
       </c>
       <c r="Z61" s="4"/>
       <c r="AA61" s="4"/>
@@ -7950,76 +7950,76 @@
         <v>0.61458333333333304</v>
       </c>
       <c r="B62">
-        <v>11080.605141767401</v>
+        <v>11.0806051417674</v>
       </c>
       <c r="C62">
-        <v>3642.0187858621298</v>
+        <v>3.6420187858621298</v>
       </c>
       <c r="D62">
-        <v>18271.4155335096</v>
+        <v>18.2714155335096</v>
       </c>
       <c r="E62">
-        <v>6005.5238649827797</v>
+        <v>6.0055238649827798</v>
       </c>
       <c r="F62">
-        <v>2458.2294070398798</v>
+        <v>2.4582294070398798</v>
       </c>
       <c r="G62">
-        <v>807.980932977272</v>
+        <v>0.80798093297727203</v>
       </c>
       <c r="H62">
-        <v>7464.1527054108201</v>
+        <v>7.4641527054108199</v>
       </c>
       <c r="I62">
-        <v>2453.3483528963402</v>
+        <v>2.4533483528963398</v>
       </c>
       <c r="J62">
-        <v>3321.35494989979</v>
+        <v>3.3213549498997899</v>
       </c>
       <c r="K62">
-        <v>1091.6765796892</v>
+        <v>1.0916765796892001</v>
       </c>
       <c r="L62">
-        <v>11947.5137975951</v>
+        <v>11.9475137975951</v>
       </c>
       <c r="M62">
-        <v>3926.9578816746898</v>
+        <v>3.92695788167469</v>
       </c>
       <c r="N62">
-        <v>16815.880172344601</v>
+        <v>16.815880172344599</v>
       </c>
       <c r="O62">
-        <v>5527.1125272421004</v>
+        <v>5.5271125272420996</v>
       </c>
       <c r="P62">
-        <v>9888.0907815631199</v>
+        <v>9.88809078156312</v>
       </c>
       <c r="Q62">
-        <v>3250.0582704654398</v>
+        <v>3.2500582704654399</v>
       </c>
       <c r="R62">
-        <v>1093.7887741935399</v>
+        <v>1.0937887741935399</v>
       </c>
       <c r="S62">
-        <v>359.51098450049199</v>
+        <v>0.35951098450049201</v>
       </c>
       <c r="T62">
-        <v>6818.18381963927</v>
+        <v>6.8181838196392697</v>
       </c>
       <c r="U62">
-        <v>2241.02864770313</v>
+        <v>2.2410286477031298</v>
       </c>
       <c r="V62">
-        <v>2670.9658064516102</v>
+        <v>2.6709658064516102</v>
       </c>
       <c r="W62">
-        <v>877.90400605688797</v>
+        <v>0.87790400605688801</v>
       </c>
       <c r="X62">
-        <v>3046.2468548387001</v>
+        <v>3.0462468548386998</v>
       </c>
       <c r="Y62">
-        <v>1001.25292163658</v>
+        <v>1.00125292163658</v>
       </c>
       <c r="Z62" s="4"/>
       <c r="AA62" s="4"/>
@@ -8074,76 +8074,76 @@
         <v>0.625</v>
       </c>
       <c r="B63">
-        <v>10816.8336948736</v>
+        <v>10.816833694873599</v>
       </c>
       <c r="C63">
-        <v>3555.3213038681101</v>
+        <v>3.55532130386811</v>
       </c>
       <c r="D63">
-        <v>17976.3953653223</v>
+        <v>17.976395365322301</v>
       </c>
       <c r="E63">
-        <v>5908.5554249924398</v>
+        <v>5.9085554249924401</v>
       </c>
       <c r="F63">
-        <v>2439.0614711681401</v>
+        <v>2.4390614711681402</v>
       </c>
       <c r="G63">
-        <v>801.68073712714204</v>
+        <v>0.80168073712714205</v>
       </c>
       <c r="H63">
-        <v>7275.3575150300603</v>
+        <v>7.27535751503006</v>
       </c>
       <c r="I63">
-        <v>2391.2943746839701</v>
+        <v>2.3912943746839699</v>
       </c>
       <c r="J63">
-        <v>3237.3459719438802</v>
+        <v>3.23734597194388</v>
       </c>
       <c r="K63">
-        <v>1064.0641639427699</v>
+        <v>1.0640641639427699</v>
       </c>
       <c r="L63">
-        <v>11645.3183266533</v>
+        <v>11.6453183266533</v>
       </c>
       <c r="M63">
-        <v>3827.6310337190498</v>
+        <v>3.82763103371905</v>
       </c>
       <c r="N63">
-        <v>16390.546256513</v>
+        <v>16.390546256513002</v>
       </c>
       <c r="O63">
-        <v>5387.3120297147498</v>
+        <v>5.3873120297147503</v>
       </c>
       <c r="P63">
-        <v>9637.9855043420102</v>
+        <v>9.6379855043420104</v>
       </c>
       <c r="Q63">
-        <v>3167.8526412215101</v>
+        <v>3.16785264122151</v>
       </c>
       <c r="R63">
-        <v>1093.7887741935399</v>
+        <v>1.0937887741935399</v>
       </c>
       <c r="S63">
-        <v>359.51098450049199</v>
+        <v>0.35951098450049201</v>
       </c>
       <c r="T63">
-        <v>6645.7274989979896</v>
+        <v>6.6457274989979904</v>
       </c>
       <c r="U63">
-        <v>2184.34499627072</v>
+        <v>2.18434499627072</v>
       </c>
       <c r="V63">
-        <v>2670.9658064516102</v>
+        <v>2.6709658064516102</v>
       </c>
       <c r="W63">
-        <v>877.90400605688797</v>
+        <v>0.87790400605688801</v>
       </c>
       <c r="X63">
-        <v>3046.2468548387001</v>
+        <v>3.0462468548386998</v>
       </c>
       <c r="Y63">
-        <v>1001.25292163658</v>
+        <v>1.00125292163658</v>
       </c>
       <c r="Z63" s="4"/>
       <c r="AA63" s="4"/>
@@ -8198,76 +8198,76 @@
         <v>0.63541666666666696</v>
       </c>
       <c r="B64">
-        <v>10590.743883250299</v>
+        <v>10.590743883250299</v>
       </c>
       <c r="C64">
-        <v>3481.0091764446602</v>
+        <v>3.48100917644466</v>
       </c>
       <c r="D64">
-        <v>17830.607428585401</v>
+        <v>17.830607428585399</v>
       </c>
       <c r="E64">
-        <v>5860.6372474602003</v>
+        <v>5.8606372474602004</v>
       </c>
       <c r="F64">
-        <v>2422.6318118495001</v>
+        <v>2.4226318118495</v>
       </c>
       <c r="G64">
-        <v>796.28056925560202</v>
+        <v>0.79628056925560198</v>
       </c>
       <c r="H64">
-        <v>7113.5330661322596</v>
+        <v>7.11353306613226</v>
       </c>
       <c r="I64">
-        <v>2338.1052505019302</v>
+        <v>2.33810525050193</v>
       </c>
       <c r="J64">
-        <v>3165.3382765531001</v>
+        <v>3.1653382765531002</v>
       </c>
       <c r="K64">
-        <v>1040.39637901726</v>
+        <v>1.0403963790172599</v>
       </c>
       <c r="L64">
-        <v>11386.293637274501</v>
+        <v>11.3862936372745</v>
       </c>
       <c r="M64">
-        <v>3742.4937354713602</v>
+        <v>3.7424937354713599</v>
       </c>
       <c r="N64">
-        <v>16025.974328657299</v>
+        <v>16.025974328657298</v>
       </c>
       <c r="O64">
-        <v>5267.4830318341601</v>
+        <v>5.2674830318341597</v>
       </c>
       <c r="P64">
-        <v>9423.6095524381999</v>
+        <v>9.4236095524382009</v>
       </c>
       <c r="Q64">
-        <v>3097.39067329813</v>
+        <v>3.09739067329813</v>
       </c>
       <c r="R64">
-        <v>1093.7887741935399</v>
+        <v>1.0937887741935399</v>
       </c>
       <c r="S64">
-        <v>359.51098450049199</v>
+        <v>0.35951098450049201</v>
       </c>
       <c r="T64">
-        <v>6497.9077955911798</v>
+        <v>6.4979077955911801</v>
       </c>
       <c r="U64">
-        <v>2135.7590093286399</v>
+        <v>2.1357590093286398</v>
       </c>
       <c r="V64">
-        <v>2670.9658064516102</v>
+        <v>2.6709658064516102</v>
       </c>
       <c r="W64">
-        <v>877.90400605688797</v>
+        <v>0.87790400605688801</v>
       </c>
       <c r="X64">
-        <v>3046.2468548387001</v>
+        <v>3.0462468548386998</v>
       </c>
       <c r="Y64">
-        <v>1001.25292163658</v>
+        <v>1.00125292163658</v>
       </c>
       <c r="Z64" s="4"/>
       <c r="AA64" s="4"/>
@@ -8322,76 +8322,76 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="B65">
-        <v>10404.378126252501</v>
+        <v>10.404378126252499</v>
       </c>
       <c r="C65">
-        <v>3419.7537143698401</v>
+        <v>3.4197537143698402</v>
       </c>
       <c r="D65">
-        <v>17764.791719450299</v>
+        <v>17.764791719450301</v>
       </c>
       <c r="E65">
-        <v>5839.0046699964096</v>
+        <v>5.8390046699964104</v>
       </c>
       <c r="F65">
-        <v>2414.2653081162298</v>
+        <v>2.4142653081162302</v>
       </c>
       <c r="G65">
-        <v>793.53063246255601</v>
+        <v>0.79353063246255595</v>
       </c>
       <c r="H65">
-        <v>6978.6793587174297</v>
+        <v>6.9786793587174296</v>
       </c>
       <c r="I65">
-        <v>2293.78098035024</v>
+        <v>2.29378098035024</v>
       </c>
       <c r="J65">
-        <v>3105.3318637274501</v>
+        <v>3.1053318637274501</v>
       </c>
       <c r="K65">
-        <v>1020.67322491266</v>
+        <v>1.02067322491266</v>
       </c>
       <c r="L65">
-        <v>11170.4397294589</v>
+        <v>11.1704397294589</v>
       </c>
       <c r="M65">
-        <v>3671.5459869316201</v>
+        <v>3.67154598693162</v>
       </c>
       <c r="N65">
-        <v>15722.164388777501</v>
+        <v>15.7221643887775</v>
       </c>
       <c r="O65">
-        <v>5167.6255336003296</v>
+        <v>5.1676255336003303</v>
       </c>
       <c r="P65">
-        <v>9244.9629258516998</v>
+        <v>9.2449629258517003</v>
       </c>
       <c r="Q65">
-        <v>3038.6723666953299</v>
+        <v>3.0386723666953301</v>
       </c>
       <c r="R65">
-        <v>1097.2139999999999</v>
+        <v>1.0972139999999999</v>
       </c>
       <c r="S65">
-        <v>360.636801779721</v>
+        <v>0.36063680177972102</v>
       </c>
       <c r="T65">
-        <v>6374.7247094188297</v>
+        <v>6.37472470941883</v>
       </c>
       <c r="U65">
-        <v>2095.2706868769101</v>
+        <v>2.0952706868769102</v>
       </c>
       <c r="V65">
-        <v>2679.3299999999899</v>
+        <v>2.67932999999999</v>
       </c>
       <c r="W65">
-        <v>880.65318352888301</v>
+        <v>0.880653183528883</v>
       </c>
       <c r="X65">
-        <v>3055.7862500000001</v>
+        <v>3.0557862500000001</v>
       </c>
       <c r="Y65">
-        <v>1004.38836919912</v>
+        <v>1.00438836919912</v>
       </c>
       <c r="Z65" s="4"/>
       <c r="AA65" s="4"/>
@@ -8446,76 +8446,76 @@
         <v>0.65625</v>
       </c>
       <c r="B66">
-        <v>10306.880887322999</v>
+        <v>10.306880887323</v>
       </c>
       <c r="C66">
-        <v>3387.7079216348902</v>
+        <v>3.38770792163489</v>
       </c>
       <c r="D66">
-        <v>17773.716544500301</v>
+        <v>17.773716544500299</v>
       </c>
       <c r="E66">
-        <v>5841.9381181318504</v>
+        <v>5.8419381181318499</v>
       </c>
       <c r="F66">
-        <v>2422.7096846919599</v>
+        <v>2.4227096846919598</v>
       </c>
       <c r="G66">
-        <v>796.30616482114306</v>
+        <v>0.79630616482114303</v>
       </c>
       <c r="H66">
-        <v>6904.5098196392701</v>
+        <v>6.9045098196392702</v>
       </c>
       <c r="I66">
-        <v>2269.4026317668099</v>
+        <v>2.2694026317668099</v>
       </c>
       <c r="J66">
-        <v>3072.3283366733399</v>
+        <v>3.07232833667334</v>
       </c>
       <c r="K66">
-        <v>1009.82549015514</v>
+        <v>1.00982549015514</v>
       </c>
       <c r="L66">
-        <v>11051.720080160299</v>
+        <v>11.051720080160299</v>
       </c>
       <c r="M66">
-        <v>3632.5247252347599</v>
+        <v>3.6325247252347599</v>
       </c>
       <c r="N66">
-        <v>15555.0689218436</v>
+        <v>15.555068921843599</v>
       </c>
       <c r="O66">
-        <v>5112.70390957173</v>
+        <v>5.1127039095717297</v>
       </c>
       <c r="P66">
-        <v>9146.7072812291208</v>
+        <v>9.1467072812291192</v>
       </c>
       <c r="Q66">
-        <v>3006.37729806378</v>
+        <v>3.00637729806378</v>
       </c>
       <c r="R66">
-        <v>1107.4896774193501</v>
+        <v>1.1074896774193499</v>
       </c>
       <c r="S66">
-        <v>364.01425361740797</v>
+        <v>0.36401425361740802</v>
       </c>
       <c r="T66">
-        <v>6306.9740120240403</v>
+        <v>6.3069740120240398</v>
       </c>
       <c r="U66">
-        <v>2073.0021095284601</v>
+        <v>2.0730021095284599</v>
       </c>
       <c r="V66">
-        <v>2704.42258064516</v>
+        <v>2.7044225806451601</v>
       </c>
       <c r="W66">
-        <v>888.90071594486596</v>
+        <v>0.88890071594486597</v>
       </c>
       <c r="X66">
-        <v>3084.4044354838702</v>
+        <v>3.08440443548387</v>
       </c>
       <c r="Y66">
-        <v>1013.7947118867301</v>
+        <v>1.0137947118867301</v>
       </c>
       <c r="Z66" s="4"/>
       <c r="AA66" s="4"/>
@@ -8570,76 +8570,76 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="B67">
-        <v>10298.2521664619</v>
+        <v>10.2982521664619</v>
       </c>
       <c r="C67">
-        <v>3384.8717982398298</v>
+        <v>3.3848717982398302</v>
       </c>
       <c r="D67">
-        <v>17808.899901041499</v>
+        <v>17.808899901041499</v>
       </c>
       <c r="E67">
-        <v>5853.5023281937702</v>
+        <v>5.8535023281937697</v>
       </c>
       <c r="F67">
-        <v>2447.9649415766999</v>
+        <v>2.4479649415767</v>
       </c>
       <c r="G67">
-        <v>804.60716633136599</v>
+        <v>0.80460716633136597</v>
       </c>
       <c r="H67">
-        <v>6891.0244488977896</v>
+        <v>6.8910244488977899</v>
       </c>
       <c r="I67">
-        <v>2264.9702047516398</v>
+        <v>2.26497020475164</v>
       </c>
       <c r="J67">
-        <v>3066.3276953907798</v>
+        <v>3.0663276953907799</v>
       </c>
       <c r="K67">
-        <v>1007.85317474468</v>
+        <v>1.0078531747446799</v>
       </c>
       <c r="L67">
-        <v>11030.134689378699</v>
+        <v>11.0301346893787</v>
       </c>
       <c r="M67">
-        <v>3625.4299503807902</v>
+        <v>3.6254299503807901</v>
       </c>
       <c r="N67">
-        <v>15524.687927855701</v>
+        <v>15.5246879278557</v>
       </c>
       <c r="O67">
-        <v>5102.7181597483504</v>
+        <v>5.10271815974835</v>
       </c>
       <c r="P67">
-        <v>9128.8426185704702</v>
+        <v>9.1288426185704701</v>
       </c>
       <c r="Q67">
-        <v>3000.5054674035</v>
+        <v>3.0005054674034999</v>
       </c>
       <c r="R67">
-        <v>1124.6158064516101</v>
+        <v>1.1246158064516101</v>
       </c>
       <c r="S67">
-        <v>369.643340013554</v>
+        <v>0.36964334001355398</v>
       </c>
       <c r="T67">
-        <v>6294.6557034068101</v>
+        <v>6.2946557034068098</v>
       </c>
       <c r="U67">
-        <v>2068.9532772832899</v>
+        <v>2.0689532772832901</v>
       </c>
       <c r="V67">
-        <v>2746.24354838709</v>
+        <v>2.7462435483870902</v>
       </c>
       <c r="W67">
-        <v>902.64660330483798</v>
+        <v>0.90264660330483804</v>
       </c>
       <c r="X67">
-        <v>3132.1014112903199</v>
+        <v>3.13210141129032</v>
       </c>
       <c r="Y67">
-        <v>1029.4719496994101</v>
+        <v>1.02947194969941</v>
       </c>
       <c r="Z67" s="4"/>
       <c r="AA67" s="4"/>
@@ -8694,76 +8694,76 @@
         <v>0.67708333333333304</v>
       </c>
       <c r="B68">
-        <v>10410.8380288318</v>
+        <v>10.410838028831799</v>
       </c>
       <c r="C68">
-        <v>3421.8769816686699</v>
+        <v>3.42187698166867</v>
       </c>
       <c r="D68">
-        <v>17940.508915228002</v>
+        <v>17.940508915228001</v>
       </c>
       <c r="E68">
-        <v>5896.7601192551501</v>
+        <v>5.8967601192551502</v>
       </c>
       <c r="F68">
-        <v>2502.7345442497799</v>
+        <v>2.5027345442497801</v>
       </c>
       <c r="G68">
-        <v>822.60906417697095</v>
+        <v>0.82260906417697099</v>
       </c>
       <c r="H68">
-        <v>6958.45130260521</v>
+        <v>6.9584513026052104</v>
       </c>
       <c r="I68">
-        <v>2287.1323398274799</v>
+        <v>2.2871323398274801</v>
       </c>
       <c r="J68">
-        <v>3096.3309018036002</v>
+        <v>3.0963309018035998</v>
       </c>
       <c r="K68">
-        <v>1017.71475179698</v>
+        <v>1.01771475179698</v>
       </c>
       <c r="L68">
-        <v>11138.061643286501</v>
+        <v>11.1380616432865</v>
       </c>
       <c r="M68">
-        <v>3660.9038246506602</v>
+        <v>3.66090382465066</v>
       </c>
       <c r="N68">
-        <v>15676.592897795501</v>
+        <v>15.6765928977955</v>
       </c>
       <c r="O68">
-        <v>5152.6469088652602</v>
+        <v>5.1526469088652602</v>
       </c>
       <c r="P68">
-        <v>9218.1659318637194</v>
+        <v>9.2181659318637195</v>
       </c>
       <c r="Q68">
-        <v>3029.8646207049101</v>
+        <v>3.02986462070491</v>
       </c>
       <c r="R68">
-        <v>1155.44283870967</v>
+        <v>1.15544283870967</v>
       </c>
       <c r="S68">
-        <v>379.77569552661498</v>
+        <v>0.379775695526615</v>
       </c>
       <c r="T68">
-        <v>6356.2472464929797</v>
+        <v>6.3562472464929796</v>
       </c>
       <c r="U68">
-        <v>2089.1974385091598</v>
+        <v>2.0891974385091601</v>
       </c>
       <c r="V68">
-        <v>2821.5212903225802</v>
+        <v>2.8215212903225799</v>
       </c>
       <c r="W68">
-        <v>927.389200552788</v>
+        <v>0.92738920055278795</v>
       </c>
       <c r="X68">
-        <v>3217.9559677419302</v>
+        <v>3.21795596774193</v>
       </c>
       <c r="Y68">
-        <v>1057.69097776224</v>
+        <v>1.0576909777622401</v>
       </c>
       <c r="Z68" s="4"/>
       <c r="AA68" s="4"/>
@@ -8818,76 +8818,76 @@
         <v>0.6875</v>
       </c>
       <c r="B69">
-        <v>10664.1600985196</v>
+        <v>10.6641600985196</v>
       </c>
       <c r="C69">
-        <v>3505.1399194660498</v>
+        <v>3.5051399194660502</v>
       </c>
       <c r="D69">
-        <v>18244.5002420645</v>
+        <v>18.2445002420645</v>
       </c>
       <c r="E69">
-        <v>5996.67723649853</v>
+        <v>5.9966772364985301</v>
       </c>
       <c r="F69">
-        <v>2590.1625906651998</v>
+        <v>2.5901625906652002</v>
       </c>
       <c r="G69">
-        <v>851.34527338055705</v>
+        <v>0.85134527338055699</v>
       </c>
       <c r="H69">
-        <v>7120.2757515029998</v>
+        <v>7.1202757515029997</v>
       </c>
       <c r="I69">
-        <v>2340.3214640095198</v>
+        <v>2.34032146400952</v>
       </c>
       <c r="J69">
-        <v>3168.3385971943799</v>
+        <v>3.16833859719438</v>
       </c>
       <c r="K69">
-        <v>1041.3825367224899</v>
+        <v>1.04138253672249</v>
       </c>
       <c r="L69">
-        <v>11397.0863326653</v>
+        <v>11.3970863326653</v>
       </c>
       <c r="M69">
-        <v>3746.0411228983498</v>
+        <v>3.7460411228983501</v>
       </c>
       <c r="N69">
-        <v>16041.1648256513</v>
+        <v>16.0411648256513</v>
       </c>
       <c r="O69">
-        <v>5272.4759067458499</v>
+        <v>5.27247590674585</v>
       </c>
       <c r="P69">
-        <v>9432.5418837675297</v>
+        <v>9.4325418837675308</v>
       </c>
       <c r="Q69">
-        <v>3100.3265886282802</v>
+        <v>3.1003265886282798</v>
       </c>
       <c r="R69">
-        <v>1201.1125161290299</v>
+        <v>1.2011125161290299</v>
       </c>
       <c r="S69">
-        <v>394.78659258300303</v>
+        <v>0.39478659258300303</v>
       </c>
       <c r="T69">
-        <v>6504.0669498998004</v>
+        <v>6.5040669498997996</v>
       </c>
       <c r="U69">
-        <v>2137.78342545123</v>
+        <v>2.13778342545123</v>
       </c>
       <c r="V69">
-        <v>2933.0438709677401</v>
+        <v>2.9330438709677402</v>
       </c>
       <c r="W69">
-        <v>964.04490017938099</v>
+        <v>0.96404490017938105</v>
       </c>
       <c r="X69">
-        <v>3345.1479032257998</v>
+        <v>3.3451479032257998</v>
       </c>
       <c r="Y69">
-        <v>1099.4969452627199</v>
+        <v>1.0994969452627199</v>
       </c>
       <c r="Z69" s="4"/>
       <c r="AA69" s="4"/>
@@ -8942,76 +8942,76 @@
         <v>0.69791666666666696</v>
       </c>
       <c r="B70">
-        <v>11108.7244518714</v>
+        <v>11.108724451871399</v>
       </c>
       <c r="C70">
-        <v>3651.2611561419299</v>
+        <v>3.6512611561419299</v>
       </c>
       <c r="D70">
-        <v>18827.943952698599</v>
+        <v>18.8279439526986</v>
       </c>
       <c r="E70">
-        <v>6188.4459104505504</v>
+        <v>6.1884459104505503</v>
       </c>
       <c r="F70">
-        <v>2722.54672490141</v>
+        <v>2.7225467249014099</v>
       </c>
       <c r="G70">
-        <v>894.85783408186603</v>
+        <v>0.89485783408186603</v>
       </c>
       <c r="H70">
-        <v>7410.2112224448902</v>
+        <v>7.4102112224448904</v>
       </c>
       <c r="I70">
-        <v>2435.6186448356598</v>
+        <v>2.4356186448356598</v>
       </c>
       <c r="J70">
-        <v>3297.3523847695301</v>
+        <v>3.2973523847695301</v>
       </c>
       <c r="K70">
-        <v>1083.78731804736</v>
+        <v>1.0837873180473601</v>
       </c>
       <c r="L70">
-        <v>11861.172234468901</v>
+        <v>11.861172234468899</v>
       </c>
       <c r="M70">
-        <v>3898.5787822587899</v>
+        <v>3.8985787822587898</v>
       </c>
       <c r="N70">
-        <v>16694.356196392699</v>
+        <v>16.6943561963927</v>
       </c>
       <c r="O70">
-        <v>5487.1695279485702</v>
+        <v>5.4871695279485699</v>
       </c>
       <c r="P70">
-        <v>9816.6321309285195</v>
+        <v>9.8166321309285198</v>
       </c>
       <c r="Q70">
-        <v>3226.5709478243102</v>
+        <v>3.2265709478243099</v>
       </c>
       <c r="R70">
-        <v>1267.3335483870901</v>
+        <v>1.26733354838709</v>
       </c>
       <c r="S70">
-        <v>416.55239331476599</v>
+        <v>0.41655239331476601</v>
       </c>
       <c r="T70">
-        <v>6768.9105851703398</v>
+        <v>6.7689105851703397</v>
       </c>
       <c r="U70">
-        <v>2224.8333187224398</v>
+        <v>2.2248333187224398</v>
       </c>
       <c r="V70">
-        <v>3094.7516129032201</v>
+        <v>3.0947516129032202</v>
       </c>
       <c r="W70">
-        <v>1017.19566463794</v>
+        <v>1.0171956646379401</v>
       </c>
       <c r="X70">
-        <v>3529.5762096774101</v>
+        <v>3.5295762096774101</v>
       </c>
       <c r="Y70">
-        <v>1160.11559813842</v>
+        <v>1.1601155981384199</v>
       </c>
       <c r="Z70" s="4"/>
       <c r="AA70" s="4"/>
@@ -9066,76 +9066,76 @@
         <v>0.70833333333333304</v>
       </c>
       <c r="B71">
-        <v>11738.5147123278</v>
+        <v>11.738514712327801</v>
       </c>
       <c r="C71">
-        <v>3858.26320435041</v>
+        <v>3.8582632043504099</v>
       </c>
       <c r="D71">
-        <v>19712.548211666501</v>
+        <v>19.712548211666501</v>
       </c>
       <c r="E71">
-        <v>6479.2012697467999</v>
+        <v>6.4792012697467998</v>
       </c>
       <c r="F71">
-        <v>2908.07717620725</v>
+        <v>2.9080771762072501</v>
       </c>
       <c r="G71">
-        <v>955.83874445275603</v>
+        <v>0.95583874445275596</v>
       </c>
       <c r="H71">
-        <v>7821.5150300601199</v>
+        <v>7.8215150300601204</v>
       </c>
       <c r="I71">
-        <v>2570.8076687983398</v>
+        <v>2.5708076687983299</v>
       </c>
       <c r="J71">
-        <v>3480.3719438877702</v>
+        <v>3.48037194388777</v>
       </c>
       <c r="K71">
-        <v>1143.9429380663701</v>
+        <v>1.1439429380663699</v>
       </c>
       <c r="L71">
-        <v>12519.526653306601</v>
+        <v>12.519526653306601</v>
       </c>
       <c r="M71">
-        <v>4114.9694153050104</v>
+        <v>4.1149694153050103</v>
       </c>
       <c r="N71">
-        <v>17620.976513025998</v>
+        <v>17.620976513026001</v>
       </c>
       <c r="O71">
-        <v>5791.7348975617297</v>
+        <v>5.7917348975617298</v>
       </c>
       <c r="P71">
-        <v>10361.504342017301</v>
+        <v>10.3615043420173</v>
       </c>
       <c r="Q71">
-        <v>3405.6617829628799</v>
+        <v>3.4056617829628801</v>
       </c>
       <c r="R71">
-        <v>1359.8146451612899</v>
+        <v>1.35981464516129</v>
       </c>
       <c r="S71">
-        <v>446.94945985395202</v>
+        <v>0.44694945985395201</v>
       </c>
       <c r="T71">
-        <v>7144.61899799599</v>
+        <v>7.1446189979959902</v>
       </c>
       <c r="U71">
-        <v>2348.3227022002102</v>
+        <v>2.34832270220021</v>
       </c>
       <c r="V71">
-        <v>3320.5848387096698</v>
+        <v>3.3205848387096699</v>
       </c>
       <c r="W71">
-        <v>1091.4234563817899</v>
+        <v>1.09142345638178</v>
       </c>
       <c r="X71">
-        <v>3787.1398790322501</v>
+        <v>3.7871398790322499</v>
       </c>
       <c r="Y71">
-        <v>1244.7726823268999</v>
+        <v>1.2447726823269001</v>
       </c>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
@@ -9190,76 +9190,76 @@
         <v>0.71875</v>
       </c>
       <c r="B72">
-        <v>12545.5829654793</v>
+        <v>12.5455829654793</v>
       </c>
       <c r="C72">
-        <v>4123.5337109557604</v>
+        <v>4.1235337109557602</v>
       </c>
       <c r="D72">
-        <v>20811.587532001198</v>
+        <v>20.811587532001202</v>
       </c>
       <c r="E72">
-        <v>6840.4380253073996</v>
+        <v>6.8404380253074004</v>
       </c>
       <c r="F72">
-        <v>3173.7841611448698</v>
+        <v>3.1737841611448698</v>
       </c>
       <c r="G72">
-        <v>1043.17240703675</v>
+        <v>1.0431724070367501</v>
       </c>
       <c r="H72">
-        <v>8340.7018036072095</v>
+        <v>8.3407018036072103</v>
       </c>
       <c r="I72">
-        <v>2741.4561088823598</v>
+        <v>2.7414561088823599</v>
       </c>
       <c r="J72">
-        <v>3711.39663326653</v>
+        <v>3.71139663326653</v>
       </c>
       <c r="K72">
-        <v>1219.8770813690501</v>
+        <v>1.21987708136905</v>
       </c>
       <c r="L72">
-        <v>13350.5641983967</v>
+        <v>13.3505641983967</v>
       </c>
       <c r="M72">
-        <v>4388.1182471830098</v>
+        <v>4.3881182471830096</v>
       </c>
       <c r="N72">
-        <v>18790.6447815631</v>
+        <v>18.790644781563099</v>
       </c>
       <c r="O72">
-        <v>6176.1862657619504</v>
+        <v>6.1761862657619497</v>
       </c>
       <c r="P72">
-        <v>11049.293854375401</v>
+        <v>11.049293854375399</v>
       </c>
       <c r="Q72">
-        <v>3631.7272633836901</v>
+        <v>3.6317272633836901</v>
       </c>
       <c r="R72">
-        <v>1496.8236774193499</v>
+        <v>1.49682367741935</v>
       </c>
       <c r="S72">
-        <v>491.98215102311599</v>
+        <v>0.49198215102311599</v>
       </c>
       <c r="T72">
-        <v>7618.8738797595197</v>
+        <v>7.6188738797595201</v>
       </c>
       <c r="U72">
-        <v>2504.2027436393701</v>
+        <v>2.5042027436393699</v>
       </c>
       <c r="V72">
-        <v>3655.15258064516</v>
+        <v>3.6551525806451601</v>
       </c>
       <c r="W72">
-        <v>1201.3905552615599</v>
+        <v>1.20139055526156</v>
       </c>
       <c r="X72">
-        <v>4168.7156854838704</v>
+        <v>4.1687156854838703</v>
       </c>
       <c r="Y72">
-        <v>1370.19058482835</v>
+        <v>1.37019058482835</v>
       </c>
       <c r="Z72" s="4"/>
       <c r="AA72" s="4"/>
@@ -9314,76 +9314,76 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="B73">
-        <v>13504.502092184301</v>
+        <v>13.5045020921843</v>
       </c>
       <c r="C73">
-        <v>4438.7151860556996</v>
+        <v>4.4387151860556999</v>
       </c>
       <c r="D73">
-        <v>22005.711970701901</v>
+        <v>22.005711970701899</v>
       </c>
       <c r="E73">
-        <v>7232.9277479139701</v>
+        <v>7.23292774791397</v>
       </c>
       <c r="F73">
-        <v>3548.8786773546999</v>
+        <v>3.5488786773547001</v>
       </c>
       <c r="G73">
-        <v>1166.46001245467</v>
+        <v>1.16646001245468</v>
       </c>
       <c r="H73">
-        <v>8940.8008016031999</v>
+        <v>8.9408008016031992</v>
       </c>
       <c r="I73">
-        <v>2938.6991110574099</v>
+        <v>2.9386991110574101</v>
       </c>
       <c r="J73">
-        <v>3978.4251703406799</v>
+        <v>3.9784251703406799</v>
       </c>
       <c r="K73">
-        <v>1307.64511713449</v>
+        <v>1.3076451171344901</v>
       </c>
       <c r="L73">
-        <v>14311.1140881763</v>
+        <v>14.3111140881763</v>
       </c>
       <c r="M73">
-        <v>4703.8357281848603</v>
+        <v>4.7038357281848597</v>
       </c>
       <c r="N73">
-        <v>20142.599014028001</v>
+        <v>20.142599014028001</v>
       </c>
       <c r="O73">
-        <v>6620.5521329024596</v>
+        <v>6.6205521329024597</v>
       </c>
       <c r="P73">
-        <v>11844.271342685301</v>
+        <v>11.8442713426853</v>
       </c>
       <c r="Q73">
-        <v>3893.0237277661899</v>
+        <v>3.8930237277661899</v>
       </c>
       <c r="R73">
-        <v>1698.912</v>
+        <v>1.698912</v>
       </c>
       <c r="S73">
-        <v>558.40537049763202</v>
+        <v>0.55840537049763295</v>
       </c>
       <c r="T73">
-        <v>8167.0386132264503</v>
+        <v>8.1670386132264507</v>
       </c>
       <c r="U73">
-        <v>2684.37577854956</v>
+        <v>2.6843757785495601</v>
       </c>
       <c r="V73">
-        <v>4148.6400000000003</v>
+        <v>4.1486400000000003</v>
       </c>
       <c r="W73">
-        <v>1363.5920261092299</v>
+        <v>1.36359202610923</v>
       </c>
       <c r="X73">
-        <v>4731.54</v>
+        <v>4.7315399999999999</v>
       </c>
       <c r="Y73">
-        <v>1555.18199101799</v>
+        <v>1.55518199101799</v>
       </c>
       <c r="Z73" s="4"/>
       <c r="AA73" s="4"/>
@@ -9438,76 +9438,76 @@
         <v>0.73958333333333304</v>
       </c>
       <c r="B74">
-        <v>14590.525779752999</v>
+        <v>14.590525779752999</v>
       </c>
       <c r="C74">
-        <v>4795.67391000726</v>
+        <v>4.7956739100072596</v>
       </c>
       <c r="D74">
-        <v>23162.155241380198</v>
+        <v>23.162155241380201</v>
       </c>
       <c r="E74">
-        <v>7613.0322695269797</v>
+        <v>7.6130322695269799</v>
       </c>
       <c r="F74">
-        <v>4064.3466821546299</v>
+        <v>4.0643466821546301</v>
       </c>
       <c r="G74">
-        <v>1335.8861523606699</v>
+        <v>1.33588615236067</v>
       </c>
       <c r="H74">
-        <v>9594.8412825651303</v>
+        <v>9.5948412825651292</v>
       </c>
       <c r="I74">
-        <v>3153.6718212931301</v>
+        <v>3.1536718212931301</v>
       </c>
       <c r="J74">
-        <v>4269.4562725450896</v>
+        <v>4.2694562725450904</v>
       </c>
       <c r="K74">
-        <v>1403.3024145417601</v>
+        <v>1.4033024145417601</v>
       </c>
       <c r="L74">
-        <v>15358.005541082101</v>
+        <v>15.3580055410821</v>
       </c>
       <c r="M74">
-        <v>5047.9323086026097</v>
+        <v>5.0479323086026104</v>
       </c>
       <c r="N74">
-        <v>21616.077222444801</v>
+        <v>21.616077222444801</v>
       </c>
       <c r="O74">
-        <v>7104.8609993364998</v>
+        <v>7.1048609993365002</v>
       </c>
       <c r="P74">
-        <v>12710.707481629899</v>
+        <v>12.7107074816299</v>
       </c>
       <c r="Q74">
-        <v>4177.8075147898098</v>
+        <v>4.1778075147898104</v>
       </c>
       <c r="R74">
-        <v>1987.7727096774199</v>
+        <v>1.98777270967742</v>
       </c>
       <c r="S74">
-        <v>653.34929437928599</v>
+        <v>0.65334929437928602</v>
       </c>
       <c r="T74">
-        <v>8764.4765811623201</v>
+        <v>8.7644765811623202</v>
       </c>
       <c r="U74">
-        <v>2880.7441424404401</v>
+        <v>2.8807441424404399</v>
       </c>
       <c r="V74">
-        <v>4854.0203225806399</v>
+        <v>4.8540203225806398</v>
       </c>
       <c r="W74">
-        <v>1595.43932624743</v>
+        <v>1.59543932624743</v>
       </c>
       <c r="X74">
-        <v>5536.02899193548</v>
+        <v>5.5360289919354804</v>
       </c>
       <c r="Y74">
-        <v>1819.6047354585501</v>
+        <v>1.8196047354585501</v>
       </c>
       <c r="Z74" s="4"/>
       <c r="AA74" s="4"/>
@@ -9562,76 +9562,76 @@
         <v>0.75</v>
       </c>
       <c r="B75">
-        <v>15768.014812269699</v>
+        <v>15.768014812269699</v>
       </c>
       <c r="C75">
-        <v>5182.6958390179198</v>
+        <v>5.1826958390179199</v>
       </c>
       <c r="D75">
-        <v>24182.200183062399</v>
+        <v>24.182200183062399</v>
       </c>
       <c r="E75">
-        <v>7948.3048284260103</v>
+        <v>7.9483048284260098</v>
       </c>
       <c r="F75">
-        <v>4722.7747780237796</v>
+        <v>4.7227747780237799</v>
       </c>
       <c r="G75">
-        <v>1552.3010018760499</v>
+        <v>1.5523010018760499</v>
       </c>
       <c r="H75">
-        <v>10275.85250501</v>
+        <v>10.27585250501</v>
       </c>
       <c r="I75">
-        <v>3377.5093855591899</v>
+        <v>3.3775093855591898</v>
       </c>
       <c r="J75">
-        <v>4572.4886573146296</v>
+        <v>4.5724886573146204</v>
       </c>
       <c r="K75">
-        <v>1502.9043427699601</v>
+        <v>1.50290434276996</v>
       </c>
       <c r="L75">
-        <v>16448.067775551099</v>
+        <v>16.448067775551099</v>
       </c>
       <c r="M75">
-        <v>5406.2184387282996</v>
+        <v>5.4062184387282999</v>
       </c>
       <c r="N75">
-        <v>23150.3174188376</v>
+        <v>23.150317418837599</v>
       </c>
       <c r="O75">
-        <v>7609.1413654173102</v>
+        <v>7.6091413654173099</v>
       </c>
       <c r="P75">
-        <v>13612.872945891701</v>
+        <v>13.6128729458917</v>
       </c>
       <c r="Q75">
-        <v>4474.3349631339897</v>
+        <v>4.4743349631339902</v>
       </c>
       <c r="R75">
-        <v>2366.8310322580601</v>
+        <v>2.3668310322580601</v>
       </c>
       <c r="S75">
-        <v>777.93973994730698</v>
+        <v>0.77793973994730703</v>
       </c>
       <c r="T75">
-        <v>9386.5511663326597</v>
+        <v>9.3865511663326604</v>
       </c>
       <c r="U75">
-        <v>3085.2101708216601</v>
+        <v>3.0852101708216599</v>
       </c>
       <c r="V75">
-        <v>5779.6577419354799</v>
+        <v>5.7796577419354804</v>
       </c>
       <c r="W75">
-        <v>1899.68163314815</v>
+        <v>1.8996816331481501</v>
       </c>
       <c r="X75">
-        <v>6591.7220564516101</v>
+        <v>6.5917220564516104</v>
       </c>
       <c r="Y75">
-        <v>2166.5942657125702</v>
+        <v>2.1665942657125701</v>
       </c>
       <c r="Z75" s="4"/>
       <c r="AA75" s="4"/>
@@ -9686,76 +9686,76 @@
         <v>0.76041666666666696</v>
       </c>
       <c r="B76">
-        <v>16934.9435860753</v>
+        <v>16.934943586075299</v>
       </c>
       <c r="C76">
-        <v>5566.2467788437098</v>
+        <v>5.56624677884371</v>
       </c>
       <c r="D76">
-        <v>25032.8685720256</v>
+        <v>25.032868572025599</v>
       </c>
       <c r="E76">
-        <v>8227.9060066563397</v>
+        <v>8.2279060066563403</v>
       </c>
       <c r="F76">
-        <v>5425.2981180910201</v>
+        <v>5.4252981180910202</v>
       </c>
       <c r="G76">
-        <v>1783.20925727331</v>
+        <v>1.78320925727331</v>
       </c>
       <c r="H76">
-        <v>10936.635671342599</v>
+        <v>10.9366356713426</v>
       </c>
       <c r="I76">
-        <v>3594.6983093025001</v>
+        <v>3.5946983093024998</v>
       </c>
       <c r="J76">
-        <v>4866.5200801603196</v>
+        <v>4.8665200801603197</v>
       </c>
       <c r="K76">
-        <v>1599.5477978824599</v>
+        <v>1.5995477978824599</v>
       </c>
       <c r="L76">
-        <v>17505.751923847602</v>
+        <v>17.505751923847601</v>
       </c>
       <c r="M76">
-        <v>5753.8624065730401</v>
+        <v>5.7538624065730399</v>
       </c>
       <c r="N76">
-        <v>24638.9861242484</v>
+        <v>24.638986124248401</v>
       </c>
       <c r="O76">
-        <v>8098.4431067630403</v>
+        <v>8.0984431067630407</v>
       </c>
       <c r="P76">
-        <v>14488.2414161656</v>
+        <v>14.4882414161656</v>
       </c>
       <c r="Q76">
-        <v>4762.0546654877498</v>
+        <v>4.7620546654877502</v>
       </c>
       <c r="R76">
-        <v>2775.5746451612899</v>
+        <v>2.7755746451612899</v>
       </c>
       <c r="S76">
-        <v>912.28726860197901</v>
+        <v>0.91228726860197895</v>
       </c>
       <c r="T76">
-        <v>9990.1482885771493</v>
+        <v>9.9901482885771493</v>
       </c>
       <c r="U76">
-        <v>3283.6029508351298</v>
+        <v>3.2836029508351299</v>
       </c>
       <c r="V76">
-        <v>6777.7848387096701</v>
+        <v>6.7777848387096702</v>
       </c>
       <c r="W76">
-        <v>2227.7501448061498</v>
+        <v>2.2277501448061501</v>
       </c>
       <c r="X76">
-        <v>7730.0898790322499</v>
+        <v>7.7300898790322501</v>
       </c>
       <c r="Y76">
-        <v>2540.7576748419001</v>
+        <v>2.5407576748418998</v>
       </c>
       <c r="Z76" s="4"/>
       <c r="AA76" s="4"/>
@@ -9810,76 +9810,76 @@
         <v>0.77083333333333304</v>
       </c>
       <c r="B77">
-        <v>17995.872799017299</v>
+        <v>17.995872799017299</v>
       </c>
       <c r="C77">
-        <v>5914.9573478576704</v>
+        <v>5.91495734785767</v>
       </c>
       <c r="D77">
-        <v>25718.230348667799</v>
+        <v>25.718230348667799</v>
       </c>
       <c r="E77">
-        <v>8453.1735289357803</v>
+        <v>8.4531735289357801</v>
       </c>
       <c r="F77">
-        <v>6042.4717195681596</v>
+        <v>6.0424717195681596</v>
       </c>
       <c r="G77">
-        <v>1986.0644102148401</v>
+        <v>1.9860644102148399</v>
       </c>
       <c r="H77">
-        <v>11543.477354709399</v>
+        <v>11.543477354709401</v>
       </c>
       <c r="I77">
-        <v>3794.1575249851298</v>
+        <v>3.7941575249851298</v>
       </c>
       <c r="J77">
-        <v>5136.5489378757502</v>
+        <v>5.1365489378757498</v>
       </c>
       <c r="K77">
-        <v>1688.30199135313</v>
+        <v>1.6883019913531301</v>
       </c>
       <c r="L77">
-        <v>18477.094509017999</v>
+        <v>18.477094509017999</v>
       </c>
       <c r="M77">
-        <v>6073.1272750018697</v>
+        <v>6.0731272750018697</v>
       </c>
       <c r="N77">
-        <v>26006.1308537074</v>
+        <v>26.006130853707401</v>
       </c>
       <c r="O77">
-        <v>8547.8018488152393</v>
+        <v>8.5478018488152401</v>
       </c>
       <c r="P77">
-        <v>15292.1512358049</v>
+        <v>15.2921512358049</v>
       </c>
       <c r="Q77">
-        <v>5026.2870452003899</v>
+        <v>5.02628704520039</v>
       </c>
       <c r="R77">
-        <v>3132.9398709677398</v>
+        <v>3.1329398709677401</v>
       </c>
       <c r="S77">
-        <v>1029.7475380682099</v>
+        <v>1.02974753806821</v>
       </c>
       <c r="T77">
-        <v>10544.4721763527</v>
+        <v>10.5444721763527</v>
       </c>
       <c r="U77">
-        <v>3465.8004018678998</v>
+        <v>3.4658004018679001</v>
       </c>
       <c r="V77">
-        <v>7650.4490322580596</v>
+        <v>7.6504490322580603</v>
       </c>
       <c r="W77">
-        <v>2514.5809943842401</v>
+        <v>2.5145809943842399</v>
       </c>
       <c r="X77">
-        <v>8725.3667741935406</v>
+        <v>8.7253667741935406</v>
       </c>
       <c r="Y77">
-        <v>2867.8893705331898</v>
+        <v>2.8678893705331898</v>
       </c>
       <c r="Z77" s="4"/>
       <c r="AA77" s="4"/>
@@ -9934,76 +9934,76 @@
         <v>0.78125</v>
       </c>
       <c r="B78">
-        <v>18857.4055682978</v>
+        <v>18.8574055682978</v>
       </c>
       <c r="C78">
-        <v>6198.1294752108997</v>
+        <v>6.1981294752108997</v>
       </c>
       <c r="D78">
-        <v>26253.414723604001</v>
+        <v>26.253414723603999</v>
       </c>
       <c r="E78">
-        <v>8629.0801263173798</v>
+        <v>8.6290801263173798</v>
       </c>
       <c r="F78">
-        <v>6450.1754786993297</v>
+        <v>6.4501754786993297</v>
       </c>
       <c r="G78">
-        <v>2120.07015546293</v>
+        <v>2.1200701554629302</v>
       </c>
       <c r="H78">
-        <v>12062.6641282565</v>
+        <v>12.0626641282565</v>
       </c>
       <c r="I78">
-        <v>3964.8059650691598</v>
+        <v>3.9648059650691598</v>
       </c>
       <c r="J78">
-        <v>5367.5736272545</v>
+        <v>5.3675736272545</v>
       </c>
       <c r="K78">
-        <v>1764.23613465581</v>
+        <v>1.76423613465581</v>
       </c>
       <c r="L78">
-        <v>19308.132054108199</v>
+        <v>19.308132054108199</v>
       </c>
       <c r="M78">
-        <v>6346.27610687988</v>
+        <v>6.3462761068798796</v>
       </c>
       <c r="N78">
-        <v>27175.7991222444</v>
+        <v>27.175799122244399</v>
       </c>
       <c r="O78">
-        <v>8932.2532170154609</v>
+        <v>8.9322532170154592</v>
       </c>
       <c r="P78">
-        <v>15979.9407481629</v>
+        <v>15.9799407481629</v>
       </c>
       <c r="Q78">
-        <v>5252.3525256211997</v>
+        <v>5.2523525256212</v>
       </c>
       <c r="R78">
-        <v>3361.28825806451</v>
+        <v>3.3612882580645098</v>
       </c>
       <c r="S78">
-        <v>1104.80202335015</v>
+        <v>1.1048020233501501</v>
       </c>
       <c r="T78">
-        <v>11018.727058116199</v>
+        <v>11.0187270581162</v>
       </c>
       <c r="U78">
-        <v>3621.6804433070602</v>
+        <v>3.62168044330706</v>
       </c>
       <c r="V78">
-        <v>8208.0619354838691</v>
+        <v>8.20806193548386</v>
       </c>
       <c r="W78">
-        <v>2697.8594925172001</v>
+        <v>2.6978594925172001</v>
       </c>
       <c r="X78">
-        <v>9361.3264516129002</v>
+        <v>9.3613264516129</v>
       </c>
       <c r="Y78">
-        <v>3076.9192080356001</v>
+        <v>3.0769192080356</v>
       </c>
       <c r="Z78" s="4"/>
       <c r="AA78" s="4"/>
@@ -10058,76 +10058,76 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B79">
-        <v>19428.2983119788</v>
+        <v>19.4282983119788</v>
       </c>
       <c r="C79">
-        <v>6385.7728458207603</v>
+        <v>6.3857728458207603</v>
       </c>
       <c r="D79">
-        <v>26622.789018586202</v>
+        <v>26.6227890185862</v>
       </c>
       <c r="E79">
-        <v>8750.4875859396907</v>
+        <v>8.7504875859396893</v>
       </c>
       <c r="F79">
-        <v>6553.7790371064702</v>
+        <v>6.5537790371064704</v>
       </c>
       <c r="G79">
-        <v>2154.1229983513299</v>
+        <v>2.1541229983513301</v>
       </c>
       <c r="H79">
-        <v>12453.7398797595</v>
+        <v>12.4537398797595</v>
       </c>
       <c r="I79">
-        <v>4093.3463485090801</v>
+        <v>4.0933463485090797</v>
       </c>
       <c r="J79">
-        <v>5541.5922244488902</v>
+        <v>5.5415922244488902</v>
       </c>
       <c r="K79">
-        <v>1821.4332815591299</v>
+        <v>1.8214332815591301</v>
       </c>
       <c r="L79">
-        <v>19934.1083867735</v>
+        <v>19.934108386773499</v>
       </c>
       <c r="M79">
-        <v>6552.0245776451302</v>
+        <v>6.5520245776451302</v>
       </c>
       <c r="N79">
-        <v>28056.847947895702</v>
+        <v>28.056847947895701</v>
       </c>
       <c r="O79">
-        <v>9221.8399618935491</v>
+        <v>9.2218399618935507</v>
       </c>
       <c r="P79">
-        <v>16498.015965263799</v>
+        <v>16.4980159652638</v>
       </c>
       <c r="Q79">
-        <v>5422.6356147693496</v>
+        <v>5.42263561476934</v>
       </c>
       <c r="R79">
-        <v>3402.3909677419301</v>
+        <v>3.4023909677419302</v>
       </c>
       <c r="S79">
-        <v>1118.3118307008999</v>
+        <v>1.1183118307008999</v>
       </c>
       <c r="T79">
-        <v>11375.958008015999</v>
+        <v>11.375958008015999</v>
       </c>
       <c r="U79">
-        <v>3739.0965784170698</v>
+        <v>3.7390965784170702</v>
       </c>
       <c r="V79">
-        <v>8308.4322580645094</v>
+        <v>8.30843225806451</v>
       </c>
       <c r="W79">
-        <v>2730.8496221811301</v>
+        <v>2.7308496221811298</v>
       </c>
       <c r="X79">
-        <v>9475.7991935483806</v>
+        <v>9.4757991935483794</v>
       </c>
       <c r="Y79">
-        <v>3114.5445787860399</v>
+        <v>3.11454457878604</v>
       </c>
       <c r="Z79" s="4"/>
       <c r="AA79" s="4"/>
@@ -10182,76 +10182,76 @@
         <v>0.80208333333333304</v>
       </c>
       <c r="B80">
-        <v>19686.527943176599</v>
+        <v>19.6865279431766</v>
       </c>
       <c r="C80">
-        <v>6470.6488210817097</v>
+        <v>6.4706488210817001</v>
       </c>
       <c r="D80">
-        <v>26793.958126809401</v>
+        <v>26.7939581268094</v>
       </c>
       <c r="E80">
-        <v>8806.7481511102906</v>
+        <v>8.8067481511102894</v>
       </c>
       <c r="F80">
-        <v>6391.3681908171102</v>
+        <v>6.3913681908171096</v>
       </c>
       <c r="G80">
-        <v>2100.7411346673698</v>
+        <v>2.1007411346673699</v>
       </c>
       <c r="H80">
-        <v>12689.7338677354</v>
+        <v>12.6897338677354</v>
       </c>
       <c r="I80">
-        <v>4170.9138212745402</v>
+        <v>4.1709138212745396</v>
       </c>
       <c r="J80">
-        <v>5646.6034468937796</v>
+        <v>5.6466034468937796</v>
       </c>
       <c r="K80">
-        <v>1855.94880124216</v>
+        <v>1.8559488012421601</v>
       </c>
       <c r="L80">
-        <v>20311.852725450899</v>
+        <v>20.311852725450901</v>
       </c>
       <c r="M80">
-        <v>6676.18313758968</v>
+        <v>6.6761831375896801</v>
       </c>
       <c r="N80">
-        <v>28588.515342685299</v>
+        <v>28.588515342685302</v>
       </c>
       <c r="O80">
-        <v>9396.5905838027393</v>
+        <v>9.3965905838027393</v>
       </c>
       <c r="P80">
-        <v>16810.6475617902</v>
+        <v>16.810647561790201</v>
       </c>
       <c r="Q80">
-        <v>5525.3926513242604</v>
+        <v>5.5253926513242604</v>
       </c>
       <c r="R80">
-        <v>3282.5080645161202</v>
+        <v>3.28250806451612</v>
       </c>
       <c r="S80">
-        <v>1078.90822592788</v>
+        <v>1.0789082259278799</v>
       </c>
       <c r="T80">
-        <v>11591.528408817599</v>
+        <v>11.5915284088176</v>
       </c>
       <c r="U80">
-        <v>3809.95114270759</v>
+        <v>3.8099511427075901</v>
       </c>
       <c r="V80">
-        <v>8015.6854838709596</v>
+        <v>8.0156854838709606</v>
       </c>
       <c r="W80">
-        <v>2634.6284106613298</v>
+        <v>2.63462841066133</v>
       </c>
       <c r="X80">
-        <v>9141.9203629032199</v>
+        <v>9.1419203629032193</v>
       </c>
       <c r="Y80">
-        <v>3004.8039140972701</v>
+        <v>3.0048039140972702</v>
       </c>
       <c r="Z80" s="4"/>
       <c r="AA80" s="4"/>
@@ -10306,76 +10306,76 @@
         <v>0.8125</v>
       </c>
       <c r="B81">
-        <v>19613.586288770999</v>
+        <v>19.613586288771</v>
       </c>
       <c r="C81">
-        <v>6446.6740586731403</v>
+        <v>6.4466740586731399</v>
       </c>
       <c r="D81">
-        <v>26714.6791036953</v>
+        <v>26.7146791036953</v>
       </c>
       <c r="E81">
-        <v>8780.6903963385703</v>
+        <v>8.7806903963385707</v>
       </c>
       <c r="F81">
-        <v>6034.0684005915</v>
+        <v>6.0340684005915</v>
       </c>
       <c r="G81">
-        <v>1983.3023728364701</v>
+        <v>1.98330237283647</v>
       </c>
       <c r="H81">
-        <v>12736.9326653306</v>
+        <v>12.736932665330601</v>
       </c>
       <c r="I81">
-        <v>4186.4273158276401</v>
+        <v>4.1864273158276397</v>
       </c>
       <c r="J81">
-        <v>5667.6056913827597</v>
+        <v>5.6676056913827599</v>
       </c>
       <c r="K81">
-        <v>1862.85190517877</v>
+        <v>1.86285190517877</v>
       </c>
       <c r="L81">
-        <v>20387.4015931863</v>
+        <v>20.387401593186301</v>
       </c>
       <c r="M81">
-        <v>6701.0148495785897</v>
+        <v>6.7010148495785904</v>
       </c>
       <c r="N81">
-        <v>28694.848821643202</v>
+        <v>28.694848821643198</v>
       </c>
       <c r="O81">
-        <v>9431.5407081845697</v>
+        <v>9.4315407081845795</v>
       </c>
       <c r="P81">
-        <v>16873.173881095499</v>
+        <v>16.8731738810955</v>
       </c>
       <c r="Q81">
-        <v>5545.9440586352403</v>
+        <v>5.5459440586352402</v>
       </c>
       <c r="R81">
-        <v>3049.5927096774199</v>
+        <v>3.04959270967742</v>
       </c>
       <c r="S81">
-        <v>1002.3526509403</v>
+        <v>1.0023526509403</v>
       </c>
       <c r="T81">
-        <v>11634.642488977899</v>
+        <v>11.634642488977899</v>
       </c>
       <c r="U81">
-        <v>3824.1220555657001</v>
+        <v>3.8241220555657001</v>
       </c>
       <c r="V81">
-        <v>7446.9203225806395</v>
+        <v>7.44692032258064</v>
       </c>
       <c r="W81">
-        <v>2447.6843425657098</v>
+        <v>2.4476843425657102</v>
       </c>
       <c r="X81">
-        <v>8493.2414919354796</v>
+        <v>8.4932414919354802</v>
       </c>
       <c r="Y81">
-        <v>2791.5934798448002</v>
+        <v>2.7915934798448001</v>
       </c>
       <c r="Z81" s="4"/>
       <c r="AA81" s="4"/>
@@ -10430,76 +10430,76 @@
         <v>0.82291666666666696</v>
       </c>
       <c r="B82">
-        <v>19198.343165104401</v>
+        <v>19.198343165104401</v>
       </c>
       <c r="C82">
-        <v>6310.1902441390803</v>
+        <v>6.31019024413908</v>
       </c>
       <c r="D82">
-        <v>26336.638206752999</v>
+        <v>26.336638206753001</v>
       </c>
       <c r="E82">
-        <v>8656.4343624060803</v>
+        <v>8.6564343624060793</v>
       </c>
       <c r="F82">
-        <v>5548.3648172958801</v>
+        <v>5.5483648172958802</v>
       </c>
       <c r="G82">
-        <v>1823.6593251787799</v>
+        <v>1.82365932517878</v>
       </c>
       <c r="H82">
-        <v>12568.3655310621</v>
+        <v>12.568365531062099</v>
       </c>
       <c r="I82">
-        <v>4131.0219781380201</v>
+        <v>4.13102197813802</v>
       </c>
       <c r="J82">
-        <v>5592.5976753507002</v>
+        <v>5.5925976753507003</v>
       </c>
       <c r="K82">
-        <v>1838.1979625480301</v>
+        <v>1.83819796254803</v>
       </c>
       <c r="L82">
-        <v>20117.5842084168</v>
+        <v>20.117584208416801</v>
       </c>
       <c r="M82">
-        <v>6612.33016390391</v>
+        <v>6.61233016390391</v>
       </c>
       <c r="N82">
-        <v>28315.0863967935</v>
+        <v>28.3150863967935</v>
       </c>
       <c r="O82">
-        <v>9306.7188353922993</v>
+        <v>9.3067188353922994</v>
       </c>
       <c r="P82">
-        <v>16649.865597862299</v>
+        <v>16.649865597862298</v>
       </c>
       <c r="Q82">
-        <v>5472.5461753817299</v>
+        <v>5.4725461753817299</v>
       </c>
       <c r="R82">
-        <v>2748.17283870967</v>
+        <v>2.74817283870967</v>
       </c>
       <c r="S82">
-        <v>903.28073036814601</v>
+        <v>0.90328073036814605</v>
       </c>
       <c r="T82">
-        <v>11480.6636312625</v>
+        <v>11.4806636312625</v>
       </c>
       <c r="U82">
-        <v>3773.5116525010399</v>
+        <v>3.7735116525010399</v>
       </c>
       <c r="V82">
-        <v>6710.8712903225796</v>
+        <v>6.7108712903225696</v>
       </c>
       <c r="W82">
-        <v>2205.7567250302</v>
+        <v>2.2057567250301999</v>
       </c>
       <c r="X82">
-        <v>7653.7747177419296</v>
+        <v>7.6537747177419302</v>
       </c>
       <c r="Y82">
-        <v>2515.6740943416098</v>
+        <v>2.5156740943416098</v>
       </c>
       <c r="Z82" s="4"/>
       <c r="AA82" s="4"/>
@@ -10554,76 +10554,76 @@
         <v>0.83333333333333304</v>
       </c>
       <c r="B83">
-        <v>18467.350023789499</v>
+        <v>18.4673500237895</v>
       </c>
       <c r="C83">
-        <v>6069.9244175941103</v>
+        <v>6.0699244175941098</v>
       </c>
       <c r="D83">
-        <v>25657.478362811798</v>
+        <v>25.657478362811801</v>
       </c>
       <c r="E83">
-        <v>8433.2053168268394</v>
+        <v>8.4332053168268395</v>
       </c>
       <c r="F83">
-        <v>5003.4808683496003</v>
+        <v>5.0034808683495999</v>
       </c>
       <c r="G83">
-        <v>1644.5646319930499</v>
+        <v>1.64456463199305</v>
       </c>
       <c r="H83">
-        <v>12184.0324649298</v>
+        <v>12.1840324649298</v>
       </c>
       <c r="I83">
-        <v>4004.6978082056798</v>
+        <v>4.0046978082056803</v>
       </c>
       <c r="J83">
-        <v>5421.5793987975903</v>
+        <v>5.42157939879759</v>
       </c>
       <c r="K83">
-        <v>1781.9869733499399</v>
+        <v>1.7819869733499401</v>
       </c>
       <c r="L83">
-        <v>19502.4005711422</v>
+        <v>19.5024005711422</v>
       </c>
       <c r="M83">
-        <v>6410.1290805656499</v>
+        <v>6.4101290805656497</v>
       </c>
       <c r="N83">
-        <v>27449.228068136199</v>
+        <v>27.4492280681362</v>
       </c>
       <c r="O83">
-        <v>9022.1249654259009</v>
+        <v>9.0221249654259008</v>
       </c>
       <c r="P83">
-        <v>16140.722712090799</v>
+        <v>16.140722712090799</v>
       </c>
       <c r="Q83">
-        <v>5305.1990015637302</v>
+        <v>5.3051990015637296</v>
       </c>
       <c r="R83">
-        <v>2422.7763870967701</v>
+        <v>2.42277638709677</v>
       </c>
       <c r="S83">
-        <v>796.32808884138205</v>
+        <v>0.79632808884138195</v>
       </c>
       <c r="T83">
-        <v>11129.591835671299</v>
+        <v>11.129591835671301</v>
       </c>
       <c r="U83">
-        <v>3658.1199335136098</v>
+        <v>3.6581199335136101</v>
       </c>
       <c r="V83">
-        <v>5916.2729032258003</v>
+        <v>5.9162729032258001</v>
       </c>
       <c r="W83">
-        <v>1944.5848651907199</v>
+        <v>1.94458486519072</v>
       </c>
       <c r="X83">
-        <v>6747.5321774193499</v>
+        <v>6.74753217741935</v>
       </c>
       <c r="Y83">
-        <v>2217.8065759006599</v>
+        <v>2.21780657590066</v>
       </c>
       <c r="Z83" s="4"/>
       <c r="AA83" s="4"/>
@@ -10678,76 +10678,76 @@
         <v>0.84375</v>
       </c>
       <c r="B84">
-        <v>17520.3682861206</v>
+        <v>17.5203682861206</v>
       </c>
       <c r="C84">
-        <v>5758.6665725276898</v>
+        <v>5.75866657252769</v>
       </c>
       <c r="D84">
-        <v>24748.5664989947</v>
+        <v>24.748566498994698</v>
       </c>
       <c r="E84">
-        <v>8134.4604341816703</v>
+        <v>8.1344604341816709</v>
       </c>
       <c r="F84">
-        <v>4444.6267889003802</v>
+        <v>4.4446267889003801</v>
       </c>
       <c r="G84">
-        <v>1460.8781789637201</v>
+        <v>1.46087817896372</v>
       </c>
       <c r="H84">
-        <v>11644.617635270501</v>
+        <v>11.6446176352705</v>
       </c>
       <c r="I84">
-        <v>3827.4007275989002</v>
+        <v>3.8274007275989002</v>
       </c>
       <c r="J84">
-        <v>5181.5537474949797</v>
+        <v>5.1815537474949798</v>
       </c>
       <c r="K84">
-        <v>1703.09435693157</v>
+        <v>1.70309435693157</v>
       </c>
       <c r="L84">
-        <v>18638.984939879701</v>
+        <v>18.638984939879698</v>
       </c>
       <c r="M84">
-        <v>6126.3380864066803</v>
+        <v>6.1263380864066797</v>
       </c>
       <c r="N84">
-        <v>26233.988308617201</v>
+        <v>26.233988308617199</v>
       </c>
       <c r="O84">
-        <v>8622.6949724906099</v>
+        <v>8.6226949724906099</v>
       </c>
       <c r="P84">
-        <v>15426.1362057448</v>
+        <v>15.4261362057448</v>
       </c>
       <c r="Q84">
-        <v>5070.3257751524998</v>
+        <v>5.0703257751524902</v>
       </c>
       <c r="R84">
-        <v>2098.52167741935</v>
+        <v>2.0985216774193498</v>
       </c>
       <c r="S84">
-        <v>689.75071974102696</v>
+        <v>0.68975071974102697</v>
       </c>
       <c r="T84">
-        <v>10636.8594909819</v>
+        <v>10.6368594909819</v>
       </c>
       <c r="U84">
-        <v>3496.1666437067001</v>
+        <v>3.4961666437067001</v>
       </c>
       <c r="V84">
-        <v>5124.4625806451604</v>
+        <v>5.1244625806451598</v>
       </c>
       <c r="W84">
-        <v>1684.3293978419199</v>
+        <v>1.68432939784192</v>
       </c>
       <c r="X84">
-        <v>5844.4694354838703</v>
+        <v>5.8444694354838704</v>
       </c>
       <c r="Y84">
-        <v>1920.9842066472299</v>
+        <v>1.92098420664723</v>
       </c>
       <c r="Z84" s="4"/>
       <c r="AA84" s="4"/>
@@ -10802,76 +10802,76 @@
         <v>0.85416666666666696</v>
       </c>
       <c r="B85">
-        <v>16513.001019846099</v>
+        <v>16.513001019846101</v>
       </c>
       <c r="C85">
-        <v>5427.5609640257799</v>
+        <v>5.4275609640257798</v>
       </c>
       <c r="D85">
-        <v>23743.4963747111</v>
+        <v>23.7434963747111</v>
       </c>
       <c r="E85">
-        <v>7804.1098597395003</v>
+        <v>7.8041098597395004</v>
       </c>
       <c r="F85">
-        <v>3919.3452692481701</v>
+        <v>3.9193452692481698</v>
       </c>
       <c r="G85">
-        <v>1288.2264927098399</v>
+        <v>1.2882264927098399</v>
       </c>
       <c r="H85">
-        <v>11051.261322645199</v>
+        <v>11.0512613226452</v>
       </c>
       <c r="I85">
-        <v>3632.3739389314401</v>
+        <v>3.63237393893144</v>
       </c>
       <c r="J85">
-        <v>4917.5255310621196</v>
+        <v>4.91752553106212</v>
       </c>
       <c r="K85">
-        <v>1616.3124788713601</v>
+        <v>1.6163124788713601</v>
       </c>
       <c r="L85">
-        <v>17689.227745490902</v>
+        <v>17.6892277454909</v>
       </c>
       <c r="M85">
-        <v>5814.1679928318199</v>
+        <v>5.8141679928318197</v>
       </c>
       <c r="N85">
-        <v>24897.224573146199</v>
+        <v>24.8972245731462</v>
       </c>
       <c r="O85">
-        <v>8183.3219802617896</v>
+        <v>8.1833219802617894</v>
       </c>
       <c r="P85">
-        <v>14640.091048764099</v>
+        <v>14.6400910487641</v>
       </c>
       <c r="Q85">
-        <v>4811.9652261001402</v>
+        <v>4.8119652261001402</v>
       </c>
       <c r="R85">
-        <v>1799.38529032258</v>
+        <v>1.79938529032258</v>
       </c>
       <c r="S85">
-        <v>591.42934402168601</v>
+        <v>0.59142934402168601</v>
       </c>
       <c r="T85">
-        <v>10094.8539118236</v>
+        <v>10.0948539118236</v>
       </c>
       <c r="U85">
-        <v>3318.0180249190998</v>
+        <v>3.3180180249191</v>
       </c>
       <c r="V85">
-        <v>4393.9896774193503</v>
+        <v>4.3939896774193503</v>
       </c>
       <c r="W85">
-        <v>1444.23456528774</v>
+        <v>1.44423456528774</v>
       </c>
       <c r="X85">
-        <v>5011.3622580645097</v>
+        <v>5.0113622580645103</v>
       </c>
       <c r="Y85">
-        <v>1647.15511951906</v>
+        <v>1.6471551195190599</v>
       </c>
       <c r="Z85" s="4"/>
       <c r="AA85" s="4"/>
@@ -10926,76 +10926,76 @@
         <v>0.86458333333333304</v>
       </c>
       <c r="B86">
-        <v>15580.6488621759</v>
+        <v>15.580648862175901</v>
       </c>
       <c r="C86">
-        <v>5121.1116293703699</v>
+        <v>5.12111162937037</v>
       </c>
       <c r="D86">
-        <v>22757.379732360801</v>
+        <v>22.7573797323608</v>
       </c>
       <c r="E86">
-        <v>7479.9889935466199</v>
+        <v>7.4799889935466197</v>
       </c>
       <c r="F86">
-        <v>3470.2599420615402</v>
+        <v>3.4702599420615399</v>
       </c>
       <c r="G86">
-        <v>1140.61928379455</v>
+        <v>1.1406192837945499</v>
       </c>
       <c r="H86">
-        <v>10491.618436873699</v>
+        <v>10.491618436873701</v>
       </c>
       <c r="I86">
-        <v>3448.4282178019098</v>
+        <v>3.4484282178019101</v>
       </c>
       <c r="J86">
-        <v>4668.49891783567</v>
+        <v>4.6684989178356702</v>
       </c>
       <c r="K86">
-        <v>1534.4613893373</v>
+        <v>1.5344613893373</v>
       </c>
       <c r="L86">
-        <v>16793.434028056101</v>
+        <v>16.793434028056101</v>
       </c>
       <c r="M86">
-        <v>5519.73483639189</v>
+        <v>5.5197348363918897</v>
       </c>
       <c r="N86">
-        <v>23636.4133226452</v>
+        <v>23.6364133226452</v>
       </c>
       <c r="O86">
-        <v>7768.9133625914201</v>
+        <v>7.7689133625914204</v>
       </c>
       <c r="P86">
-        <v>13898.7075484301</v>
+        <v>13.898707548430099</v>
       </c>
       <c r="Q86">
-        <v>4568.2842536984799</v>
+        <v>4.5682842536984802</v>
       </c>
       <c r="R86">
-        <v>1547.0603225806401</v>
+        <v>1.5470603225806401</v>
       </c>
       <c r="S86">
-        <v>508.49413778514202</v>
+        <v>0.50849413778514196</v>
       </c>
       <c r="T86">
-        <v>9583.6441042084098</v>
+        <v>9.5836441042084104</v>
       </c>
       <c r="U86">
-        <v>3149.9914867444299</v>
+        <v>3.1499914867444301</v>
       </c>
       <c r="V86">
-        <v>3777.82741935483</v>
+        <v>3.7778274193548298</v>
       </c>
       <c r="W86">
-        <v>1241.71182485081</v>
+        <v>1.2417118248508101</v>
       </c>
       <c r="X86">
-        <v>4308.6268145161202</v>
+        <v>4.3086268145161197</v>
       </c>
       <c r="Y86">
-        <v>1416.1771490788799</v>
+        <v>1.4161771490788799</v>
       </c>
       <c r="Z86" s="4"/>
       <c r="AA86" s="4"/>
@@ -11050,76 +11050,76 @@
         <v>0.875</v>
       </c>
       <c r="B87">
-        <v>14836.4676004266</v>
+        <v>14.8364676004266</v>
       </c>
       <c r="C87">
-        <v>4876.5110772614298</v>
+        <v>4.87651107726143</v>
       </c>
       <c r="D87">
-        <v>21879.9202969492</v>
+        <v>21.879920296949201</v>
       </c>
       <c r="E87">
-        <v>7191.5820241875899</v>
+        <v>7.1915820241875901</v>
       </c>
       <c r="F87">
-        <v>3129.7505033453999</v>
+        <v>3.1297505033454001</v>
       </c>
       <c r="G87">
-        <v>1028.6992436251701</v>
+        <v>1.0286992436251701</v>
       </c>
       <c r="H87">
-        <v>10039.858517033999</v>
+        <v>10.039858517034</v>
       </c>
       <c r="I87">
-        <v>3299.9419127937299</v>
+        <v>3.2999419127937299</v>
       </c>
       <c r="J87">
-        <v>4467.4774348697301</v>
+        <v>4.4674774348697301</v>
       </c>
       <c r="K87">
-        <v>1468.38882308692</v>
+        <v>1.46838882308692</v>
       </c>
       <c r="L87">
-        <v>16070.323436873699</v>
+        <v>16.0703234368737</v>
       </c>
       <c r="M87">
-        <v>5282.0598787837598</v>
+        <v>5.2820598787837598</v>
       </c>
       <c r="N87">
-        <v>22618.6500240481</v>
+        <v>22.618650024048101</v>
       </c>
       <c r="O87">
-        <v>7434.3907435081201</v>
+        <v>7.4343907435081196</v>
       </c>
       <c r="P87">
-        <v>13300.2413493653</v>
+        <v>13.300241349365299</v>
       </c>
       <c r="Q87">
-        <v>4371.5779265790798</v>
+        <v>4.3715779265790804</v>
       </c>
       <c r="R87">
-        <v>1357.5311612903199</v>
+        <v>1.35753116129032</v>
       </c>
       <c r="S87">
-        <v>446.19891500113198</v>
+        <v>0.44619891500113201</v>
       </c>
       <c r="T87">
-        <v>9170.9807655310597</v>
+        <v>9.1709807655310591</v>
       </c>
       <c r="U87">
-        <v>3014.35560653114</v>
+        <v>3.0143556065311401</v>
       </c>
       <c r="V87">
-        <v>3315.00870967741</v>
+        <v>3.3150087096774099</v>
       </c>
       <c r="W87">
-        <v>1089.59067140046</v>
+        <v>1.08959067140046</v>
       </c>
       <c r="X87">
-        <v>3780.7802822580602</v>
+        <v>3.7807802822580601</v>
       </c>
       <c r="Y87">
-        <v>1242.68238395188</v>
+        <v>1.2426823839518799</v>
       </c>
       <c r="Z87" s="4"/>
       <c r="AA87" s="4"/>
@@ -11174,76 +11174,76 @@
         <v>0.88541666666666696</v>
       </c>
       <c r="B88">
-        <v>14238.690760617999</v>
+        <v>14.238690760618001</v>
       </c>
       <c r="C88">
-        <v>4680.0313315722697</v>
+        <v>4.6800313315722697</v>
       </c>
       <c r="D88">
-        <v>21073.5731579475</v>
+        <v>21.0735731579475</v>
       </c>
       <c r="E88">
-        <v>6926.54853634131</v>
+        <v>6.9265485363413104</v>
       </c>
       <c r="F88">
-        <v>2884.42891848212</v>
+        <v>2.8844289184821199</v>
       </c>
       <c r="G88">
-        <v>948.06593802333305</v>
+        <v>0.94806593802333305</v>
       </c>
       <c r="H88">
-        <v>9669.01082164328</v>
+        <v>9.6690108216432797</v>
       </c>
       <c r="I88">
-        <v>3178.0501698765602</v>
+        <v>3.1780501698765602</v>
       </c>
       <c r="J88">
-        <v>4302.4597995991899</v>
+        <v>4.3024597995991902</v>
       </c>
       <c r="K88">
-        <v>1414.15014929929</v>
+        <v>1.4141501492992901</v>
       </c>
       <c r="L88">
-        <v>15476.725190380699</v>
+        <v>15.4767251903807</v>
       </c>
       <c r="M88">
-        <v>5086.9535702994699</v>
+        <v>5.0869535702994702</v>
       </c>
       <c r="N88">
-        <v>21783.172689378702</v>
+        <v>21.783172689378699</v>
       </c>
       <c r="O88">
-        <v>7159.7826233651003</v>
+        <v>7.1597826233650999</v>
       </c>
       <c r="P88">
-        <v>12808.9631262525</v>
+        <v>12.8089631262525</v>
       </c>
       <c r="Q88">
-        <v>4210.1025834213497</v>
+        <v>4.2101025834213504</v>
       </c>
       <c r="R88">
-        <v>1223.94735483871</v>
+        <v>1.2239473548387101</v>
       </c>
       <c r="S88">
-        <v>402.29204111119702</v>
+        <v>0.40229204111119699</v>
       </c>
       <c r="T88">
-        <v>8832.2272785571095</v>
+        <v>8.8322272785571094</v>
       </c>
       <c r="U88">
-        <v>2903.0127197888901</v>
+        <v>2.9030127197888902</v>
       </c>
       <c r="V88">
-        <v>2988.80516129032</v>
+        <v>2.9888051612903199</v>
       </c>
       <c r="W88">
-        <v>982.37274999267697</v>
+        <v>0.98237274999267699</v>
       </c>
       <c r="X88">
-        <v>3408.7438709677399</v>
+        <v>3.40874387096774</v>
       </c>
       <c r="Y88">
-        <v>1120.39992901296</v>
+        <v>1.12039992901296</v>
       </c>
       <c r="Z88" s="4"/>
       <c r="AA88" s="4"/>
@@ -11298,76 +11298,76 @@
         <v>0.89583333333333304</v>
       </c>
       <c r="B89">
-        <v>13712.5249971556</v>
+        <v>13.712524997155599</v>
       </c>
       <c r="C89">
-        <v>4507.0890084328803</v>
+        <v>4.5070890084328799</v>
       </c>
       <c r="D89">
-        <v>20276.605989069001</v>
+        <v>20.276605989069001</v>
       </c>
       <c r="E89">
-        <v>6664.5980955815203</v>
+        <v>6.6645980955815203</v>
       </c>
       <c r="F89">
-        <v>2706.42872769733</v>
+        <v>2.7064287276973298</v>
       </c>
       <c r="G89">
-        <v>889.56010459356605</v>
+        <v>0.88956010459356605</v>
       </c>
       <c r="H89">
-        <v>9331.8765531062108</v>
+        <v>9.3318765531062091</v>
       </c>
       <c r="I89">
-        <v>3067.2394944973198</v>
+        <v>3.0672394944973198</v>
       </c>
       <c r="J89">
-        <v>4152.44376753507</v>
+        <v>4.1524437675350701</v>
       </c>
       <c r="K89">
-        <v>1364.8422640378101</v>
+        <v>1.3648422640378099</v>
       </c>
       <c r="L89">
-        <v>14937.0904208416</v>
+        <v>14.937090420841599</v>
       </c>
       <c r="M89">
-        <v>4909.5841989501096</v>
+        <v>4.9095841989501103</v>
       </c>
       <c r="N89">
-        <v>21023.647839679299</v>
+        <v>21.023647839679299</v>
       </c>
       <c r="O89">
-        <v>6910.1388777805496</v>
+        <v>6.9101388777805504</v>
       </c>
       <c r="P89">
-        <v>12362.3465597862</v>
+        <v>12.3623465597862</v>
       </c>
       <c r="Q89">
-        <v>4063.3068169143298</v>
+        <v>4.0633068169143298</v>
       </c>
       <c r="R89">
-        <v>1131.4662580645099</v>
+        <v>1.1314662580645101</v>
       </c>
       <c r="S89">
-        <v>371.89497457201202</v>
+        <v>0.37189497457201198</v>
       </c>
       <c r="T89">
-        <v>8524.2695631262504</v>
+        <v>8.5242695631262499</v>
       </c>
       <c r="U89">
-        <v>2801.7919136595701</v>
+        <v>2.8017919136595699</v>
       </c>
       <c r="V89">
-        <v>2762.9719354838699</v>
+        <v>2.7629719354838702</v>
       </c>
       <c r="W89">
-        <v>908.14495824882704</v>
+        <v>0.90814495824882702</v>
       </c>
       <c r="X89">
-        <v>3151.1802016129</v>
+        <v>3.1511802016128998</v>
       </c>
       <c r="Y89">
-        <v>1035.74284482448</v>
+        <v>1.0357428448244801</v>
       </c>
       <c r="Z89" s="4"/>
       <c r="AA89" s="4"/>
@@ -11422,76 +11422,76 @@
         <v>0.90625</v>
       </c>
       <c r="B90">
-        <v>13184.538577348199</v>
+        <v>13.184538577348199</v>
       </c>
       <c r="C90">
-        <v>4333.5482644919002</v>
+        <v>4.3335482644919097</v>
       </c>
       <c r="D90">
-        <v>19418.1486095982</v>
+        <v>19.418148609598202</v>
       </c>
       <c r="E90">
-        <v>6382.4367999759897</v>
+        <v>6.3824367999759897</v>
       </c>
       <c r="F90">
-        <v>2571.4333905714602</v>
+        <v>2.5714333905714599</v>
       </c>
       <c r="G90">
-        <v>845.18928300703203</v>
+        <v>0.845189283007032</v>
       </c>
       <c r="H90">
-        <v>8981.2569138276504</v>
+        <v>8.9812569138276501</v>
       </c>
       <c r="I90">
-        <v>2951.9963921029198</v>
+        <v>2.9519963921029202</v>
       </c>
       <c r="J90">
-        <v>3996.4270941883701</v>
+        <v>3.9964270941883702</v>
       </c>
       <c r="K90">
-        <v>1313.56206336587</v>
+        <v>1.31356206336587</v>
       </c>
       <c r="L90">
-        <v>14375.870260521</v>
+        <v>14.375870260520999</v>
       </c>
       <c r="M90">
-        <v>4725.1200527467799</v>
+        <v>4.7251200527467798</v>
       </c>
       <c r="N90">
-        <v>20233.741995991899</v>
+        <v>20.233741995991899</v>
       </c>
       <c r="O90">
-        <v>6650.5093823726002</v>
+        <v>6.6505093823726096</v>
       </c>
       <c r="P90">
-        <v>11897.8653306613</v>
+        <v>11.8978653306613</v>
       </c>
       <c r="Q90">
-        <v>3910.63921974703</v>
+        <v>3.9106392197470301</v>
       </c>
       <c r="R90">
-        <v>1067.52870967741</v>
+        <v>1.06752870967741</v>
       </c>
       <c r="S90">
-        <v>350.87971869306898</v>
+        <v>0.350879718693069</v>
       </c>
       <c r="T90">
-        <v>8203.9935390781502</v>
+        <v>8.2039935390781498</v>
       </c>
       <c r="U90">
-        <v>2696.52227528507</v>
+        <v>2.6965222752850702</v>
       </c>
       <c r="V90">
-        <v>2606.8403225806401</v>
+        <v>2.60684032258064</v>
       </c>
       <c r="W90">
-        <v>856.82697877159796</v>
+        <v>0.85682697877159797</v>
       </c>
       <c r="X90">
-        <v>2973.11149193548</v>
+        <v>2.9731114919354802</v>
       </c>
       <c r="Y90">
-        <v>977.21449032380895</v>
+        <v>0.97721449032380903</v>
       </c>
       <c r="Z90" s="4"/>
       <c r="AA90" s="4"/>
@@ -11546,76 +11546,76 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B91">
-        <v>12590.720177322301</v>
+        <v>12.5907201773223</v>
       </c>
       <c r="C91">
-        <v>4138.36959504066</v>
+        <v>4.1383695950406603</v>
       </c>
       <c r="D91">
-        <v>18449.100092381999</v>
+        <v>18.449100092382</v>
       </c>
       <c r="E91">
-        <v>6063.92595521986</v>
+        <v>6.0639259552198599</v>
       </c>
       <c r="F91">
-        <v>2455.81093582325</v>
+        <v>2.4558109358232501</v>
       </c>
       <c r="G91">
-        <v>807.18601992953404</v>
+        <v>0.80718601992953398</v>
       </c>
       <c r="H91">
-        <v>8576.6957915831608</v>
+        <v>8.5766957915831608</v>
       </c>
       <c r="I91">
-        <v>2819.0235816478298</v>
+        <v>2.81902358164783</v>
       </c>
       <c r="J91">
-        <v>3816.4078557114199</v>
+        <v>3.8164078557114198</v>
       </c>
       <c r="K91">
-        <v>1254.39260105209</v>
+        <v>1.2543926010520901</v>
       </c>
       <c r="L91">
-        <v>13728.308537074099</v>
+        <v>13.728308537074099</v>
       </c>
       <c r="M91">
-        <v>4512.2768071275596</v>
+        <v>4.5122768071275603</v>
       </c>
       <c r="N91">
-        <v>19322.312176352701</v>
+        <v>19.3223121763527</v>
       </c>
       <c r="O91">
-        <v>6350.9368876711396</v>
+        <v>6.3509368876711401</v>
       </c>
       <c r="P91">
-        <v>11361.925450901799</v>
+        <v>11.361925450901801</v>
       </c>
       <c r="Q91">
-        <v>3734.4842999386101</v>
+        <v>3.7344842999386101</v>
       </c>
       <c r="R91">
-        <v>1019.57554838709</v>
+        <v>1.0195755483870901</v>
       </c>
       <c r="S91">
-        <v>335.11827678386101</v>
+        <v>0.33511827678386102</v>
       </c>
       <c r="T91">
-        <v>7834.4442805611197</v>
+        <v>7.8344442805611196</v>
       </c>
       <c r="U91">
-        <v>2575.0573079298902</v>
+        <v>2.5750573079298902</v>
       </c>
       <c r="V91">
-        <v>2489.7416129032199</v>
+        <v>2.4897416129032202</v>
       </c>
       <c r="W91">
-        <v>818.33849416367605</v>
+        <v>0.81833849416367599</v>
       </c>
       <c r="X91">
-        <v>2839.55995967741</v>
+        <v>2.8395599596774099</v>
       </c>
       <c r="Y91">
-        <v>933.31822444830095</v>
+        <v>0.93331822444830104</v>
       </c>
       <c r="Z91" s="4"/>
       <c r="AA91" s="4"/>
@@ -11670,76 +11670,76 @@
         <v>0.92708333333333304</v>
       </c>
       <c r="B92">
-        <v>11937.7669800892</v>
+        <v>11.937766980089201</v>
       </c>
       <c r="C92">
-        <v>3923.7542576843998</v>
+        <v>3.9237542576843998</v>
       </c>
       <c r="D92">
-        <v>17392.101005746001</v>
+        <v>17.392101005745999</v>
       </c>
       <c r="E92">
-        <v>5716.5071562540397</v>
+        <v>5.7165071562540399</v>
       </c>
       <c r="F92">
-        <v>2353.1460938813102</v>
+        <v>2.35314609388131</v>
       </c>
       <c r="G92">
-        <v>773.44171822251496</v>
+        <v>0.77344171822251495</v>
       </c>
       <c r="H92">
-        <v>8124.9358717434798</v>
+        <v>8.1249358717434799</v>
       </c>
       <c r="I92">
-        <v>2670.5372766396499</v>
+        <v>2.6705372766396498</v>
       </c>
       <c r="J92">
-        <v>3615.38637274549</v>
+        <v>3.61538637274549</v>
       </c>
       <c r="K92">
-        <v>1188.3200348017001</v>
+        <v>1.1883200348017</v>
       </c>
       <c r="L92">
-        <v>13005.197945891699</v>
+        <v>13.0051979458917</v>
       </c>
       <c r="M92">
-        <v>4274.6018495194203</v>
+        <v>4.2746018495194198</v>
       </c>
       <c r="N92">
-        <v>18304.5488777555</v>
+        <v>18.304548877755501</v>
       </c>
       <c r="O92">
-        <v>6016.4142685878296</v>
+        <v>6.0164142685878303</v>
       </c>
       <c r="P92">
-        <v>10763.459251836999</v>
+        <v>10.763459251837</v>
       </c>
       <c r="Q92">
-        <v>3537.7779728191999</v>
+        <v>3.5377779728192</v>
       </c>
       <c r="R92">
-        <v>983.039806451613</v>
+        <v>0.98303980645161304</v>
       </c>
       <c r="S92">
-        <v>323.10955913875102</v>
+        <v>0.323109559138751</v>
       </c>
       <c r="T92">
-        <v>7421.7809418837596</v>
+        <v>7.4217809418837604</v>
       </c>
       <c r="U92">
-        <v>2439.4214277166002</v>
+        <v>2.4394214277166002</v>
       </c>
       <c r="V92">
-        <v>2400.5235483870902</v>
+        <v>2.4005235483870901</v>
       </c>
       <c r="W92">
-        <v>789.01393446240195</v>
+        <v>0.78901393446240198</v>
       </c>
       <c r="X92">
-        <v>2737.8064112903198</v>
+        <v>2.73780641129032</v>
       </c>
       <c r="Y92">
-        <v>899.87345044791402</v>
+        <v>0.899873450447914</v>
       </c>
       <c r="Z92" s="4"/>
       <c r="AA92" s="4"/>
@@ -11794,76 +11794,76 @@
         <v>0.9375</v>
       </c>
       <c r="B93">
-        <v>11240.4349645743</v>
+        <v>11.2404349645743</v>
       </c>
       <c r="C93">
-        <v>3694.5523081523102</v>
+        <v>3.6945523081523102</v>
       </c>
       <c r="D93">
-        <v>16291.8516098327</v>
+        <v>16.291851609832701</v>
       </c>
       <c r="E93">
-        <v>5354.8726680846903</v>
+        <v>5.3548726680846901</v>
       </c>
       <c r="F93">
-        <v>2254.1582449576499</v>
+        <v>2.25415824495765</v>
       </c>
       <c r="G93">
-        <v>740.90598567546397</v>
+        <v>0.74090598567546395</v>
       </c>
       <c r="H93">
-        <v>7639.4625250501003</v>
+        <v>7.6394625250501003</v>
       </c>
       <c r="I93">
-        <v>2510.9699040935502</v>
+        <v>2.51096990409355</v>
       </c>
       <c r="J93">
-        <v>3399.3632865731402</v>
+        <v>3.39936328657314</v>
       </c>
       <c r="K93">
-        <v>1117.3166800251699</v>
+        <v>1.1173166800251699</v>
       </c>
       <c r="L93">
-        <v>12228.123877755501</v>
+        <v>12.2281238777555</v>
       </c>
       <c r="M93">
-        <v>4019.1899547763601</v>
+        <v>4.0191899547763601</v>
       </c>
       <c r="N93">
-        <v>17210.8330941883</v>
+        <v>17.210833094188299</v>
       </c>
       <c r="O93">
-        <v>5656.9272749460697</v>
+        <v>5.65692727494607</v>
       </c>
       <c r="P93">
-        <v>10120.331396125501</v>
+        <v>10.120331396125501</v>
       </c>
       <c r="Q93">
-        <v>3326.39206904909</v>
+        <v>3.3263920690490898</v>
       </c>
       <c r="R93">
-        <v>951.07103225806395</v>
+        <v>0.951071032258064</v>
       </c>
       <c r="S93">
-        <v>312.60193119927902</v>
+        <v>0.31260193119927898</v>
       </c>
       <c r="T93">
-        <v>6978.3218316633202</v>
+        <v>6.9783218316633198</v>
       </c>
       <c r="U93">
-        <v>2293.6634668903798</v>
+        <v>2.2936634668903801</v>
       </c>
       <c r="V93">
-        <v>2322.45774193548</v>
+        <v>2.3224577419354802</v>
       </c>
       <c r="W93">
-        <v>763.35494472378696</v>
+        <v>0.76335494472378695</v>
       </c>
       <c r="X93">
-        <v>2648.7720564516098</v>
+        <v>2.6487720564516102</v>
       </c>
       <c r="Y93">
-        <v>870.60927319757502</v>
+        <v>0.87060927319757497</v>
       </c>
       <c r="Z93" s="4"/>
       <c r="AA93" s="4"/>
@@ -11918,76 +11918,76 @@
         <v>0.94791666666666696</v>
       </c>
       <c r="B94">
-        <v>10506.102120240401</v>
+        <v>10.506102120240399</v>
       </c>
       <c r="C94">
-        <v>3453.1887743089901</v>
+        <v>3.4531887743089902</v>
       </c>
       <c r="D94">
-        <v>15168.9258380519</v>
+        <v>15.1689258380519</v>
       </c>
       <c r="E94">
-        <v>4985.7848156046302</v>
+        <v>4.9857848156046298</v>
       </c>
       <c r="F94">
-        <v>2154.2070791583101</v>
+        <v>2.1542070791583101</v>
       </c>
       <c r="G94">
-        <v>708.05362618312301</v>
+        <v>0.70805362618312295</v>
       </c>
       <c r="H94">
-        <v>7127.01843687374</v>
+        <v>7.1270184368737404</v>
       </c>
       <c r="I94">
-        <v>2342.5376775170998</v>
+        <v>2.3425376775170998</v>
       </c>
       <c r="J94">
-        <v>3171.3389178356701</v>
+        <v>3.1713389178356701</v>
       </c>
       <c r="K94">
-        <v>1042.3686944277199</v>
+        <v>1.04236869442772</v>
       </c>
       <c r="L94">
-        <v>11407.879028056101</v>
+        <v>11.407879028056101</v>
       </c>
       <c r="M94">
-        <v>3749.5885103253399</v>
+        <v>3.7495885103253399</v>
       </c>
       <c r="N94">
-        <v>16056.3553226452</v>
+        <v>16.056355322645199</v>
       </c>
       <c r="O94">
-        <v>5277.4687816575397</v>
+        <v>5.2774687816575403</v>
       </c>
       <c r="P94">
-        <v>9441.4742150968596</v>
+        <v>9.44147421509685</v>
       </c>
       <c r="Q94">
-        <v>3103.26250395842</v>
+        <v>3.1032625039584198</v>
       </c>
       <c r="R94">
-        <v>920.24400000000003</v>
+        <v>0.92024399999999995</v>
       </c>
       <c r="S94">
-        <v>302.46957568621701</v>
+        <v>0.30246957568621702</v>
       </c>
       <c r="T94">
-        <v>6510.2261042084101</v>
+        <v>6.5102261042084102</v>
       </c>
       <c r="U94">
-        <v>2139.80784157382</v>
+        <v>2.13980784157381</v>
       </c>
       <c r="V94">
-        <v>2247.1799999999998</v>
+        <v>2.24717999999999</v>
       </c>
       <c r="W94">
-        <v>738.61234747583705</v>
+        <v>0.73861234747583704</v>
       </c>
       <c r="X94">
-        <v>2562.9175</v>
+        <v>2.5629175000000002</v>
       </c>
       <c r="Y94">
-        <v>842.39024513474897</v>
+        <v>0.84239024513474903</v>
       </c>
       <c r="Z94" s="4"/>
       <c r="AA94" s="4"/>
@@ -12042,76 +12042,76 @@
         <v>0.95833333333333304</v>
       </c>
       <c r="B95">
-        <v>9760.9872541857894</v>
+        <v>9.7609872541857907</v>
       </c>
       <c r="C95">
-        <v>3208.28136130434</v>
+        <v>3.2082813613043402</v>
       </c>
       <c r="D95">
-        <v>14080.5101305521</v>
+        <v>14.080510130552099</v>
       </c>
       <c r="E95">
-        <v>4628.0398727224501</v>
+        <v>4.6280398727224501</v>
       </c>
       <c r="F95">
-        <v>2050.0214248658599</v>
+        <v>2.0500214248658599</v>
       </c>
       <c r="G95">
-        <v>673.80945762953297</v>
+        <v>0.67380945762953304</v>
       </c>
       <c r="H95">
-        <v>6607.8316633266504</v>
+        <v>6.6078316633266496</v>
       </c>
       <c r="I95">
-        <v>2171.8892374330799</v>
+        <v>2.17188923743308</v>
       </c>
       <c r="J95">
-        <v>2940.3142284569099</v>
+        <v>2.9403142284569102</v>
       </c>
       <c r="K95">
-        <v>966.43455112504</v>
+        <v>0.96643455112503995</v>
       </c>
       <c r="L95">
-        <v>10576.8414829659</v>
+        <v>10.5768414829659</v>
       </c>
       <c r="M95">
-        <v>3476.4396784473302</v>
+        <v>3.4764396784473299</v>
       </c>
       <c r="N95">
-        <v>14886.687054108201</v>
+        <v>14.886687054108201</v>
       </c>
       <c r="O95">
-        <v>4893.0174134573199</v>
+        <v>4.8930174134573203</v>
       </c>
       <c r="P95">
-        <v>8753.6847027388103</v>
+        <v>8.7536847027388092</v>
       </c>
       <c r="Q95">
-        <v>2877.1970235376002</v>
+        <v>2.8771970235376001</v>
       </c>
       <c r="R95">
-        <v>887.13348387096801</v>
+        <v>0.88713348387096802</v>
       </c>
       <c r="S95">
-        <v>291.58667532033598</v>
+        <v>0.291586675320336</v>
       </c>
       <c r="T95">
-        <v>6035.9712224448804</v>
+        <v>6.0359712224448803</v>
       </c>
       <c r="U95">
-        <v>1983.9278001346599</v>
+        <v>1.9839278001346601</v>
       </c>
       <c r="V95">
-        <v>2166.3261290322498</v>
+        <v>2.16632612903225</v>
       </c>
       <c r="W95">
-        <v>712.036965246558</v>
+        <v>0.71203696524655802</v>
       </c>
       <c r="X95">
-        <v>2470.7033467741899</v>
+        <v>2.4707033467741901</v>
       </c>
       <c r="Y95">
-        <v>812.08091869689804</v>
+        <v>0.81208091869689802</v>
       </c>
       <c r="Z95" s="4"/>
       <c r="AA95" s="4"/>
@@ -12166,76 +12166,76 @@
         <v>0.96875</v>
       </c>
       <c r="B96">
-        <v>9005.0903664102407</v>
+        <v>9.00509036641024</v>
       </c>
       <c r="C96">
-        <v>2959.8300691383502</v>
+        <v>2.9598300691383499</v>
       </c>
       <c r="D96">
-        <v>13010.5406325203</v>
+        <v>13.0105406325203</v>
       </c>
       <c r="E96">
-        <v>4276.3579056931803</v>
+        <v>4.2763579056931897</v>
       </c>
       <c r="F96">
-        <v>1941.60128208028</v>
+        <v>1.9416012820802799</v>
       </c>
       <c r="G96">
-        <v>638.17348001469304</v>
+        <v>0.63817348001469298</v>
       </c>
       <c r="H96">
-        <v>6081.9022044088097</v>
+        <v>6.0819022044088102</v>
       </c>
       <c r="I96">
-        <v>1999.0245838414601</v>
+        <v>1.99902458384146</v>
       </c>
       <c r="J96">
-        <v>2706.2892184368702</v>
+        <v>2.7062892184368699</v>
       </c>
       <c r="K96">
-        <v>889.51425011712797</v>
+        <v>0.88951425011712804</v>
       </c>
       <c r="L96">
-        <v>9735.0112424849594</v>
+        <v>9.7350112424849602</v>
       </c>
       <c r="M96">
-        <v>3199.7434591423398</v>
+        <v>3.1997434591423399</v>
       </c>
       <c r="N96">
-        <v>13701.8282885771</v>
+        <v>13.701828288577101</v>
       </c>
       <c r="O96">
-        <v>4503.5731703454103</v>
+        <v>4.50357317034541</v>
       </c>
       <c r="P96">
-        <v>8056.9628590514303</v>
+        <v>8.0569628590514295</v>
       </c>
       <c r="Q96">
-        <v>2648.1956277866502</v>
+        <v>2.6481956277866501</v>
       </c>
       <c r="R96">
-        <v>851.73948387096698</v>
+        <v>0.85173948387096698</v>
       </c>
       <c r="S96">
-        <v>279.95323010163497</v>
+        <v>0.27995323010163498</v>
       </c>
       <c r="T96">
-        <v>5555.55718637274</v>
+        <v>5.5555571863727398</v>
       </c>
       <c r="U96">
-        <v>1826.02334257292</v>
+        <v>1.82602334257292</v>
       </c>
       <c r="V96">
-        <v>2079.89612903225</v>
+        <v>2.07989612903225</v>
       </c>
       <c r="W96">
-        <v>683.62879803594797</v>
+        <v>0.683628798035949</v>
       </c>
       <c r="X96">
-        <v>2372.1295967741898</v>
+        <v>2.3721295967741902</v>
       </c>
       <c r="Y96">
-        <v>779.68129388402303</v>
+        <v>0.77968129388402296</v>
       </c>
       <c r="Z96" s="4"/>
       <c r="AA96" s="4"/>
@@ -12290,76 +12290,76 @@
         <v>0.97916666666666696</v>
       </c>
       <c r="B97">
-        <v>8259.2946939039302</v>
+        <v>8.2592946939039305</v>
       </c>
       <c r="C97">
-        <v>2714.6988858743398</v>
+        <v>2.7146988858743399</v>
       </c>
       <c r="D97">
-        <v>11968.0710682831</v>
+        <v>11.9680710682831</v>
       </c>
       <c r="E97">
-        <v>3933.7147297956999</v>
+        <v>3.9337147297957</v>
       </c>
       <c r="F97">
-        <v>1835.6406681104099</v>
+        <v>1.83564066811041</v>
       </c>
       <c r="G97">
-        <v>603.34591042780198</v>
+        <v>0.60334591042780195</v>
       </c>
       <c r="H97">
-        <v>5562.7154308617201</v>
+        <v>5.5627154308617204</v>
       </c>
       <c r="I97">
-        <v>1828.3761437574301</v>
+        <v>1.82837614375744</v>
       </c>
       <c r="J97">
-        <v>2475.2645290581099</v>
+        <v>2.4752645290581099</v>
       </c>
       <c r="K97">
-        <v>813.58010681444705</v>
+        <v>0.81358010681444703</v>
       </c>
       <c r="L97">
-        <v>8903.9736973947893</v>
+        <v>8.9039736973947896</v>
       </c>
       <c r="M97">
-        <v>2926.59462726434</v>
+        <v>2.9265946272643402</v>
       </c>
       <c r="N97">
-        <v>12532.160020040001</v>
+        <v>12.532160020039999</v>
       </c>
       <c r="O97">
-        <v>4119.1218021451896</v>
+        <v>4.1191218021451901</v>
       </c>
       <c r="P97">
-        <v>7369.1733466933802</v>
+        <v>7.3691733466933798</v>
       </c>
       <c r="Q97">
-        <v>2422.13014736584</v>
+        <v>2.4221301473658401</v>
       </c>
       <c r="R97">
-        <v>817.48722580645097</v>
+        <v>0.81748722580645095</v>
       </c>
       <c r="S97">
-        <v>268.69505730934401</v>
+        <v>0.26869505730934401</v>
       </c>
       <c r="T97">
-        <v>5081.3023046092103</v>
+        <v>5.0813023046092098</v>
       </c>
       <c r="U97">
-        <v>1670.1433011337699</v>
+        <v>1.6701433011337701</v>
       </c>
       <c r="V97">
-        <v>1996.25419354838</v>
+        <v>1.99625419354838</v>
       </c>
       <c r="W97">
-        <v>656.13702331600405</v>
+        <v>0.65613702331600399</v>
       </c>
       <c r="X97">
-        <v>2276.73564516129</v>
+        <v>2.2767356451612901</v>
       </c>
       <c r="Y97">
-        <v>748.32681825865996</v>
+        <v>0.74832681825865999</v>
       </c>
       <c r="Z97" s="4"/>
       <c r="AA97" s="4"/>
@@ -12414,76 +12414,76 @@
         <v>0.98958333333333304</v>
       </c>
       <c r="B98">
-        <v>7524.9618495700997</v>
+        <v>7.5249618495700998</v>
       </c>
       <c r="C98">
-        <v>2473.3353520310302</v>
+        <v>2.4733353520310302</v>
       </c>
       <c r="D98">
-        <v>10946.1754374558</v>
+        <v>10.9461754374558</v>
       </c>
       <c r="E98">
-        <v>3597.8338787910202</v>
+        <v>3.59783387879102</v>
       </c>
       <c r="F98">
-        <v>1735.6895023110701</v>
+        <v>1.7356895023110701</v>
       </c>
       <c r="G98">
-        <v>570.49355093546103</v>
+        <v>0.57049355093546095</v>
       </c>
       <c r="H98">
-        <v>5050.2713426853697</v>
+        <v>5.0502713426853703</v>
       </c>
       <c r="I98">
-        <v>1659.94391718099</v>
+        <v>1.65994391718099</v>
       </c>
       <c r="J98">
-        <v>2247.2401603206399</v>
+        <v>2.24724016032064</v>
       </c>
       <c r="K98">
-        <v>738.63212121699496</v>
+        <v>0.73863212121699495</v>
       </c>
       <c r="L98">
-        <v>8083.72884769539</v>
+        <v>8.0837288476953901</v>
       </c>
       <c r="M98">
-        <v>2656.9931828133199</v>
+        <v>2.65699318281332</v>
       </c>
       <c r="N98">
-        <v>11377.6822484969</v>
+        <v>11.3776822484969</v>
       </c>
       <c r="O98">
-        <v>3739.66330885667</v>
+        <v>3.7396633088566702</v>
       </c>
       <c r="P98">
-        <v>6690.3161656646598</v>
+        <v>6.6903161656646599</v>
       </c>
       <c r="Q98">
-        <v>2199.00058227517</v>
+        <v>2.1990005822751701</v>
       </c>
       <c r="R98">
-        <v>786.66019354838704</v>
+        <v>0.78666019354838701</v>
       </c>
       <c r="S98">
-        <v>258.562701796282</v>
+        <v>0.25856270179628199</v>
       </c>
       <c r="T98">
-        <v>4613.2065771543002</v>
+        <v>4.6132065771543003</v>
       </c>
       <c r="U98">
-        <v>1516.2876758172099</v>
+        <v>1.5162876758172099</v>
       </c>
       <c r="V98">
-        <v>1920.9764516129001</v>
+        <v>1.9209764516129</v>
       </c>
       <c r="W98">
-        <v>631.39442606805403</v>
+        <v>0.63139442606805396</v>
       </c>
       <c r="X98">
-        <v>2190.8810887096702</v>
+        <v>2.1908810887096699</v>
       </c>
       <c r="Y98">
-        <v>720.10779019583299</v>
+        <v>0.72010779019583304</v>
       </c>
     </row>
   </sheetData>
@@ -12498,6 +12498,14 @@
     <protectedRange sqref="T3:W97" name="Plage1_13"/>
   </protectedRanges>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12510,14 +12518,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12852,6 +12852,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12864,14 +12872,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_winter_week.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_winter_week.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\max\github\rhtlab\grodent-magnenat-mini-projet-trey\input-data\load_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D565C2D-3590-4AF0-ABF2-1D7C4BC230CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158F7420-C329-4E7B-8A26-0DA3E7965F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3771" yWindow="1663" windowWidth="20983" windowHeight="14794" activeTab="1" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
+    <workbookView xWindow="2914" yWindow="2914" windowWidth="19749" windowHeight="11512" activeTab="1" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
   <sheets>
     <sheet name="load" sheetId="5" r:id="rId1"/>
@@ -12498,6 +12498,14 @@
     <protectedRange sqref="T3:W97" name="Plage1_13"/>
   </protectedRanges>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12510,14 +12518,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12888,13 +12888,13 @@
         <v>0.375</v>
       </c>
       <c r="V12">
-        <v>4.8376171900000001E-2</v>
+        <v>2.0517543907087502E-2</v>
       </c>
       <c r="W12">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>2.4705898399999999E-2</v>
+        <v>2.1000013639999999E-2</v>
       </c>
       <c r="Y12">
         <v>0</v>
@@ -12905,13 +12905,13 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="V13">
-        <v>7.49433672E-2</v>
+        <v>3.1785355613699995E-2</v>
       </c>
       <c r="W13">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>4.6312296900000001E-2</v>
+        <v>3.9365452364999998E-2</v>
       </c>
       <c r="Y13">
         <v>0</v>
@@ -12922,13 +12922,13 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="V14">
-        <v>9.3193320300000007E-2</v>
+        <v>3.9525616972237505E-2</v>
       </c>
       <c r="W14">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>5.4580335899999999E-2</v>
+        <v>4.6393285515E-2</v>
       </c>
       <c r="Y14">
         <v>0</v>
@@ -12939,13 +12939,13 @@
         <v>0.5</v>
       </c>
       <c r="V15">
-        <v>0.1008156719</v>
+        <v>4.2758446844587503E-2</v>
       </c>
       <c r="W15">
         <v>0</v>
       </c>
       <c r="X15">
-        <v>6.0555222700000001E-2</v>
+        <v>5.1471939294999998E-2</v>
       </c>
       <c r="Y15">
         <v>0</v>
@@ -12956,13 +12956,13 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="V16">
-        <v>9.47980234E-2</v>
+        <v>4.0206211674524997E-2</v>
       </c>
       <c r="W16">
         <v>0</v>
       </c>
       <c r="X16">
-        <v>5.2116585899999998E-2</v>
+        <v>4.4299098014999996E-2</v>
       </c>
       <c r="Y16">
         <v>0</v>
@@ -12973,13 +12973,13 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="V17">
-        <v>7.373625780000001E-2</v>
+        <v>3.1273390339425007E-2</v>
       </c>
       <c r="W17">
         <v>0</v>
       </c>
       <c r="X17">
-        <v>3.2105078099999997E-2</v>
+        <v>2.7289316384999995E-2</v>
       </c>
       <c r="Y17">
         <v>0</v>
@@ -12990,13 +12990,13 @@
         <v>0.625</v>
       </c>
       <c r="V18">
-        <v>4.2594929699999999E-2</v>
+        <v>1.80655745590125E-2</v>
       </c>
       <c r="W18">
         <v>0</v>
       </c>
       <c r="X18">
-        <v>1.9520521499999999E-2</v>
+        <v>1.6592443274999997E-2</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -13007,7 +13007,7 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="V19">
-        <v>2.3089286999999998E-3</v>
+        <v>9.7927438488749994E-4</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -13140,6 +13140,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -13152,14 +13160,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
